--- a/data.xlsx
+++ b/data.xlsx
@@ -546,12 +546,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>23 days, 4:35:53.496961</t>
+          <t>22 days, 4:35:23.556806</t>
         </is>
       </c>
     </row>
@@ -603,12 +603,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>23 days, 4:20:53.496894</t>
+          <t>22 days, 4:20:23.556746</t>
         </is>
       </c>
     </row>
@@ -665,12 +665,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>23 days, 1:50:53.496840</t>
+          <t>22 days, 1:50:23.556696</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>23 days, 1:50:53.496794</t>
+          <t>22 days, 1:50:23.556655</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>23 days, 1:50:53.496699</t>
+          <t>22 days, 1:50:23.556619</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>23 days, 1:50:53.496652</t>
+          <t>22 days, 1:50:23.556583</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>23 days, 1:50:53.496611</t>
+          <t>22 days, 1:50:23.556547</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>23 days, 1:50:53.496570</t>
+          <t>22 days, 1:50:23.556515</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>22 days, 21:50:53.496532</t>
+          <t>21 days, 21:50:23.556482</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>20 days, 1:50:53.496437</t>
+          <t>19 days, 1:50:23.556394</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>20 days, 1:50:53.496396</t>
+          <t>19 days, 1:50:23.556359</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>20 days, 1:50:53.496356</t>
+          <t>19 days, 1:50:23.556325</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>20 days, 1:50:53.496316</t>
+          <t>19 days, 1:50:23.556291</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>20 days, 1:50:53.496278</t>
+          <t>19 days, 1:50:23.556257</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>20 days, 1:50:53.496240</t>
+          <t>19 days, 1:50:23.556223</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>20 days, 1:20:53.496197</t>
+          <t>19 days, 1:20:23.556184</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>20 days, 1:20:53.496156</t>
+          <t>19 days, 1:20:23.556150</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>20 days, 1:20:53.496115</t>
+          <t>19 days, 1:20:23.556098</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>20 days, 1:20:53.496074</t>
+          <t>19 days, 1:20:23.556061</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>20 days, 1:20:53.496038</t>
+          <t>19 days, 1:20:23.556030</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>20 days, 1:20:53.496002</t>
+          <t>19 days, 1:20:23.555999</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>20 days, 1:20:53.495967</t>
+          <t>19 days, 1:20:23.555970</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>20 days, 1:20:53.495935</t>
+          <t>19 days, 1:20:23.555942</t>
         </is>
       </c>
     </row>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>19 days, 21:50:53.495897</t>
+          <t>18 days, 21:50:23.555908</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>19 days, 21:50:53.495857</t>
+          <t>18 days, 21:50:23.555874</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495818</t>
+          <t>18 days, 21:20:23.555842</t>
         </is>
       </c>
     </row>
@@ -2136,12 +2136,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495781</t>
+          <t>18 days, 21:20:23.555811</t>
         </is>
       </c>
     </row>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495718</t>
+          <t>18 days, 21:20:23.555780</t>
         </is>
       </c>
     </row>
@@ -2250,12 +2250,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495677</t>
+          <t>18 days, 21:20:23.555748</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495640</t>
+          <t>18 days, 21:20:23.555715</t>
         </is>
       </c>
     </row>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495603</t>
+          <t>18 days, 21:20:23.555683</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495566</t>
+          <t>18 days, 21:20:23.555652</t>
         </is>
       </c>
     </row>
@@ -2478,12 +2478,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495529</t>
+          <t>18 days, 21:20:23.555620</t>
         </is>
       </c>
     </row>
@@ -2535,12 +2535,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495493</t>
+          <t>18 days, 21:20:23.555587</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2592,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495459</t>
+          <t>18 days, 21:20:23.555556</t>
         </is>
       </c>
     </row>
@@ -2649,12 +2649,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495423</t>
+          <t>18 days, 21:20:23.555525</t>
         </is>
       </c>
     </row>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495387</t>
+          <t>18 days, 21:20:23.555494</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495352</t>
+          <t>18 days, 21:20:23.555464</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495317</t>
+          <t>18 days, 21:20:23.555433</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495282</t>
+          <t>18 days, 21:20:23.555403</t>
         </is>
       </c>
     </row>
@@ -2934,12 +2934,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495247</t>
+          <t>18 days, 21:20:23.555372</t>
         </is>
       </c>
     </row>
@@ -2991,12 +2991,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495212</t>
+          <t>18 days, 21:20:23.555340</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495175</t>
+          <t>18 days, 21:20:23.555310</t>
         </is>
       </c>
     </row>
@@ -3105,12 +3105,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495138</t>
+          <t>18 days, 21:20:23.555278</t>
         </is>
       </c>
     </row>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495101</t>
+          <t>18 days, 21:20:23.555247</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3219,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495063</t>
+          <t>18 days, 21:20:23.555217</t>
         </is>
       </c>
     </row>
@@ -3276,12 +3276,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>19 days, 21:20:53.495024</t>
+          <t>18 days, 21:20:23.555182</t>
         </is>
       </c>
     </row>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>19 days, 20:20:53.494992</t>
+          <t>18 days, 20:20:23.555156</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -3443,12 +3443,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>19 days, 0:50:53.494906</t>
+          <t>18 days, 0:50:23.555072</t>
         </is>
       </c>
     </row>
@@ -3495,17 +3495,17 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>PEPCODC &amp; WASA02 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>19 days, 0:50:53.494871</t>
+          <t>18 days, 0:50:23.555041</t>
         </is>
       </c>
     </row>
@@ -3552,17 +3552,17 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>PEPCODC &amp; WASA02 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>19 days, 0:50:53.494836</t>
+          <t>18 days, 0:50:23.555013</t>
         </is>
       </c>
     </row>
@@ -3609,17 +3609,17 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>PEPCODC &amp; WASA02 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>19 days, 0:50:53.494804</t>
+          <t>18 days, 0:50:23.554985</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3671,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>19 days, 0:20:53.494749</t>
+          <t>18 days, 0:20:23.554952</t>
         </is>
       </c>
     </row>
@@ -3728,12 +3728,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>19 days, 0:20:53.494703</t>
+          <t>18 days, 0:20:23.554917</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>19 days, 0:20:53.494662</t>
+          <t>18 days, 0:20:23.554881</t>
         </is>
       </c>
     </row>
@@ -3842,12 +3842,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>19 days, 0:20:53.494623</t>
+          <t>18 days, 0:20:23.554848</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>19 days, 0:20:53.494585</t>
+          <t>18 days, 0:20:23.554813</t>
         </is>
       </c>
     </row>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>19 days, 0:20:53.494545</t>
+          <t>18 days, 0:20:23.554776</t>
         </is>
       </c>
     </row>
@@ -4013,12 +4013,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>18 days, 23:05:53.494508</t>
+          <t>17 days, 23:05:23.554742</t>
         </is>
       </c>
     </row>
@@ -4070,12 +4070,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>18 days, 23:05:53.494473</t>
+          <t>17 days, 23:05:23.554711</t>
         </is>
       </c>
     </row>
@@ -4127,12 +4127,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>18 days, 23:05:53.494439</t>
+          <t>17 days, 23:05:23.554679</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4184,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>18 days, 23:05:53.494400</t>
+          <t>17 days, 23:05:23.554645</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>18 days, 23:05:53.494361</t>
+          <t>17 days, 23:05:23.554611</t>
         </is>
       </c>
     </row>
@@ -4298,12 +4298,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>18 days, 23:05:53.494321</t>
+          <t>17 days, 23:05:23.554576</t>
         </is>
       </c>
     </row>
@@ -4355,12 +4355,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>18 days, 23:05:53.494285</t>
+          <t>17 days, 23:05:23.554544</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4412,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>18 days, 23:05:53.494245</t>
+          <t>17 days, 23:05:23.554507</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>18 days, 23:05:53.494208</t>
+          <t>17 days, 23:05:23.554475</t>
         </is>
       </c>
     </row>
@@ -4526,12 +4526,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>18 days, 23:05:53.494172</t>
+          <t>17 days, 23:05:23.554444</t>
         </is>
       </c>
     </row>
@@ -4583,12 +4583,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>18 days, 23:05:53.494137</t>
+          <t>17 days, 23:05:23.554412</t>
         </is>
       </c>
     </row>
@@ -4636,12 +4636,12 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -4689,12 +4689,12 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -4795,12 +4795,12 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>18 days, 18:50:53.493965</t>
+          <t>17 days, 18:50:23.554264</t>
         </is>
       </c>
     </row>
@@ -4909,12 +4909,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>18 days, 18:50:53.493921</t>
+          <t>17 days, 18:50:23.554227</t>
         </is>
       </c>
     </row>
@@ -4966,12 +4966,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>18 days, 18:50:53.493875</t>
+          <t>17 days, 18:50:23.554187</t>
         </is>
       </c>
     </row>
@@ -5023,12 +5023,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>18 days, 18:50:53.493833</t>
+          <t>17 days, 18:50:23.554151</t>
         </is>
       </c>
     </row>
@@ -5076,12 +5076,12 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5134,12 +5134,12 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5192,12 +5192,12 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5250,12 +5250,12 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5308,12 +5308,12 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5366,12 +5366,12 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5482,12 +5482,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5598,12 +5598,12 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5772,12 +5772,12 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5830,12 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5888,12 +5888,12 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -5946,12 +5946,12 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6004,12 +6004,12 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6120,12 +6120,12 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6178,12 +6178,12 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6236,12 +6236,12 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6294,12 +6294,12 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6352,12 +6352,12 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6410,12 +6410,12 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6468,12 +6468,12 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6816,12 +6816,12 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6932,12 +6932,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7048,12 +7048,12 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7106,12 +7106,12 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7164,12 +7164,12 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7222,12 +7222,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7280,12 +7280,12 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7386,12 +7386,12 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7497,12 +7497,12 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>17 days, 3:50:53.492387</t>
+          <t>16 days, 3:50:23.552849</t>
         </is>
       </c>
     </row>
@@ -7612,12 +7612,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7670,12 +7670,12 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7728,12 +7728,12 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7844,12 +7844,12 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7902,12 +7902,12 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -7959,12 +7959,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>17 days, 3:50:53.492161</t>
+          <t>16 days, 3:50:23.552650</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -8075,12 +8075,12 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -8133,12 +8133,12 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -8191,12 +8191,12 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -8307,12 +8307,12 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>17 days, 3:50:53.491945</t>
+          <t>16 days, 3:50:23.552461</t>
         </is>
       </c>
     </row>
@@ -8422,12 +8422,12 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -8533,12 +8533,12 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>16 days, 23:05:53.491816</t>
+          <t>15 days, 23:05:23.552348</t>
         </is>
       </c>
     </row>
@@ -8643,12 +8643,12 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -8701,12 +8701,12 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -8754,12 +8754,12 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -8869,12 +8869,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.491597</t>
+          <t>15 days, 18:50:23.552190</t>
         </is>
       </c>
     </row>
@@ -8931,12 +8931,12 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.491540</t>
+          <t>15 days, 18:50:23.552147</t>
         </is>
       </c>
     </row>
@@ -8993,12 +8993,12 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.491494</t>
+          <t>15 days, 18:50:23.552096</t>
         </is>
       </c>
     </row>
@@ -9055,12 +9055,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.491447</t>
+          <t>15 days, 18:50:23.552055</t>
         </is>
       </c>
     </row>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.491394</t>
+          <t>15 days, 18:50:23.552011</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.491346</t>
+          <t>15 days, 18:50:23.551969</t>
         </is>
       </c>
     </row>
@@ -9241,12 +9241,12 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.491298</t>
+          <t>15 days, 18:50:23.551929</t>
         </is>
       </c>
     </row>
@@ -9303,12 +9303,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.491251</t>
+          <t>15 days, 18:50:23.551890</t>
         </is>
       </c>
     </row>
@@ -9365,12 +9365,12 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.491203</t>
+          <t>15 days, 18:50:23.551847</t>
         </is>
       </c>
     </row>
@@ -9427,12 +9427,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.491157</t>
+          <t>15 days, 18:50:23.551806</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.491110</t>
+          <t>15 days, 18:50:23.551763</t>
         </is>
       </c>
     </row>
@@ -9551,12 +9551,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.491062</t>
+          <t>15 days, 18:50:23.551719</t>
         </is>
       </c>
     </row>
@@ -9613,12 +9613,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.491017</t>
+          <t>15 days, 18:50:23.551678</t>
         </is>
       </c>
     </row>
@@ -9675,12 +9675,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.490971</t>
+          <t>15 days, 18:50:23.551636</t>
         </is>
       </c>
     </row>
@@ -9737,12 +9737,12 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.490927</t>
+          <t>15 days, 18:50:23.551595</t>
         </is>
       </c>
     </row>
@@ -9799,12 +9799,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.490880</t>
+          <t>15 days, 18:50:23.551552</t>
         </is>
       </c>
     </row>
@@ -9861,12 +9861,12 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.490833</t>
+          <t>15 days, 18:50:23.551509</t>
         </is>
       </c>
     </row>
@@ -9923,12 +9923,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>16 days, 18:50:53.490786</t>
+          <t>15 days, 18:50:23.551466</t>
         </is>
       </c>
     </row>
@@ -9976,12 +9976,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>16 days, 4:50:53.490729</t>
+          <t>15 days, 4:50:23.551432</t>
         </is>
       </c>
     </row>
@@ -10029,12 +10029,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>16 days, 4:50:53.490688</t>
+          <t>15 days, 4:50:23.551399</t>
         </is>
       </c>
     </row>
@@ -10082,12 +10082,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>16 days, 4:50:53.490649</t>
+          <t>15 days, 4:50:23.551364</t>
         </is>
       </c>
     </row>
@@ -10135,12 +10135,12 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>16 days, 4:50:53.490613</t>
+          <t>15 days, 4:50:23.551332</t>
         </is>
       </c>
     </row>
@@ -10188,12 +10188,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>16 days, 4:50:53.490575</t>
+          <t>15 days, 4:50:23.551297</t>
         </is>
       </c>
     </row>
@@ -10241,12 +10241,12 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>16 days, 4:50:53.490540</t>
+          <t>15 days, 4:50:23.551265</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490502</t>
+          <t>15 days, 4:35:23.551238</t>
         </is>
       </c>
     </row>
@@ -10360,12 +10360,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490468</t>
+          <t>15 days, 4:35:23.551209</t>
         </is>
       </c>
     </row>
@@ -10422,12 +10422,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490434</t>
+          <t>15 days, 4:35:23.551179</t>
         </is>
       </c>
     </row>
@@ -10484,12 +10484,12 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490403</t>
+          <t>15 days, 4:35:23.551152</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490368</t>
+          <t>15 days, 4:35:23.551122</t>
         </is>
       </c>
     </row>
@@ -10608,12 +10608,12 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490336</t>
+          <t>15 days, 4:35:23.551081</t>
         </is>
       </c>
     </row>
@@ -10670,12 +10670,12 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490304</t>
+          <t>15 days, 4:35:23.551052</t>
         </is>
       </c>
     </row>
@@ -10732,12 +10732,12 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490271</t>
+          <t>15 days, 4:35:23.551021</t>
         </is>
       </c>
     </row>
@@ -10794,12 +10794,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490236</t>
+          <t>15 days, 4:35:23.550990</t>
         </is>
       </c>
     </row>
@@ -10856,12 +10856,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490202</t>
+          <t>15 days, 4:35:23.550958</t>
         </is>
       </c>
     </row>
@@ -10918,12 +10918,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490169</t>
+          <t>15 days, 4:35:23.550924</t>
         </is>
       </c>
     </row>
@@ -10980,12 +10980,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490134</t>
+          <t>15 days, 4:35:23.550892</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490100</t>
+          <t>15 days, 4:35:23.550861</t>
         </is>
       </c>
     </row>
@@ -11104,12 +11104,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490065</t>
+          <t>15 days, 4:35:23.550829</t>
         </is>
       </c>
     </row>
@@ -11166,12 +11166,12 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490030</t>
+          <t>15 days, 4:35:23.550796</t>
         </is>
       </c>
     </row>
@@ -11228,12 +11228,12 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>16 days, 4:35:53.490000</t>
+          <t>15 days, 4:35:23.550769</t>
         </is>
       </c>
     </row>
@@ -11281,12 +11281,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -11338,12 +11338,12 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>15 days, 21:20:53.489929</t>
+          <t>14 days, 21:20:23.550708</t>
         </is>
       </c>
     </row>
@@ -11395,12 +11395,12 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>15 days, 21:20:53.489888</t>
+          <t>14 days, 21:20:23.550676</t>
         </is>
       </c>
     </row>
@@ -11448,12 +11448,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -11558,12 +11558,12 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>13 days, 4:35:53.489790</t>
+          <t>12 days, 4:35:23.550592</t>
         </is>
       </c>
     </row>
@@ -11615,12 +11615,12 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>13 days, 4:35:53.489727</t>
+          <t>12 days, 4:35:23.550558</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>13 days, 4:35:53.489689</t>
+          <t>12 days, 4:35:23.550527</t>
         </is>
       </c>
     </row>
@@ -11729,12 +11729,12 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>13 days, 4:35:53.489653</t>
+          <t>12 days, 4:35:23.550494</t>
         </is>
       </c>
     </row>
@@ -11786,12 +11786,12 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>13 days, 4:35:53.489616</t>
+          <t>12 days, 4:35:23.550461</t>
         </is>
       </c>
     </row>
@@ -11843,12 +11843,12 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>13 days, 4:35:53.489583</t>
+          <t>12 days, 4:35:23.550432</t>
         </is>
       </c>
     </row>
@@ -11900,12 +11900,12 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>13 days, 4:35:53.489550</t>
+          <t>12 days, 4:35:23.550403</t>
         </is>
       </c>
     </row>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>12 days, 21:20:53.489512</t>
+          <t>11 days, 21:20:23.550369</t>
         </is>
       </c>
     </row>
@@ -12006,12 +12006,12 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>12 days, 21:20:53.489472</t>
+          <t>11 days, 21:20:23.550333</t>
         </is>
       </c>
     </row>
@@ -12059,12 +12059,12 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>12 days, 21:20:53.489432</t>
+          <t>11 days, 21:20:23.550298</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>12 days, 21:05:53.489398</t>
+          <t>11 days, 21:05:23.550268</t>
         </is>
       </c>
     </row>
@@ -12165,12 +12165,12 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>12 days, 21:05:53.489364</t>
+          <t>11 days, 21:05:23.550239</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>12 days, 21:05:53.489327</t>
+          <t>11 days, 21:05:23.550206</t>
         </is>
       </c>
     </row>
@@ -12275,12 +12275,12 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>12 days, 0:20:53.489291</t>
+          <t>11 days, 0:20:23.550176</t>
         </is>
       </c>
     </row>
@@ -12328,12 +12328,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -12381,12 +12381,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -12439,12 +12439,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -12497,12 +12497,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -12555,12 +12555,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -12613,12 +12613,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -12719,12 +12719,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -12772,12 +12772,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -12825,12 +12825,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -12878,12 +12878,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -12936,12 +12936,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -12994,12 +12994,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13052,12 +13052,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13110,12 +13110,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13168,12 +13168,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13226,12 +13226,12 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13284,12 +13284,12 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13337,12 +13337,12 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13390,12 +13390,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13443,12 +13443,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13496,12 +13496,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13549,12 +13549,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13602,12 +13602,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13660,12 +13660,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13713,12 +13713,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13766,12 +13766,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13824,12 +13824,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13882,12 +13882,12 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13935,12 +13935,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -13988,12 +13988,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14041,12 +14041,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14094,12 +14094,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14147,12 +14147,12 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14200,12 +14200,12 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14253,12 +14253,12 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14306,12 +14306,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14359,12 +14359,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14412,12 +14412,12 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14465,12 +14465,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14518,12 +14518,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14571,12 +14571,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14624,12 +14624,12 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14677,12 +14677,12 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14734,12 +14734,12 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>10 days, 22:35:53.487887</t>
+          <t>9 days, 22:35:23.548927</t>
         </is>
       </c>
     </row>
@@ -14787,12 +14787,12 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -14897,12 +14897,12 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>9 days, 18:50:53.487725</t>
+          <t>8 days, 18:50:23.548822</t>
         </is>
       </c>
     </row>
@@ -14954,12 +14954,12 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>9 days, 18:50:53.487674</t>
+          <t>8 days, 18:50:23.548783</t>
         </is>
       </c>
     </row>
@@ -15011,12 +15011,12 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>9 days, 18:50:53.487628</t>
+          <t>8 days, 18:50:23.548745</t>
         </is>
       </c>
     </row>
@@ -15068,12 +15068,12 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>9 days, 18:50:53.487585</t>
+          <t>8 days, 18:50:23.548707</t>
         </is>
       </c>
     </row>
@@ -15125,12 +15125,12 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>9 days, 18:50:53.487542</t>
+          <t>8 days, 18:50:23.548668</t>
         </is>
       </c>
     </row>
@@ -15182,12 +15182,12 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>9 days, 18:50:53.487501</t>
+          <t>8 days, 18:50:23.548628</t>
         </is>
       </c>
     </row>
@@ -15239,12 +15239,12 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>9 days, 18:50:53.487457</t>
+          <t>8 days, 18:50:23.548588</t>
         </is>
       </c>
     </row>
@@ -15296,12 +15296,12 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>9 days, 18:50:53.487416</t>
+          <t>8 days, 18:50:23.548549</t>
         </is>
       </c>
     </row>
@@ -15353,12 +15353,12 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>9 days, 18:50:53.487376</t>
+          <t>8 days, 18:50:23.548511</t>
         </is>
       </c>
     </row>
@@ -15410,12 +15410,12 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>9 days, 18:50:53.487333</t>
+          <t>8 days, 18:50:23.548470</t>
         </is>
       </c>
     </row>
@@ -15468,12 +15468,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -15579,12 +15579,12 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -15637,12 +15637,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -15695,12 +15695,12 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -15753,12 +15753,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -15811,12 +15811,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -15869,12 +15869,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -15927,12 +15927,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -15989,12 +15989,12 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>8 days, 23:50:53.487018</t>
+          <t>7 days, 23:50:23.548192</t>
         </is>
       </c>
     </row>
@@ -16047,12 +16047,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16105,12 +16105,12 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16163,12 +16163,12 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16221,12 +16221,12 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16279,12 +16279,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16337,12 +16337,12 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16395,12 +16395,12 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16457,12 +16457,12 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>8 days, 23:35:53.486787</t>
+          <t>7 days, 23:35:23.547954</t>
         </is>
       </c>
     </row>
@@ -16515,12 +16515,12 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16573,12 +16573,12 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16631,12 +16631,12 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16689,12 +16689,12 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16747,12 +16747,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16805,12 +16805,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16867,12 +16867,12 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>8 days, 23:35:53.486544</t>
+          <t>7 days, 23:35:23.547773</t>
         </is>
       </c>
     </row>
@@ -16925,12 +16925,12 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -16983,12 +16983,12 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -17045,12 +17045,12 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>8 days, 23:35:53.486447</t>
+          <t>7 days, 23:35:23.547693</t>
         </is>
       </c>
     </row>
@@ -17103,12 +17103,12 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -17161,12 +17161,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -17223,12 +17223,12 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>8 days, 23:35:53.486354</t>
+          <t>7 days, 23:35:23.547612</t>
         </is>
       </c>
     </row>
@@ -17285,12 +17285,12 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>8 days, 23:35:53.486321</t>
+          <t>7 days, 23:35:23.547583</t>
         </is>
       </c>
     </row>
@@ -17347,12 +17347,12 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>8 days, 23:35:53.486286</t>
+          <t>7 days, 23:35:23.547551</t>
         </is>
       </c>
     </row>
@@ -17405,12 +17405,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -17463,12 +17463,12 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -17521,12 +17521,12 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -17583,12 +17583,12 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>8 days, 23:35:53.486160</t>
+          <t>7 days, 23:35:23.547441</t>
         </is>
       </c>
     </row>
@@ -17645,12 +17645,12 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>8 days, 23:35:53.486126</t>
+          <t>7 days, 23:35:23.547411</t>
         </is>
       </c>
     </row>
@@ -17703,12 +17703,12 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -17761,12 +17761,12 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -17819,12 +17819,12 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -17877,12 +17877,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -17939,12 +17939,12 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>8 days, 23:35:53.485980</t>
+          <t>7 days, 23:35:23.547283</t>
         </is>
       </c>
     </row>
@@ -17997,12 +17997,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18055,12 +18055,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18117,12 +18117,12 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>8 days, 23:35:53.485886</t>
+          <t>7 days, 23:35:23.547204</t>
         </is>
       </c>
     </row>
@@ -18175,12 +18175,12 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18233,12 +18233,12 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18291,12 +18291,12 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18349,12 +18349,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18407,12 +18407,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18465,12 +18465,12 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18523,12 +18523,12 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18581,12 +18581,12 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18639,12 +18639,12 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18697,12 +18697,12 @@
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18759,12 +18759,12 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.485552</t>
+          <t>7 days, 23:20:23.546900</t>
         </is>
       </c>
     </row>
@@ -18817,12 +18817,12 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18879,12 +18879,12 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.485490</t>
+          <t>7 days, 23:20:23.546848</t>
         </is>
       </c>
     </row>
@@ -18937,12 +18937,12 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -18999,12 +18999,12 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.485427</t>
+          <t>7 days, 23:20:23.546793</t>
         </is>
       </c>
     </row>
@@ -19057,12 +19057,12 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -19115,12 +19115,12 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -19173,12 +19173,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -19231,12 +19231,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -19289,12 +19289,12 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -19347,12 +19347,12 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -19405,12 +19405,12 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -19467,12 +19467,12 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.485199</t>
+          <t>7 days, 23:20:23.546590</t>
         </is>
       </c>
     </row>
@@ -19525,12 +19525,12 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -19583,12 +19583,12 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -19645,12 +19645,12 @@
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.485105</t>
+          <t>7 days, 23:20:23.546511</t>
         </is>
       </c>
     </row>
@@ -19703,12 +19703,12 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -19761,12 +19761,12 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -19819,12 +19819,12 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -19877,12 +19877,12 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -19939,12 +19939,12 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.484962</t>
+          <t>7 days, 23:20:23.546384</t>
         </is>
       </c>
     </row>
@@ -19997,12 +19997,12 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -20059,12 +20059,12 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.484901</t>
+          <t>7 days, 23:20:23.546328</t>
         </is>
       </c>
     </row>
@@ -20117,12 +20117,12 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -20179,12 +20179,12 @@
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.484838</t>
+          <t>7 days, 23:20:23.546273</t>
         </is>
       </c>
     </row>
@@ -20241,12 +20241,12 @@
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.484806</t>
+          <t>7 days, 23:20:23.546245</t>
         </is>
       </c>
     </row>
@@ -20299,12 +20299,12 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -20357,12 +20357,12 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -20415,12 +20415,12 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -20473,12 +20473,12 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -20531,12 +20531,12 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -20589,12 +20589,12 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -20647,12 +20647,12 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -20709,12 +20709,12 @@
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.484560</t>
+          <t>7 days, 23:20:23.546040</t>
         </is>
       </c>
     </row>
@@ -20767,12 +20767,12 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -20825,12 +20825,12 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -20883,12 +20883,12 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -20941,12 +20941,12 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -20999,12 +20999,12 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -21061,12 +21061,12 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.484359</t>
+          <t>7 days, 23:20:23.545861</t>
         </is>
       </c>
     </row>
@@ -21119,12 +21119,12 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -21177,12 +21177,12 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -21239,12 +21239,12 @@
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.484255</t>
+          <t>7 days, 23:20:23.545769</t>
         </is>
       </c>
     </row>
@@ -21301,12 +21301,12 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.484213</t>
+          <t>7 days, 23:20:23.545732</t>
         </is>
       </c>
     </row>
@@ -21363,12 +21363,12 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>8 days, 23:20:53.484176</t>
+          <t>7 days, 23:20:23.545697</t>
         </is>
       </c>
     </row>
@@ -21421,12 +21421,12 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -21479,12 +21479,12 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -21537,12 +21537,12 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -21595,12 +21595,12 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -21653,12 +21653,12 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -21711,12 +21711,12 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -21769,12 +21769,12 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -21827,12 +21827,12 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -21885,12 +21885,12 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -21943,12 +21943,12 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22001,12 +22001,12 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22059,12 +22059,12 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22117,12 +22117,12 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22175,12 +22175,12 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22233,12 +22233,12 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22291,12 +22291,12 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22349,12 +22349,12 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22407,12 +22407,12 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22465,12 +22465,12 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22523,12 +22523,12 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22581,12 +22581,12 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22639,12 +22639,12 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22697,12 +22697,12 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22755,12 +22755,12 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22808,12 +22808,12 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22857,12 +22857,12 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22910,12 +22910,12 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -22963,12 +22963,12 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23016,12 +23016,12 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23073,12 +23073,12 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>5 days, 18:50:53.483283</t>
+          <t>4 days, 18:50:23.544892</t>
         </is>
       </c>
     </row>
@@ -23126,12 +23126,12 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23183,12 +23183,12 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>5 days, 18:50:53.483209</t>
+          <t>4 days, 18:50:23.544827</t>
         </is>
       </c>
     </row>
@@ -23236,12 +23236,12 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23289,12 +23289,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23342,12 +23342,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23395,12 +23395,12 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23448,12 +23448,12 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23554,12 +23554,12 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23607,12 +23607,12 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23660,12 +23660,12 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23713,12 +23713,12 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23766,12 +23766,12 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23819,12 +23819,12 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23872,12 +23872,12 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23925,12 +23925,12 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -23978,12 +23978,12 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24031,12 +24031,12 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24084,12 +24084,12 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24137,12 +24137,12 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24190,12 +24190,12 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24243,12 +24243,12 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24296,12 +24296,12 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24349,12 +24349,12 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24406,12 +24406,12 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>5 days, 18:50:53.482584</t>
+          <t>4 days, 18:50:23.544291</t>
         </is>
       </c>
     </row>
@@ -24459,12 +24459,12 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24512,12 +24512,12 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24565,12 +24565,12 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24618,12 +24618,12 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24671,12 +24671,12 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24724,12 +24724,12 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24781,12 +24781,12 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>4 days, 19:20:53.482374</t>
+          <t>3 days, 19:20:23.544094</t>
         </is>
       </c>
     </row>
@@ -24838,12 +24838,12 @@
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>4 days, 19:20:53.482287</t>
+          <t>3 days, 19:20:23.544058</t>
         </is>
       </c>
     </row>
@@ -24891,12 +24891,12 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -24948,12 +24948,12 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>4 days, 19:20:53.482199</t>
+          <t>3 days, 19:20:23.543992</t>
         </is>
       </c>
     </row>
@@ -25006,12 +25006,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25059,12 +25059,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25112,12 +25112,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25170,12 +25170,12 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25223,12 +25223,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25280,12 +25280,12 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>4 days, 19:20:53.481999</t>
+          <t>3 days, 19:20:23.543816</t>
         </is>
       </c>
     </row>
@@ -25333,12 +25333,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25391,12 +25391,12 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25449,12 +25449,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25507,12 +25507,12 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25560,12 +25560,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25618,12 +25618,12 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25671,12 +25671,12 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25724,12 +25724,12 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25782,12 +25782,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25840,12 +25840,12 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25898,12 +25898,12 @@
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -25956,12 +25956,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26009,12 +26009,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26062,12 +26062,12 @@
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26120,12 +26120,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26173,12 +26173,12 @@
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26226,12 +26226,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26279,12 +26279,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26332,12 +26332,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26385,12 +26385,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26438,12 +26438,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26491,12 +26491,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26549,12 +26549,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26602,12 +26602,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26655,12 +26655,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26708,12 +26708,12 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26761,12 +26761,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26814,12 +26814,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26867,12 +26867,12 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26920,12 +26920,12 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -26973,12 +26973,12 @@
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27026,12 +27026,12 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27079,12 +27079,12 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27132,12 +27132,12 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27185,12 +27185,12 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27238,12 +27238,12 @@
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27291,12 +27291,12 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27344,12 +27344,12 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27397,12 +27397,12 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27450,12 +27450,12 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27503,12 +27503,12 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27556,12 +27556,12 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27609,12 +27609,12 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27662,12 +27662,12 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27711,12 +27711,12 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27760,12 +27760,12 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27809,12 +27809,12 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27858,12 +27858,12 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27911,12 +27911,12 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -27964,12 +27964,12 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28017,12 +28017,12 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28070,12 +28070,12 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28123,12 +28123,12 @@
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28176,12 +28176,12 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28229,12 +28229,12 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28282,12 +28282,12 @@
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28335,12 +28335,12 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28388,12 +28388,12 @@
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28441,12 +28441,12 @@
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28494,12 +28494,12 @@
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28547,12 +28547,12 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28600,12 +28600,12 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28653,12 +28653,12 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28706,12 +28706,12 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28759,12 +28759,12 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28812,12 +28812,12 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28865,12 +28865,12 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28918,12 +28918,12 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -28971,12 +28971,12 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29024,12 +29024,12 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29077,12 +29077,12 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29130,12 +29130,12 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29183,12 +29183,12 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29236,12 +29236,12 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29289,12 +29289,12 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29342,12 +29342,12 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29395,12 +29395,12 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29448,12 +29448,12 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29501,12 +29501,12 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29554,12 +29554,12 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29607,12 +29607,12 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29660,12 +29660,12 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29713,12 +29713,12 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29766,12 +29766,12 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29819,12 +29819,12 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29872,12 +29872,12 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29925,12 +29925,12 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>
@@ -29978,12 +29978,12 @@
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>05/22/26 12:09 PM</t>
+          <t>05/23/26 12:09 PM</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -546,12 +546,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>22 days, 4:35:23.556806</t>
+          <t>21 days, 2:41:02.318678</t>
         </is>
       </c>
     </row>
@@ -603,12 +603,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>22 days, 4:20:23.556746</t>
+          <t>21 days, 2:26:02.318618</t>
         </is>
       </c>
     </row>
@@ -660,17 +660,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22 days, 1:50:23.556696</t>
+          <t>20 days, 23:56:02.318575</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 days, 1:50:23.556655</t>
+          <t>20 days, 23:56:02.318536</t>
         </is>
       </c>
     </row>
@@ -784,17 +784,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 days, 1:50:23.556619</t>
+          <t>20 days, 23:56:02.318501</t>
         </is>
       </c>
     </row>
@@ -846,17 +846,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22 days, 1:50:23.556583</t>
+          <t>20 days, 23:56:02.318468</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>22 days, 1:50:23.556547</t>
+          <t>20 days, 23:56:02.318438</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>22 days, 1:50:23.556515</t>
+          <t>20 days, 23:56:02.318379</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>21 days, 21:50:23.556482</t>
+          <t>20 days, 19:56:02.318343</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>19 days, 1:50:23.556394</t>
+          <t>17 days, 23:56:02.318255</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>19 days, 1:50:23.556359</t>
+          <t>17 days, 23:56:02.318220</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19 days, 1:50:23.556325</t>
+          <t>17 days, 23:56:02.318185</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19 days, 1:50:23.556291</t>
+          <t>17 days, 23:56:02.318151</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>19 days, 1:50:23.556257</t>
+          <t>17 days, 23:56:02.318119</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19 days, 1:50:23.556223</t>
+          <t>17 days, 23:56:02.318087</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>19 days, 1:20:23.556184</t>
+          <t>17 days, 23:26:02.318048</t>
         </is>
       </c>
     </row>
@@ -1561,17 +1561,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ATT01, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>ATT01 &amp; WASA02 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19 days, 1:20:23.556150</t>
+          <t>17 days, 23:26:02.318014</t>
         </is>
       </c>
     </row>
@@ -1618,17 +1618,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ATT01, COMDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>ATT01, COMDC &amp; WASA02 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>19 days, 1:20:23.556098</t>
+          <t>17 days, 23:26:02.317980</t>
         </is>
       </c>
     </row>
@@ -1675,17 +1675,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>ATT01, COMDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>ATT01, COMDC &amp; WASA02 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>19 days, 1:20:23.556061</t>
+          <t>17 days, 23:26:02.317946</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>19 days, 1:20:23.556030</t>
+          <t>17 days, 23:26:02.317918</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>19 days, 1:20:23.555999</t>
+          <t>17 days, 23:26:02.317890</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>19 days, 1:20:23.555970</t>
+          <t>17 days, 23:26:02.317862</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>19 days, 1:20:23.555942</t>
+          <t>17 days, 23:26:02.317836</t>
         </is>
       </c>
     </row>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>18 days, 21:50:23.555908</t>
+          <t>17 days, 19:56:02.317801</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>18 days, 21:50:23.555874</t>
+          <t>17 days, 19:56:02.317768</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555842</t>
+          <t>17 days, 19:26:02.317736</t>
         </is>
       </c>
     </row>
@@ -2136,12 +2136,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555811</t>
+          <t>17 days, 19:26:02.317707</t>
         </is>
       </c>
     </row>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555780</t>
+          <t>17 days, 19:26:02.317677</t>
         </is>
       </c>
     </row>
@@ -2250,12 +2250,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555748</t>
+          <t>17 days, 19:26:02.317647</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555715</t>
+          <t>17 days, 19:26:02.317617</t>
         </is>
       </c>
     </row>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555683</t>
+          <t>17 days, 19:26:02.317587</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555652</t>
+          <t>17 days, 19:26:02.317557</t>
         </is>
       </c>
     </row>
@@ -2478,12 +2478,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555620</t>
+          <t>17 days, 19:26:02.317528</t>
         </is>
       </c>
     </row>
@@ -2535,12 +2535,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555587</t>
+          <t>17 days, 19:26:02.317498</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2592,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555556</t>
+          <t>17 days, 19:26:02.317469</t>
         </is>
       </c>
     </row>
@@ -2649,12 +2649,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555525</t>
+          <t>17 days, 19:26:02.317440</t>
         </is>
       </c>
     </row>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555494</t>
+          <t>17 days, 19:26:02.317397</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555464</t>
+          <t>17 days, 19:26:02.317367</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555433</t>
+          <t>17 days, 19:26:02.317336</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555403</t>
+          <t>17 days, 19:26:02.317307</t>
         </is>
       </c>
     </row>
@@ -2934,12 +2934,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555372</t>
+          <t>17 days, 19:26:02.317278</t>
         </is>
       </c>
     </row>
@@ -2991,12 +2991,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555340</t>
+          <t>17 days, 19:26:02.317248</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555310</t>
+          <t>17 days, 19:26:02.317220</t>
         </is>
       </c>
     </row>
@@ -3105,12 +3105,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555278</t>
+          <t>17 days, 19:26:02.317191</t>
         </is>
       </c>
     </row>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555247</t>
+          <t>17 days, 19:26:02.317163</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3219,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555217</t>
+          <t>17 days, 19:26:02.317134</t>
         </is>
       </c>
     </row>
@@ -3276,12 +3276,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>18 days, 21:20:23.555182</t>
+          <t>17 days, 19:26:02.317101</t>
         </is>
       </c>
     </row>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>18 days, 20:20:23.555156</t>
+          <t>17 days, 18:26:02.317075</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -3438,17 +3438,17 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded &amp; WGL07 - 24-hour delay</t>
+          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>18 days, 0:50:23.555072</t>
+          <t>16 days, 22:56:02.317007</t>
         </is>
       </c>
     </row>
@@ -3500,12 +3500,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>18 days, 0:50:23.555041</t>
+          <t>16 days, 22:56:02.316978</t>
         </is>
       </c>
     </row>
@@ -3557,12 +3557,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>18 days, 0:50:23.555013</t>
+          <t>16 days, 22:56:02.316950</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>18 days, 0:50:23.554985</t>
+          <t>16 days, 22:56:02.316923</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3671,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>18 days, 0:20:23.554952</t>
+          <t>16 days, 22:26:02.316893</t>
         </is>
       </c>
     </row>
@@ -3728,12 +3728,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>18 days, 0:20:23.554917</t>
+          <t>16 days, 22:26:02.316859</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>18 days, 0:20:23.554881</t>
+          <t>16 days, 22:26:02.316824</t>
         </is>
       </c>
     </row>
@@ -3842,12 +3842,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>18 days, 0:20:23.554848</t>
+          <t>16 days, 22:26:02.316792</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>18 days, 0:20:23.554813</t>
+          <t>16 days, 22:26:02.316759</t>
         </is>
       </c>
     </row>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>18 days, 0:20:23.554776</t>
+          <t>16 days, 22:26:02.316726</t>
         </is>
       </c>
     </row>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>17 days, 23:05:23.554742</t>
+          <t>16 days, 21:11:02.316697</t>
         </is>
       </c>
     </row>
@@ -4065,17 +4065,17 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>17 days, 23:05:23.554711</t>
+          <t>16 days, 21:11:02.316667</t>
         </is>
       </c>
     </row>
@@ -4122,17 +4122,17 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>17 days, 23:05:23.554679</t>
+          <t>16 days, 21:11:02.316638</t>
         </is>
       </c>
     </row>
@@ -4179,17 +4179,17 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; VDC &amp; WGL07 - 24-hour delay &amp; WASA02 - Not yet responded</t>
+          <t>VDC &amp; WGL07 - 24-hour delay &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>17 days, 23:05:23.554645</t>
+          <t>16 days, 21:11:02.316605</t>
         </is>
       </c>
     </row>
@@ -4236,17 +4236,17 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded &amp; WGL07 - 24-hour delay</t>
+          <t>WASA02 - Not yet responded &amp; WGL07 - 24-hour delay</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>17 days, 23:05:23.554611</t>
+          <t>16 days, 21:11:02.316573</t>
         </is>
       </c>
     </row>
@@ -4293,17 +4293,17 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; VDC &amp; WGL07 - 24-hour delay &amp; WASA02 - Not yet responded</t>
+          <t>VDC &amp; WGL07 - 24-hour delay &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>17 days, 23:05:23.554576</t>
+          <t>16 days, 21:11:02.316540</t>
         </is>
       </c>
     </row>
@@ -4350,17 +4350,17 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>17 days, 23:05:23.554544</t>
+          <t>16 days, 21:11:02.316508</t>
         </is>
       </c>
     </row>
@@ -4407,17 +4407,17 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC - Incorrect work site mapping, insufficient information, and/or wrong address &amp; WASA02 - Not yet responded</t>
+          <t>PEPCODC - Incorrect work site mapping, insufficient information, and/or wrong address &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>17 days, 23:05:23.554507</t>
+          <t>16 days, 21:11:02.316476</t>
         </is>
       </c>
     </row>
@@ -4464,17 +4464,17 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>17 days, 23:05:23.554475</t>
+          <t>16 days, 21:11:02.316446</t>
         </is>
       </c>
     </row>
@@ -4521,17 +4521,17 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>17 days, 23:05:23.554444</t>
+          <t>16 days, 21:11:02.316406</t>
         </is>
       </c>
     </row>
@@ -4578,17 +4578,17 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>17 days, 23:05:23.554412</t>
+          <t>16 days, 21:11:02.316377</t>
         </is>
       </c>
     </row>
@@ -4636,12 +4636,12 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -4689,12 +4689,12 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -4795,12 +4795,12 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>17 days, 18:50:23.554264</t>
+          <t>16 days, 16:56:02.316234</t>
         </is>
       </c>
     </row>
@@ -4909,12 +4909,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>17 days, 18:50:23.554227</t>
+          <t>16 days, 16:56:02.316194</t>
         </is>
       </c>
     </row>
@@ -4966,12 +4966,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>17 days, 18:50:23.554187</t>
+          <t>16 days, 16:56:02.316156</t>
         </is>
       </c>
     </row>
@@ -5023,12 +5023,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>17 days, 18:50:23.554151</t>
+          <t>16 days, 16:56:02.316123</t>
         </is>
       </c>
     </row>
@@ -5076,12 +5076,12 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5134,12 +5134,12 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5192,12 +5192,12 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5250,12 +5250,12 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5308,12 +5308,12 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5366,12 +5366,12 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5482,12 +5482,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5598,12 +5598,12 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5772,12 +5772,12 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5830,12 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5888,12 +5888,12 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -5946,12 +5946,12 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6004,12 +6004,12 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6120,12 +6120,12 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6178,12 +6178,12 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6236,12 +6236,12 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6294,12 +6294,12 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6352,12 +6352,12 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6410,12 +6410,12 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6468,12 +6468,12 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6816,12 +6816,12 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6932,12 +6932,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7048,12 +7048,12 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7106,12 +7106,12 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7164,12 +7164,12 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7222,12 +7222,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7280,12 +7280,12 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7386,12 +7386,12 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7497,12 +7497,12 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>16 days, 3:50:23.552849</t>
+          <t>15 days, 1:56:02.314919</t>
         </is>
       </c>
     </row>
@@ -7612,12 +7612,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7670,12 +7670,12 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7728,12 +7728,12 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7844,12 +7844,12 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7902,12 +7902,12 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -7959,12 +7959,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>16 days, 3:50:23.552650</t>
+          <t>15 days, 1:56:02.314730</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -8075,12 +8075,12 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -8133,12 +8133,12 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -8191,12 +8191,12 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -8307,12 +8307,12 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>16 days, 3:50:23.552461</t>
+          <t>15 days, 1:56:02.314547</t>
         </is>
       </c>
     </row>
@@ -8422,12 +8422,12 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -8533,12 +8533,12 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>15 days, 23:05:23.552348</t>
+          <t>14 days, 21:11:02.314441</t>
         </is>
       </c>
     </row>
@@ -8643,12 +8643,12 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -8701,12 +8701,12 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -8754,12 +8754,12 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -8869,12 +8869,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.552190</t>
+          <t>14 days, 16:56:02.314267</t>
         </is>
       </c>
     </row>
@@ -8931,12 +8931,12 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.552147</t>
+          <t>14 days, 16:56:02.314225</t>
         </is>
       </c>
     </row>
@@ -8993,12 +8993,12 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.552096</t>
+          <t>14 days, 16:56:02.314185</t>
         </is>
       </c>
     </row>
@@ -9055,12 +9055,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.552055</t>
+          <t>14 days, 16:56:02.314147</t>
         </is>
       </c>
     </row>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.552011</t>
+          <t>14 days, 16:56:02.314107</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.551969</t>
+          <t>14 days, 16:56:02.314067</t>
         </is>
       </c>
     </row>
@@ -9241,12 +9241,12 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.551929</t>
+          <t>14 days, 16:56:02.314027</t>
         </is>
       </c>
     </row>
@@ -9303,12 +9303,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.551890</t>
+          <t>14 days, 16:56:02.313988</t>
         </is>
       </c>
     </row>
@@ -9365,12 +9365,12 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.551847</t>
+          <t>14 days, 16:56:02.313941</t>
         </is>
       </c>
     </row>
@@ -9427,12 +9427,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.551806</t>
+          <t>14 days, 16:56:02.313901</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.551763</t>
+          <t>14 days, 16:56:02.313861</t>
         </is>
       </c>
     </row>
@@ -9551,12 +9551,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.551719</t>
+          <t>14 days, 16:56:02.313819</t>
         </is>
       </c>
     </row>
@@ -9613,12 +9613,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.551678</t>
+          <t>14 days, 16:56:02.313778</t>
         </is>
       </c>
     </row>
@@ -9675,12 +9675,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.551636</t>
+          <t>14 days, 16:56:02.313738</t>
         </is>
       </c>
     </row>
@@ -9737,12 +9737,12 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.551595</t>
+          <t>14 days, 16:56:02.313699</t>
         </is>
       </c>
     </row>
@@ -9799,12 +9799,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.551552</t>
+          <t>14 days, 16:56:02.313659</t>
         </is>
       </c>
     </row>
@@ -9861,12 +9861,12 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.551509</t>
+          <t>14 days, 16:56:02.313618</t>
         </is>
       </c>
     </row>
@@ -9923,12 +9923,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>15 days, 18:50:23.551466</t>
+          <t>14 days, 16:56:02.313577</t>
         </is>
       </c>
     </row>
@@ -9976,12 +9976,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>15 days, 4:50:23.551432</t>
+          <t>14 days, 2:56:02.313546</t>
         </is>
       </c>
     </row>
@@ -10029,12 +10029,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>15 days, 4:50:23.551399</t>
+          <t>14 days, 2:56:02.313514</t>
         </is>
       </c>
     </row>
@@ -10082,12 +10082,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>15 days, 4:50:23.551364</t>
+          <t>14 days, 2:56:02.313480</t>
         </is>
       </c>
     </row>
@@ -10135,12 +10135,12 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>15 days, 4:50:23.551332</t>
+          <t>14 days, 2:56:02.313448</t>
         </is>
       </c>
     </row>
@@ -10188,12 +10188,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>15 days, 4:50:23.551297</t>
+          <t>14 days, 2:56:02.313401</t>
         </is>
       </c>
     </row>
@@ -10241,12 +10241,12 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>15 days, 4:50:23.551265</t>
+          <t>14 days, 2:56:02.313367</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.551238</t>
+          <t>14 days, 2:41:02.313341</t>
         </is>
       </c>
     </row>
@@ -10360,12 +10360,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.551209</t>
+          <t>14 days, 2:41:02.313311</t>
         </is>
       </c>
     </row>
@@ -10422,12 +10422,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.551179</t>
+          <t>14 days, 2:41:02.313282</t>
         </is>
       </c>
     </row>
@@ -10484,12 +10484,12 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.551152</t>
+          <t>14 days, 2:41:02.313255</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.551122</t>
+          <t>14 days, 2:41:02.313223</t>
         </is>
       </c>
     </row>
@@ -10608,12 +10608,12 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.551081</t>
+          <t>14 days, 2:41:02.313194</t>
         </is>
       </c>
     </row>
@@ -10670,12 +10670,12 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.551052</t>
+          <t>14 days, 2:41:02.313166</t>
         </is>
       </c>
     </row>
@@ -10732,12 +10732,12 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.551021</t>
+          <t>14 days, 2:41:02.313135</t>
         </is>
       </c>
     </row>
@@ -10794,12 +10794,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.550990</t>
+          <t>14 days, 2:41:02.313103</t>
         </is>
       </c>
     </row>
@@ -10856,12 +10856,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.550958</t>
+          <t>14 days, 2:41:02.313073</t>
         </is>
       </c>
     </row>
@@ -10918,12 +10918,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.550924</t>
+          <t>14 days, 2:41:02.313043</t>
         </is>
       </c>
     </row>
@@ -10980,12 +10980,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.550892</t>
+          <t>14 days, 2:41:02.313013</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.550861</t>
+          <t>14 days, 2:41:02.312983</t>
         </is>
       </c>
     </row>
@@ -11104,12 +11104,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.550829</t>
+          <t>14 days, 2:41:02.312953</t>
         </is>
       </c>
     </row>
@@ -11166,12 +11166,12 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.550796</t>
+          <t>14 days, 2:41:02.312923</t>
         </is>
       </c>
     </row>
@@ -11228,12 +11228,12 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>15 days, 4:35:23.550769</t>
+          <t>14 days, 2:41:02.312897</t>
         </is>
       </c>
     </row>
@@ -11281,12 +11281,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -11338,12 +11338,12 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>14 days, 21:20:23.550708</t>
+          <t>13 days, 19:26:02.312838</t>
         </is>
       </c>
     </row>
@@ -11395,12 +11395,12 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>14 days, 21:20:23.550676</t>
+          <t>13 days, 19:26:02.312805</t>
         </is>
       </c>
     </row>
@@ -11448,12 +11448,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -11558,12 +11558,12 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>12 days, 4:35:23.550592</t>
+          <t>11 days, 2:41:02.312723</t>
         </is>
       </c>
     </row>
@@ -11615,12 +11615,12 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>12 days, 4:35:23.550558</t>
+          <t>11 days, 2:41:02.312690</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>12 days, 4:35:23.550527</t>
+          <t>11 days, 2:41:02.312660</t>
         </is>
       </c>
     </row>
@@ -11729,12 +11729,12 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>12 days, 4:35:23.550494</t>
+          <t>11 days, 2:41:02.312629</t>
         </is>
       </c>
     </row>
@@ -11786,12 +11786,12 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>12 days, 4:35:23.550461</t>
+          <t>11 days, 2:41:02.312597</t>
         </is>
       </c>
     </row>
@@ -11843,12 +11843,12 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>12 days, 4:35:23.550432</t>
+          <t>11 days, 2:41:02.312571</t>
         </is>
       </c>
     </row>
@@ -11900,12 +11900,12 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>12 days, 4:35:23.550403</t>
+          <t>11 days, 2:41:02.312543</t>
         </is>
       </c>
     </row>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>11 days, 21:20:23.550369</t>
+          <t>10 days, 19:26:02.312510</t>
         </is>
       </c>
     </row>
@@ -12006,12 +12006,12 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>11 days, 21:20:23.550333</t>
+          <t>10 days, 19:26:02.312476</t>
         </is>
       </c>
     </row>
@@ -12059,12 +12059,12 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>11 days, 21:20:23.550298</t>
+          <t>10 days, 19:26:02.312441</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>11 days, 21:05:23.550268</t>
+          <t>10 days, 19:11:02.312402</t>
         </is>
       </c>
     </row>
@@ -12165,12 +12165,12 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>11 days, 21:05:23.550239</t>
+          <t>10 days, 19:11:02.312374</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>11 days, 21:05:23.550206</t>
+          <t>10 days, 19:11:02.312342</t>
         </is>
       </c>
     </row>
@@ -12275,12 +12275,12 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>11 days, 0:20:23.550176</t>
+          <t>9 days, 22:26:02.312312</t>
         </is>
       </c>
     </row>
@@ -12328,12 +12328,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -12381,12 +12381,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -12439,12 +12439,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -12497,12 +12497,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -12555,12 +12555,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -12613,12 +12613,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -12719,12 +12719,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -12772,12 +12772,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -12825,12 +12825,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -12878,12 +12878,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -12936,12 +12936,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -12994,12 +12994,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13052,12 +13052,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13110,12 +13110,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13168,12 +13168,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13226,12 +13226,12 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13284,12 +13284,12 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13337,12 +13337,12 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13390,12 +13390,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13443,12 +13443,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13496,12 +13496,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13549,12 +13549,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13602,12 +13602,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13660,12 +13660,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13713,12 +13713,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13766,12 +13766,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13824,12 +13824,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13882,12 +13882,12 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13935,12 +13935,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -13988,12 +13988,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14041,12 +14041,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14094,12 +14094,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14147,12 +14147,12 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14200,12 +14200,12 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14253,12 +14253,12 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14306,12 +14306,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14359,12 +14359,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14412,12 +14412,12 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14465,12 +14465,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14518,12 +14518,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14571,12 +14571,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14624,12 +14624,12 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14677,12 +14677,12 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14734,12 +14734,12 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>9 days, 22:35:23.548927</t>
+          <t>8 days, 20:41:02.311151</t>
         </is>
       </c>
     </row>
@@ -14787,12 +14787,12 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -14897,12 +14897,12 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>8 days, 18:50:23.548822</t>
+          <t>7 days, 16:56:02.311050</t>
         </is>
       </c>
     </row>
@@ -14954,12 +14954,12 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>8 days, 18:50:23.548783</t>
+          <t>7 days, 16:56:02.311013</t>
         </is>
       </c>
     </row>
@@ -15011,12 +15011,12 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>8 days, 18:50:23.548745</t>
+          <t>7 days, 16:56:02.310977</t>
         </is>
       </c>
     </row>
@@ -15068,12 +15068,12 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>8 days, 18:50:23.548707</t>
+          <t>7 days, 16:56:02.310941</t>
         </is>
       </c>
     </row>
@@ -15125,12 +15125,12 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>8 days, 18:50:23.548668</t>
+          <t>7 days, 16:56:02.310905</t>
         </is>
       </c>
     </row>
@@ -15182,12 +15182,12 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>8 days, 18:50:23.548628</t>
+          <t>7 days, 16:56:02.310868</t>
         </is>
       </c>
     </row>
@@ -15239,12 +15239,12 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>8 days, 18:50:23.548588</t>
+          <t>7 days, 16:56:02.310828</t>
         </is>
       </c>
     </row>
@@ -15296,12 +15296,12 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>8 days, 18:50:23.548549</t>
+          <t>7 days, 16:56:02.310790</t>
         </is>
       </c>
     </row>
@@ -15353,12 +15353,12 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>8 days, 18:50:23.548511</t>
+          <t>7 days, 16:56:02.310754</t>
         </is>
       </c>
     </row>
@@ -15410,12 +15410,12 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>8 days, 18:50:23.548470</t>
+          <t>7 days, 16:56:02.310715</t>
         </is>
       </c>
     </row>
@@ -15468,12 +15468,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -15579,12 +15579,12 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -15637,12 +15637,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -15695,12 +15695,12 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -15753,12 +15753,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -15811,12 +15811,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -15869,12 +15869,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -15927,12 +15927,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -15989,12 +15989,12 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>7 days, 23:50:23.548192</t>
+          <t>6 days, 21:56:02.310446</t>
         </is>
       </c>
     </row>
@@ -16047,12 +16047,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16105,12 +16105,12 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16163,12 +16163,12 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16221,12 +16221,12 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16279,12 +16279,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16337,12 +16337,12 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16395,12 +16395,12 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16457,12 +16457,12 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>7 days, 23:35:23.547954</t>
+          <t>6 days, 21:41:02.310232</t>
         </is>
       </c>
     </row>
@@ -16515,12 +16515,12 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16573,12 +16573,12 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16631,12 +16631,12 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16689,12 +16689,12 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16747,12 +16747,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16805,12 +16805,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16867,12 +16867,12 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>7 days, 23:35:23.547773</t>
+          <t>6 days, 21:41:02.310058</t>
         </is>
       </c>
     </row>
@@ -16925,12 +16925,12 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -16983,12 +16983,12 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -17045,12 +17045,12 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>7 days, 23:35:23.547693</t>
+          <t>6 days, 21:41:02.309981</t>
         </is>
       </c>
     </row>
@@ -17103,12 +17103,12 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -17161,12 +17161,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -17223,12 +17223,12 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>7 days, 23:35:23.547612</t>
+          <t>6 days, 21:41:02.309903</t>
         </is>
       </c>
     </row>
@@ -17285,12 +17285,12 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>7 days, 23:35:23.547583</t>
+          <t>6 days, 21:41:02.309875</t>
         </is>
       </c>
     </row>
@@ -17347,12 +17347,12 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>7 days, 23:35:23.547551</t>
+          <t>6 days, 21:41:02.309846</t>
         </is>
       </c>
     </row>
@@ -17405,12 +17405,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -17463,12 +17463,12 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -17521,12 +17521,12 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -17583,12 +17583,12 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>7 days, 23:35:23.547441</t>
+          <t>6 days, 21:41:02.309740</t>
         </is>
       </c>
     </row>
@@ -17645,12 +17645,12 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>7 days, 23:35:23.547411</t>
+          <t>6 days, 21:41:02.309712</t>
         </is>
       </c>
     </row>
@@ -17703,12 +17703,12 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -17761,12 +17761,12 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -17819,12 +17819,12 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -17877,12 +17877,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -17939,12 +17939,12 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>7 days, 23:35:23.547283</t>
+          <t>6 days, 21:41:02.309587</t>
         </is>
       </c>
     </row>
@@ -17997,12 +17997,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18055,12 +18055,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18117,12 +18117,12 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>7 days, 23:35:23.547204</t>
+          <t>6 days, 21:41:02.309503</t>
         </is>
       </c>
     </row>
@@ -18175,12 +18175,12 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18233,12 +18233,12 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18291,12 +18291,12 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18349,12 +18349,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18407,12 +18407,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18465,12 +18465,12 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18523,12 +18523,12 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18581,12 +18581,12 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18639,12 +18639,12 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18697,12 +18697,12 @@
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18759,12 +18759,12 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.546900</t>
+          <t>6 days, 21:26:02.309201</t>
         </is>
       </c>
     </row>
@@ -18817,12 +18817,12 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18879,12 +18879,12 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.546848</t>
+          <t>6 days, 21:26:02.309149</t>
         </is>
       </c>
     </row>
@@ -18937,12 +18937,12 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -18999,12 +18999,12 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.546793</t>
+          <t>6 days, 21:26:02.309095</t>
         </is>
       </c>
     </row>
@@ -19057,12 +19057,12 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -19115,12 +19115,12 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -19173,12 +19173,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -19231,12 +19231,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -19289,12 +19289,12 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -19347,12 +19347,12 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -19405,12 +19405,12 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -19467,12 +19467,12 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.546590</t>
+          <t>6 days, 21:26:02.308899</t>
         </is>
       </c>
     </row>
@@ -19525,12 +19525,12 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -19583,12 +19583,12 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -19645,12 +19645,12 @@
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.546511</t>
+          <t>6 days, 21:26:02.308822</t>
         </is>
       </c>
     </row>
@@ -19703,12 +19703,12 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -19761,12 +19761,12 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -19819,12 +19819,12 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -19877,12 +19877,12 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -19939,12 +19939,12 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.546384</t>
+          <t>6 days, 21:26:02.308702</t>
         </is>
       </c>
     </row>
@@ -19997,12 +19997,12 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -20059,12 +20059,12 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.546328</t>
+          <t>6 days, 21:26:02.308649</t>
         </is>
       </c>
     </row>
@@ -20117,12 +20117,12 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -20179,12 +20179,12 @@
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.546273</t>
+          <t>6 days, 21:26:02.308596</t>
         </is>
       </c>
     </row>
@@ -20241,12 +20241,12 @@
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.546245</t>
+          <t>6 days, 21:26:02.308569</t>
         </is>
       </c>
     </row>
@@ -20299,12 +20299,12 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -20357,12 +20357,12 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -20415,12 +20415,12 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -20473,12 +20473,12 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -20531,12 +20531,12 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -20589,12 +20589,12 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -20647,12 +20647,12 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -20709,12 +20709,12 @@
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.546040</t>
+          <t>6 days, 21:26:02.308362</t>
         </is>
       </c>
     </row>
@@ -20767,12 +20767,12 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -20825,12 +20825,12 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -20883,12 +20883,12 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -20941,12 +20941,12 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -20999,12 +20999,12 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -21061,12 +21061,12 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.545861</t>
+          <t>6 days, 21:26:02.308190</t>
         </is>
       </c>
     </row>
@@ -21119,12 +21119,12 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -21177,12 +21177,12 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -21239,12 +21239,12 @@
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.545769</t>
+          <t>6 days, 21:26:02.308100</t>
         </is>
       </c>
     </row>
@@ -21301,12 +21301,12 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.545732</t>
+          <t>6 days, 21:26:02.308063</t>
         </is>
       </c>
     </row>
@@ -21363,12 +21363,12 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>7 days, 23:20:23.545697</t>
+          <t>6 days, 21:26:02.308030</t>
         </is>
       </c>
     </row>
@@ -21421,12 +21421,12 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -21479,12 +21479,12 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -21537,12 +21537,12 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -21595,12 +21595,12 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -21653,12 +21653,12 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -21711,12 +21711,12 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -21769,12 +21769,12 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -21827,12 +21827,12 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -21885,12 +21885,12 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -21943,12 +21943,12 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22001,12 +22001,12 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22059,12 +22059,12 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22117,12 +22117,12 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22175,12 +22175,12 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22233,12 +22233,12 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22291,12 +22291,12 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22349,12 +22349,12 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22407,12 +22407,12 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22465,12 +22465,12 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22523,12 +22523,12 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22581,12 +22581,12 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22639,12 +22639,12 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22697,12 +22697,12 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22755,12 +22755,12 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22808,12 +22808,12 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22857,12 +22857,12 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22910,12 +22910,12 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -22963,12 +22963,12 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23016,12 +23016,12 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23073,12 +23073,12 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>4 days, 18:50:23.544892</t>
+          <t>3 days, 16:56:02.307246</t>
         </is>
       </c>
     </row>
@@ -23126,12 +23126,12 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23183,12 +23183,12 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>4 days, 18:50:23.544827</t>
+          <t>3 days, 16:56:02.307185</t>
         </is>
       </c>
     </row>
@@ -23236,12 +23236,12 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23289,12 +23289,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23342,12 +23342,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23395,12 +23395,12 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23448,12 +23448,12 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23554,12 +23554,12 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23607,12 +23607,12 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23660,12 +23660,12 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23713,12 +23713,12 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23766,12 +23766,12 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23819,12 +23819,12 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23872,12 +23872,12 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23925,12 +23925,12 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -23978,12 +23978,12 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24031,12 +24031,12 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24084,12 +24084,12 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24137,12 +24137,12 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24190,12 +24190,12 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24243,12 +24243,12 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24296,12 +24296,12 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24349,12 +24349,12 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24406,12 +24406,12 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>4 days, 18:50:23.544291</t>
+          <t>3 days, 16:56:02.306665</t>
         </is>
       </c>
     </row>
@@ -24459,12 +24459,12 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24512,12 +24512,12 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24565,12 +24565,12 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24618,12 +24618,12 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24671,12 +24671,12 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24724,12 +24724,12 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24781,12 +24781,12 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>3 days, 19:20:23.544094</t>
+          <t>2 days, 17:26:02.306485</t>
         </is>
       </c>
     </row>
@@ -24838,12 +24838,12 @@
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>3 days, 19:20:23.544058</t>
+          <t>2 days, 17:26:02.306450</t>
         </is>
       </c>
     </row>
@@ -24891,12 +24891,12 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -24948,12 +24948,12 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>3 days, 19:20:23.543992</t>
+          <t>2 days, 17:26:02.306378</t>
         </is>
       </c>
     </row>
@@ -25006,12 +25006,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25059,12 +25059,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25112,12 +25112,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25170,12 +25170,12 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25223,12 +25223,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25280,12 +25280,12 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>3 days, 19:20:23.543816</t>
+          <t>2 days, 17:26:02.306208</t>
         </is>
       </c>
     </row>
@@ -25333,12 +25333,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25391,12 +25391,12 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25449,12 +25449,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25507,12 +25507,12 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25560,12 +25560,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25618,12 +25618,12 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25671,12 +25671,12 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25724,12 +25724,12 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25782,12 +25782,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25840,12 +25840,12 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25898,12 +25898,12 @@
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -25956,12 +25956,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26009,12 +26009,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26062,12 +26062,12 @@
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26120,12 +26120,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26173,12 +26173,12 @@
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26226,12 +26226,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26279,12 +26279,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26332,12 +26332,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26385,12 +26385,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26438,12 +26438,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26491,12 +26491,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26549,12 +26549,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26602,12 +26602,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26655,12 +26655,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26708,12 +26708,12 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26761,12 +26761,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26814,12 +26814,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26867,12 +26867,12 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26920,12 +26920,12 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -26973,12 +26973,12 @@
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27026,12 +27026,12 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27079,12 +27079,12 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27132,12 +27132,12 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27185,12 +27185,12 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27238,12 +27238,12 @@
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27291,12 +27291,12 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27344,12 +27344,12 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27397,12 +27397,12 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27450,12 +27450,12 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27503,12 +27503,12 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27556,12 +27556,12 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27609,12 +27609,12 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27662,12 +27662,12 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27711,12 +27711,12 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27760,12 +27760,12 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27809,12 +27809,12 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27858,12 +27858,12 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27911,12 +27911,12 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -27964,12 +27964,12 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28017,12 +28017,12 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28070,12 +28070,12 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28123,12 +28123,12 @@
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28176,12 +28176,12 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28229,12 +28229,12 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28282,12 +28282,12 @@
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28335,12 +28335,12 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28388,12 +28388,12 @@
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28441,12 +28441,12 @@
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28494,12 +28494,12 @@
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28547,12 +28547,12 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28600,12 +28600,12 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28653,12 +28653,12 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28706,12 +28706,12 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28759,12 +28759,12 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28812,12 +28812,12 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28865,12 +28865,12 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28918,12 +28918,12 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -28971,12 +28971,12 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29024,12 +29024,12 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29077,12 +29077,12 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29130,12 +29130,12 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29183,12 +29183,12 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29236,12 +29236,12 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29289,12 +29289,12 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29342,12 +29342,12 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29395,12 +29395,12 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29448,12 +29448,12 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29501,12 +29501,12 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29554,12 +29554,12 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29607,12 +29607,12 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29660,12 +29660,12 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29713,12 +29713,12 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29766,12 +29766,12 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29819,12 +29819,12 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29872,12 +29872,12 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29925,12 +29925,12 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>
@@ -29978,12 +29978,12 @@
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>05/23/26 12:09 PM</t>
+          <t>05/24/26 02:03 PM</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M561"/>
+  <dimension ref="A1:M553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -551,12 +551,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>23 days, 17:25:46.597029</t>
+          <t>22 days, 18:44:06.950893</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>20 days, 23:10:46.596970</t>
+          <t>20 days, 0:29:06.950836</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>20 days, 23:10:46.596925</t>
+          <t>20 days, 0:29:06.950795</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>20 days, 23:10:46.596888</t>
+          <t>20 days, 0:29:06.950764</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>COMDC, MCI03, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, MCI03, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>20 days, 22:55:46.596839</t>
+          <t>20 days, 0:14:06.950720</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>COMDC, MCI03, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, MCI03, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>20 days, 22:55:46.596791</t>
+          <t>20 days, 0:14:06.950680</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>20 days, 22:55:46.596756</t>
+          <t>20 days, 0:14:06.950652</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>COMDC, MCI03, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, MCI03, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>20 days, 22:55:46.596711</t>
+          <t>20 days, 0:14:06.950613</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>COMDC, MCI03, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, MCI03, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>20 days, 22:55:46.596588</t>
+          <t>20 days, 0:14:06.950573</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>COMDC, MCI03, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, MCI03, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>20 days, 22:55:46.596542</t>
+          <t>20 days, 0:14:06.950537</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>20 days, 22:55:46.596507</t>
+          <t>20 days, 0:14:06.950509</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>20 days, 22:55:46.596473</t>
+          <t>20 days, 0:14:06.950482</t>
         </is>
       </c>
     </row>
@@ -1230,17 +1230,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; NEON03, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; NEON03, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.596433</t>
+          <t>19 days, 20:59:06.950449</t>
         </is>
       </c>
     </row>
@@ -1287,17 +1287,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; NEON03, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; NEON03, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.596394</t>
+          <t>19 days, 20:59:06.950415</t>
         </is>
       </c>
     </row>
@@ -1344,17 +1344,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.596355</t>
+          <t>19 days, 20:59:06.950382</t>
         </is>
       </c>
     </row>
@@ -1401,17 +1401,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.596318</t>
+          <t>19 days, 20:59:06.950351</t>
         </is>
       </c>
     </row>
@@ -1458,17 +1458,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.596281</t>
+          <t>19 days, 20:59:06.950320</t>
         </is>
       </c>
     </row>
@@ -1515,17 +1515,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.596243</t>
+          <t>19 days, 20:59:06.950271</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.596205</t>
+          <t>19 days, 20:59:06.950239</t>
         </is>
       </c>
     </row>
@@ -1629,17 +1629,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.596167</t>
+          <t>19 days, 20:59:06.950207</t>
         </is>
       </c>
     </row>
@@ -1686,17 +1686,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.596129</t>
+          <t>19 days, 20:59:06.950175</t>
         </is>
       </c>
     </row>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.596093</t>
+          <t>19 days, 20:59:06.950145</t>
         </is>
       </c>
     </row>
@@ -1800,17 +1800,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.596056</t>
+          <t>19 days, 20:59:06.950114</t>
         </is>
       </c>
     </row>
@@ -1857,17 +1857,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.596019</t>
+          <t>19 days, 20:59:06.950084</t>
         </is>
       </c>
     </row>
@@ -1914,17 +1914,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.595982</t>
+          <t>19 days, 20:59:06.950053</t>
         </is>
       </c>
     </row>
@@ -1971,17 +1971,17 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.595944</t>
+          <t>19 days, 20:59:06.950023</t>
         </is>
       </c>
     </row>
@@ -2028,17 +2028,17 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>20 days, 19:40:46.595907</t>
+          <t>19 days, 20:59:06.949992</t>
         </is>
       </c>
     </row>
@@ -2090,17 +2090,17 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC - 24-hour delay</t>
+          <t>PEPCODC - 24-hour delay</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>20 days, 1:55:46.595868</t>
+          <t>19 days, 3:14:06.949962</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2150,19 +2150,15 @@
           <t>06/25/26 03:00 pm</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>20 days, 1:25:46.595826</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2180,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2212,19 +2208,15 @@
           <t>06/25/26 03:00 pm</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>VDC &amp; WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>20 days, 1:25:46.595789</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2238,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2274,19 +2266,15 @@
           <t>06/25/26 03:00 pm</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>20 days, 1:25:46.595751</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2296,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2336,19 +2324,15 @@
           <t>06/25/26 03:00 pm</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>20 days, 1:25:46.595712</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -2400,17 +2384,17 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PEPCODC - 24-hour delay &amp; WASA02 - Not yet responded</t>
+          <t>PEPCODC &amp; WASA02 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>20 days, 0:55:46.595647</t>
+          <t>19 days, 2:14:06.949788</t>
         </is>
       </c>
     </row>
@@ -2458,12 +2442,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>20 days, 0:40:46.595608</t>
+          <t>19 days, 1:59:06.949756</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2490,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2516,7 +2500,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19 days, 23:40:46.595570</t>
+          <t>19 days, 0:59:06.949725</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2553,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>19 days, 22:55:46.595537</t>
+          <t>19 days, 0:14:06.949696</t>
         </is>
       </c>
     </row>
@@ -2617,12 +2601,12 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2659,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -2723,12 +2707,12 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2760,12 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2818,12 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2876,12 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -2950,12 +2934,12 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3008,12 +2992,12 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3050,12 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3124,12 +3108,12 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3182,12 +3166,12 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3224,12 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3298,12 +3282,12 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3335,12 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3403,17 +3387,17 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded</t>
+          <t>WASA02 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>18 days, 0:40:46.594966</t>
+          <t>17 days, 1:59:06.949175</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3419,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3458,19 +3442,15 @@
           <t>06/23/26 01:00 pm</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>WASA02 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>17 days, 23:25:46.594931</t>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3498,12 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3551,12 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3624,12 +3604,12 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3677,12 +3657,12 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3730,12 +3710,12 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3783,12 +3763,12 @@
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3836,12 +3816,12 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3889,12 +3869,12 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3922,12 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -3995,12 +3975,12 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4048,12 +4028,12 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4101,12 +4081,12 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4134,12 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4187,12 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4240,12 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4313,12 +4293,12 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4346,12 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4419,12 +4399,12 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4472,12 +4452,12 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4525,12 +4505,12 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4578,12 +4558,12 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4631,12 +4611,12 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4684,12 +4664,12 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4717,12 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4790,12 +4770,12 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4823,12 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4896,12 +4876,12 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4934,12 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5007,12 +4987,12 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5040,12 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5113,12 +5093,12 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5146,12 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5199,12 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5272,12 +5252,12 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5325,12 +5305,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5378,12 +5358,12 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5431,12 +5411,12 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5484,12 +5464,12 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5517,12 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5590,12 +5570,12 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5643,12 +5623,12 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -5695,17 +5675,17 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded &amp; WGL07 - Not complete/In progress</t>
+          <t>WASA02 - Not complete/In progress &amp; WGL07 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593542</t>
+          <t>16 days, 18:44:06.948087</t>
         </is>
       </c>
     </row>
@@ -5752,17 +5732,17 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded &amp; WGL07 - Not complete/In progress</t>
+          <t>WASA02 - Not complete/In progress &amp; WGL07 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593501</t>
+          <t>16 days, 18:44:06.948056</t>
         </is>
       </c>
     </row>
@@ -5809,17 +5789,17 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded &amp; WGL07 - Not complete/In progress</t>
+          <t>WASA02 - Not complete/In progress &amp; WGL07 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593463</t>
+          <t>16 days, 18:44:06.948025</t>
         </is>
       </c>
     </row>
@@ -5866,17 +5846,17 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded</t>
+          <t>WASA02 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593432</t>
+          <t>16 days, 18:44:06.947999</t>
         </is>
       </c>
     </row>
@@ -5923,17 +5903,17 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded</t>
+          <t>WASA02 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593395</t>
+          <t>16 days, 18:44:06.947972</t>
         </is>
       </c>
     </row>
@@ -5980,17 +5960,17 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded</t>
+          <t>WASA02 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593365</t>
+          <t>16 days, 18:44:06.947946</t>
         </is>
       </c>
     </row>
@@ -6037,17 +6017,17 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded</t>
+          <t>WASA02 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593335</t>
+          <t>16 days, 18:44:06.947921</t>
         </is>
       </c>
     </row>
@@ -6094,17 +6074,17 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded</t>
+          <t>WASA02 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593305</t>
+          <t>16 days, 18:44:06.947895</t>
         </is>
       </c>
     </row>
@@ -6151,17 +6131,17 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded &amp; WGL07 - Not complete/In progress</t>
+          <t>WASA02 - Not complete/In progress &amp; WGL07 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593269</t>
+          <t>16 days, 18:44:06.947866</t>
         </is>
       </c>
     </row>
@@ -6208,17 +6188,17 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded</t>
+          <t>WASA02 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593238</t>
+          <t>16 days, 18:44:06.947840</t>
         </is>
       </c>
     </row>
@@ -6265,17 +6245,17 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded</t>
+          <t>WASA02 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593209</t>
+          <t>16 days, 18:44:06.947814</t>
         </is>
       </c>
     </row>
@@ -6322,17 +6302,17 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded</t>
+          <t>WASA02 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593178</t>
+          <t>16 days, 18:44:06.947789</t>
         </is>
       </c>
     </row>
@@ -6379,17 +6359,17 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>WASA02 - Not yet responded</t>
+          <t>WASA02 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593148</t>
+          <t>16 days, 18:44:06.947763</t>
         </is>
       </c>
     </row>
@@ -6446,12 +6426,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593114</t>
+          <t>16 days, 18:44:06.947734</t>
         </is>
       </c>
     </row>
@@ -6508,12 +6488,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593079</t>
+          <t>16 days, 18:44:06.947704</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6550,12 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593044</t>
+          <t>16 days, 18:44:06.947675</t>
         </is>
       </c>
     </row>
@@ -6632,12 +6612,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>17 days, 17:25:46.593008</t>
+          <t>16 days, 18:44:06.947645</t>
         </is>
       </c>
     </row>
@@ -6690,12 +6670,12 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -6748,12 +6728,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6786,12 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -6864,12 +6844,12 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -6922,12 +6902,12 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -6980,12 +6960,12 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7038,12 +7018,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7096,12 +7076,12 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7154,12 +7134,12 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7212,12 +7192,12 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7270,12 +7250,12 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7308,12 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7386,12 +7366,12 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7424,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7502,12 +7482,12 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7560,12 +7540,12 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7618,12 +7598,12 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7676,12 +7656,12 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7734,12 +7714,12 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7792,12 +7772,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7841,12 +7821,12 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7870,12 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7939,12 +7919,12 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -7992,12 +7972,12 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -8045,12 +8025,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -8102,12 +8082,12 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>16 days, 21:55:46.592045</t>
+          <t>15 days, 23:14:06.946949</t>
         </is>
       </c>
     </row>
@@ -8159,12 +8139,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>16 days, 21:55:46.592006</t>
+          <t>15 days, 23:14:06.946917</t>
         </is>
       </c>
     </row>
@@ -8216,12 +8196,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>16 days, 21:55:46.591971</t>
+          <t>15 days, 23:14:06.946886</t>
         </is>
       </c>
     </row>
@@ -8273,12 +8253,12 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>16 days, 21:55:46.591939</t>
+          <t>15 days, 23:14:06.946858</t>
         </is>
       </c>
     </row>
@@ -8330,12 +8310,12 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>16 days, 21:55:46.591909</t>
+          <t>15 days, 23:14:06.946831</t>
         </is>
       </c>
     </row>
@@ -8387,12 +8367,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>16 days, 21:25:46.591873</t>
+          <t>15 days, 22:44:06.946799</t>
         </is>
       </c>
     </row>
@@ -8444,12 +8424,12 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>16 days, 21:25:46.591836</t>
+          <t>15 days, 22:44:06.946767</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8477,12 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -8550,12 +8530,12 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -8603,12 +8583,12 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -8656,12 +8636,12 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -8709,12 +8689,12 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -8762,12 +8742,12 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -8815,12 +8795,12 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -8868,12 +8848,12 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8901,12 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -8974,12 +8954,12 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9027,12 +9007,12 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9080,12 +9060,12 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9133,12 +9113,12 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9186,12 +9166,12 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9239,12 +9219,12 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9292,12 +9272,12 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9345,12 +9325,12 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9398,12 +9378,12 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9451,12 +9431,12 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9484,12 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9557,12 +9537,12 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9610,12 +9590,12 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9663,12 +9643,12 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9696,12 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9769,12 +9749,12 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9822,12 +9802,12 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9875,12 +9855,12 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9928,12 +9908,12 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9961,12 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10034,12 +10014,12 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10087,12 +10067,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10140,12 +10120,12 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10193,12 +10173,12 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10246,12 +10226,12 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10299,12 +10279,12 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10352,12 +10332,12 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10409,12 +10389,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>16 days, 19:10:46.590655</t>
+          <t>15 days, 20:29:06.945779</t>
         </is>
       </c>
     </row>
@@ -10462,12 +10442,12 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10495,12 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10568,12 +10548,12 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10621,12 +10601,12 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10674,12 +10654,12 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10727,12 +10707,12 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10760,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10833,12 +10813,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10886,12 +10866,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10939,12 +10919,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -10992,12 +10972,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11025,12 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11098,12 +11078,12 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11151,12 +11131,12 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11204,12 +11184,12 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11257,12 +11237,12 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11290,12 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11363,12 +11343,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11416,12 +11396,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11469,12 +11449,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11522,12 +11502,12 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11575,12 +11555,12 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11628,12 +11608,12 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11681,12 +11661,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11734,12 +11714,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11787,12 +11767,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11840,12 +11820,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11898,7 +11878,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11931,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12004,7 +11984,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12037,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12090,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12163,7 +12143,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12216,7 +12196,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12249,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12302,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12375,7 +12355,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12408,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12476,12 +12456,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12529,12 +12509,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12582,12 +12562,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12644,12 +12624,12 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>12 days, 1:25:46.589366</t>
+          <t>11 days, 2:44:06.944704</t>
         </is>
       </c>
     </row>
@@ -12706,12 +12686,12 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>12 days, 1:10:46.589327</t>
+          <t>11 days, 2:29:06.944672</t>
         </is>
       </c>
     </row>
@@ -12768,12 +12748,12 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>12 days, 1:10:46.589289</t>
+          <t>11 days, 2:29:06.944641</t>
         </is>
       </c>
     </row>
@@ -12826,12 +12806,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12879,12 +12859,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12932,12 +12912,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -12985,12 +12965,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -13038,12 +13018,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -13096,12 +13076,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -13149,12 +13129,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -13202,12 +13182,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -13255,12 +13235,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -13312,12 +13292,12 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>10 days, 18:10:46.588964</t>
+          <t>9 days, 19:29:06.944369</t>
         </is>
       </c>
     </row>
@@ -13365,12 +13345,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -13418,12 +13398,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -13471,12 +13451,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13509,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -13591,12 +13571,12 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.588784</t>
+          <t>9 days, 18:44:06.944208</t>
         </is>
       </c>
     </row>
@@ -13653,12 +13633,12 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.588748</t>
+          <t>9 days, 18:44:06.944178</t>
         </is>
       </c>
     </row>
@@ -13715,12 +13695,12 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.588713</t>
+          <t>9 days, 18:44:06.944150</t>
         </is>
       </c>
     </row>
@@ -13773,12 +13753,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -13831,12 +13811,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -13893,12 +13873,12 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.588575</t>
+          <t>9 days, 18:44:06.944067</t>
         </is>
       </c>
     </row>
@@ -13951,12 +13931,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -14009,12 +13989,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -14067,12 +14047,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -14125,12 +14105,12 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -14187,12 +14167,12 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.588407</t>
+          <t>9 days, 18:44:06.943935</t>
         </is>
       </c>
     </row>
@@ -14245,12 +14225,12 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -14303,12 +14283,12 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -14361,12 +14341,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -14423,12 +14403,12 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.588282</t>
+          <t>9 days, 18:44:06.943830</t>
         </is>
       </c>
     </row>
@@ -14481,12 +14461,12 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -14539,12 +14519,12 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -14597,12 +14577,12 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -14659,12 +14639,12 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.588164</t>
+          <t>9 days, 18:44:06.943733</t>
         </is>
       </c>
     </row>
@@ -14721,12 +14701,12 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.588131</t>
+          <t>9 days, 18:44:06.943705</t>
         </is>
       </c>
     </row>
@@ -14783,12 +14763,12 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.588098</t>
+          <t>9 days, 18:44:06.943678</t>
         </is>
       </c>
     </row>
@@ -14841,12 +14821,12 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -14899,12 +14879,12 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -14961,12 +14941,12 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.588008</t>
+          <t>9 days, 18:44:06.943602</t>
         </is>
       </c>
     </row>
@@ -15019,12 +14999,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -15081,12 +15061,12 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.587946</t>
+          <t>9 days, 18:44:06.943548</t>
         </is>
       </c>
     </row>
@@ -15139,12 +15119,12 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -15197,12 +15177,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -15255,12 +15235,12 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -15313,12 +15293,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -15371,12 +15351,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -15429,12 +15409,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -15487,12 +15467,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -15545,12 +15525,12 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -15603,12 +15583,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -15665,12 +15645,12 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.587622</t>
+          <t>9 days, 18:44:06.943291</t>
         </is>
       </c>
     </row>
@@ -15727,12 +15707,12 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.587589</t>
+          <t>9 days, 18:44:06.943263</t>
         </is>
       </c>
     </row>
@@ -15785,12 +15765,12 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -15843,12 +15823,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -15905,12 +15885,12 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.587497</t>
+          <t>9 days, 18:44:06.943177</t>
         </is>
       </c>
     </row>
@@ -15967,12 +15947,12 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.587462</t>
+          <t>9 days, 18:44:06.943147</t>
         </is>
       </c>
     </row>
@@ -16025,12 +16005,12 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -16087,12 +16067,12 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.587401</t>
+          <t>9 days, 18:44:06.943095</t>
         </is>
       </c>
     </row>
@@ -16145,12 +16125,12 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -16203,12 +16183,12 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -16265,12 +16245,12 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.587315</t>
+          <t>9 days, 18:44:06.943021</t>
         </is>
       </c>
     </row>
@@ -16323,12 +16303,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -16381,12 +16361,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -16439,12 +16419,12 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -16497,12 +16477,12 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -16555,12 +16535,12 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -16613,12 +16593,12 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -16671,12 +16651,12 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -16729,12 +16709,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -16791,12 +16771,12 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.587060</t>
+          <t>9 days, 18:44:06.942803</t>
         </is>
       </c>
     </row>
@@ -16853,12 +16833,12 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.587026</t>
+          <t>9 days, 18:44:06.942775</t>
         </is>
       </c>
     </row>
@@ -16911,12 +16891,12 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -16969,12 +16949,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -17031,12 +17011,12 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586935</t>
+          <t>9 days, 18:44:06.942699</t>
         </is>
       </c>
     </row>
@@ -17093,12 +17073,12 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586901</t>
+          <t>9 days, 18:44:06.942670</t>
         </is>
       </c>
     </row>
@@ -17155,12 +17135,12 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586868</t>
+          <t>9 days, 18:44:06.942642</t>
         </is>
       </c>
     </row>
@@ -17213,12 +17193,12 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -17275,12 +17255,12 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586807</t>
+          <t>9 days, 18:44:06.942591</t>
         </is>
       </c>
     </row>
@@ -17337,12 +17317,12 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586774</t>
+          <t>9 days, 18:44:06.942562</t>
         </is>
       </c>
     </row>
@@ -17395,12 +17375,12 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -17453,12 +17433,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -17515,12 +17495,12 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586658</t>
+          <t>9 days, 18:44:06.942489</t>
         </is>
       </c>
     </row>
@@ -17573,12 +17553,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -17631,12 +17611,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -17693,12 +17673,12 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586570</t>
+          <t>9 days, 18:44:06.942418</t>
         </is>
       </c>
     </row>
@@ -17755,12 +17735,12 @@
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586534</t>
+          <t>9 days, 18:44:06.942389</t>
         </is>
       </c>
     </row>
@@ -17813,12 +17793,12 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -17875,12 +17855,12 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586474</t>
+          <t>9 days, 18:44:06.942339</t>
         </is>
       </c>
     </row>
@@ -17933,12 +17913,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -17991,12 +17971,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -18053,12 +18033,12 @@
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586380</t>
+          <t>9 days, 18:44:06.942239</t>
         </is>
       </c>
     </row>
@@ -18115,12 +18095,12 @@
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586347</t>
+          <t>9 days, 18:44:06.942208</t>
         </is>
       </c>
     </row>
@@ -18173,12 +18153,12 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -18235,12 +18215,12 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586287</t>
+          <t>9 days, 18:44:06.942160</t>
         </is>
       </c>
     </row>
@@ -18297,12 +18277,12 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586254</t>
+          <t>9 days, 18:44:06.942131</t>
         </is>
       </c>
     </row>
@@ -18355,12 +18335,12 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -18417,12 +18397,12 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586190</t>
+          <t>9 days, 18:44:06.942077</t>
         </is>
       </c>
     </row>
@@ -18475,12 +18455,12 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -18537,12 +18517,12 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586127</t>
+          <t>9 days, 18:44:06.942025</t>
         </is>
       </c>
     </row>
@@ -18595,12 +18575,12 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -18657,12 +18637,12 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586068</t>
+          <t>9 days, 18:44:06.941977</t>
         </is>
       </c>
     </row>
@@ -18719,12 +18699,12 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.586037</t>
+          <t>9 days, 18:44:06.941950</t>
         </is>
       </c>
     </row>
@@ -18777,12 +18757,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -18835,12 +18815,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -18893,12 +18873,12 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -18951,12 +18931,12 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18958,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -19006,19 +18986,15 @@
           <t>06/16/26 07:00 am</t>
         </is>
       </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t>WASA02 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M330" t="inlineStr">
-        <is>
-          <t>10 days, 17:25:46.585864</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19071,12 +19047,12 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19098,7 +19074,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -19126,19 +19102,15 @@
           <t>06/16/26 07:00 am</t>
         </is>
       </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>WASA02 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>10 days, 17:25:46.585790</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19191,12 +19163,12 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19218,7 +19190,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -19246,19 +19218,15 @@
           <t>06/16/26 07:00 am</t>
         </is>
       </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>WASA02 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M334" t="inlineStr">
-        <is>
-          <t>10 days, 17:25:46.585714</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19280,7 +19248,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -19308,19 +19276,15 @@
           <t>06/16/26 07:00 am</t>
         </is>
       </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>WASA02 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M335" t="inlineStr">
-        <is>
-          <t>10 days, 17:25:46.585644</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19373,12 +19337,12 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19431,12 +19395,12 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19489,12 +19453,12 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19516,7 +19480,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -19544,19 +19508,15 @@
           <t>06/16/26 07:00 am</t>
         </is>
       </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>WASA02 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>10 days, 17:25:46.585497</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19609,12 +19569,12 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19667,12 +19627,12 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19725,12 +19685,12 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19783,12 +19743,12 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19841,12 +19801,12 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19899,12 +19859,12 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -19957,12 +19917,12 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20015,12 +19975,12 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20073,12 +20033,12 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20131,12 +20091,12 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20189,12 +20149,12 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20247,12 +20207,12 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20309,12 +20269,12 @@
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.585139</t>
+          <t>9 days, 18:44:06.941221</t>
         </is>
       </c>
     </row>
@@ -20367,12 +20327,12 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20425,12 +20385,12 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20483,12 +20443,12 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20541,12 +20501,12 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20599,12 +20559,12 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20657,12 +20617,12 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20715,12 +20675,12 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20777,12 +20737,12 @@
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>10 days, 17:25:46.584904</t>
+          <t>9 days, 18:44:06.941027</t>
         </is>
       </c>
     </row>
@@ -20835,12 +20795,12 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20893,12 +20853,12 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -20951,12 +20911,12 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21009,12 +20969,12 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21066,12 +21026,12 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>10 days, 3:10:46.584764</t>
+          <t>9 days, 4:29:06.940913</t>
         </is>
       </c>
     </row>
@@ -21119,12 +21079,12 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21177,12 +21137,12 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21235,12 +21195,12 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21293,12 +21253,12 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21351,12 +21311,12 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21409,12 +21369,12 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21467,12 +21427,12 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21524,12 +21484,12 @@
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>9 days, 20:25:46.584480</t>
+          <t>8 days, 21:44:06.940697</t>
         </is>
       </c>
     </row>
@@ -21577,12 +21537,12 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21630,12 +21590,12 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21688,12 +21648,12 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21746,12 +21706,12 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21804,12 +21764,12 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21862,12 +21822,12 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21920,12 +21880,12 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -21982,7 +21942,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>6 days, 23:55:46.584215</t>
+          <t>6 days, 1:14:06.940476</t>
         </is>
       </c>
     </row>
@@ -22035,7 +21995,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22088,7 +22048,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22141,7 +22101,7 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22154,7 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22247,7 +22207,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22300,7 +22260,7 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22353,7 +22313,7 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22405,12 +22365,12 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>6 days, 20:25:46.583964</t>
+          <t>5 days, 21:44:06.940250</t>
         </is>
       </c>
     </row>
@@ -22458,12 +22418,12 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22511,12 +22471,12 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22564,12 +22524,12 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22617,12 +22577,12 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22670,12 +22630,12 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22723,12 +22683,12 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22776,12 +22736,12 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22829,12 +22789,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22882,12 +22842,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22935,12 +22895,12 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -22988,12 +22948,12 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23041,12 +23001,12 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23094,12 +23054,12 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23147,12 +23107,12 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23200,12 +23160,12 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23253,12 +23213,12 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23306,12 +23266,12 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23359,12 +23319,12 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23412,12 +23372,12 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23465,12 +23425,12 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23518,12 +23478,12 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23571,12 +23531,12 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23628,12 +23588,12 @@
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>6 days, 19:55:46.583261</t>
+          <t>5 days, 21:14:06.939670</t>
         </is>
       </c>
     </row>
@@ -23685,12 +23645,12 @@
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>6 days, 18:55:46.583229</t>
+          <t>5 days, 20:14:06.939645</t>
         </is>
       </c>
     </row>
@@ -23738,12 +23698,12 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23796,7 +23756,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23849,7 +23809,7 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23902,7 +23862,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -23955,7 +23915,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24008,7 +23968,7 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24061,7 +24021,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24118,7 +24078,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>5 days, 22:55:46.582981</t>
+          <t>5 days, 0:14:06.939438</t>
         </is>
       </c>
     </row>
@@ -24175,7 +24135,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>5 days, 22:55:46.582943</t>
+          <t>5 days, 0:14:06.939405</t>
         </is>
       </c>
     </row>
@@ -24232,7 +24192,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>5 days, 22:55:46.582903</t>
+          <t>5 days, 0:14:06.939369</t>
         </is>
       </c>
     </row>
@@ -24289,7 +24249,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>5 days, 22:55:46.582863</t>
+          <t>5 days, 0:14:06.939336</t>
         </is>
       </c>
     </row>
@@ -24337,12 +24297,12 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24390,12 +24350,12 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24443,12 +24403,12 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24496,12 +24456,12 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24549,12 +24509,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24602,12 +24562,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24655,12 +24615,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24712,12 +24672,12 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>5 days, 21:40:46.582581</t>
+          <t>4 days, 22:59:06.939109</t>
         </is>
       </c>
     </row>
@@ -24765,12 +24725,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24818,12 +24778,12 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24871,12 +24831,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24924,12 +24884,12 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -24977,12 +24937,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25030,12 +24990,12 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25083,12 +25043,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25140,12 +25100,12 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>5 days, 17:25:46.582326</t>
+          <t>4 days, 18:44:06.938899</t>
         </is>
       </c>
     </row>
@@ -25197,12 +25157,12 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>5 days, 17:25:46.582274</t>
+          <t>4 days, 18:44:06.938861</t>
         </is>
       </c>
     </row>
@@ -25250,12 +25210,12 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25303,12 +25263,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25356,12 +25316,12 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25414,12 +25374,12 @@
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25472,12 +25432,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25530,12 +25490,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25588,12 +25548,12 @@
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25646,12 +25606,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25704,12 +25664,12 @@
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25762,12 +25722,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25820,12 +25780,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25878,12 +25838,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25936,12 +25896,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -25994,12 +25954,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26052,12 +26012,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26110,12 +26070,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26168,12 +26128,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26226,12 +26186,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26284,12 +26244,12 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26342,12 +26302,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26400,12 +26360,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26458,12 +26418,12 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26516,12 +26476,12 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26574,12 +26534,12 @@
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26632,12 +26592,12 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26690,12 +26650,12 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26748,12 +26708,12 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26806,12 +26766,12 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26864,12 +26824,12 @@
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26922,12 +26882,12 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -26980,12 +26940,12 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27038,12 +26998,12 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27096,12 +27056,12 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27154,12 +27114,12 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27212,12 +27172,12 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27270,12 +27230,12 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27328,12 +27288,12 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27386,12 +27346,12 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27444,12 +27404,12 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27502,12 +27462,12 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27560,12 +27520,12 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27613,12 +27573,12 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27666,12 +27626,12 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27719,12 +27679,12 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27777,12 +27737,12 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27834,12 +27794,12 @@
       </c>
       <c r="K487" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>4 days, 2:25:46.580846</t>
+          <t>3 days, 3:44:06.937622</t>
         </is>
       </c>
     </row>
@@ -27892,12 +27852,12 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -27950,12 +27910,12 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28008,12 +27968,12 @@
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28061,12 +28021,12 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28119,12 +28079,12 @@
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28177,12 +28137,12 @@
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28234,12 +28194,12 @@
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>4 days, 2:25:46.580611</t>
+          <t>3 days, 3:44:06.937441</t>
         </is>
       </c>
     </row>
@@ -28292,12 +28252,12 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28350,12 +28310,12 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28408,12 +28368,12 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28466,12 +28426,12 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28524,12 +28484,12 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28582,12 +28542,12 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28639,12 +28599,12 @@
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>4 days, 2:25:46.580404</t>
+          <t>3 days, 3:44:06.937253</t>
         </is>
       </c>
     </row>
@@ -28692,12 +28652,12 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28750,12 +28710,12 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28808,7 +28768,7 @@
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28856,12 +28816,12 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28909,12 +28869,12 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -28967,12 +28927,12 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29020,12 +28980,12 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29073,12 +29033,12 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29131,12 +29091,12 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29189,12 +29149,12 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29247,12 +29207,12 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29305,12 +29265,12 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29363,12 +29323,12 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29421,12 +29381,12 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29479,12 +29439,12 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29537,12 +29497,12 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29595,12 +29555,12 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29653,12 +29613,12 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29711,12 +29671,12 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29769,12 +29729,12 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29827,12 +29787,12 @@
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29885,12 +29845,12 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -29943,12 +29903,12 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -30001,12 +29961,12 @@
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -30059,12 +30019,12 @@
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -30117,12 +30077,12 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -30170,12 +30130,12 @@
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M528" t="inlineStr">
         <is>
-          <t>3 days, 3:25:46.579382</t>
+          <t>2 days, 4:44:06.936379</t>
         </is>
       </c>
     </row>
@@ -30223,16 +30183,17 @@
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M529" t="inlineStr">
         <is>
-          <t>3 days, 3:25:46.579339</t>
+          <t>2 days, 4:44:06.936346</t>
         </is>
       </c>
     </row>
     <row r="530">
+      <c r="A530" t="inlineStr"/>
       <c r="B530" t="inlineStr">
         <is>
           <t>5TH ST NE</t>
@@ -30243,6 +30204,11 @@
           <t>New</t>
         </is>
       </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="E530" t="inlineStr">
         <is>
           <t xml:space="preserve"> 26361713</t>
@@ -30261,6 +30227,21 @@
       <c r="I530" t="inlineStr">
         <is>
           <t>06/08/26 05:00 pm</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>PEPCODC &amp; WASA02 - Not complete/In progress</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>2 days, 4:44:06.936312</t>
         </is>
       </c>
     </row>
@@ -30308,12 +30289,12 @@
       </c>
       <c r="K531" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M531" t="inlineStr">
         <is>
-          <t>3 days, 3:25:46.579300</t>
+          <t>2 days, 4:44:06.936271</t>
         </is>
       </c>
     </row>
@@ -30357,12 +30338,12 @@
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -30410,12 +30391,12 @@
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M533" t="inlineStr">
         <is>
-          <t>3 days, 3:25:46.579230</t>
+          <t>2 days, 4:44:06.936210</t>
         </is>
       </c>
     </row>
@@ -30467,12 +30448,12 @@
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M534" t="inlineStr">
         <is>
-          <t>3 days, 3:10:46.579198</t>
+          <t>2 days, 4:29:06.936183</t>
         </is>
       </c>
     </row>
@@ -30520,12 +30501,12 @@
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -30573,12 +30554,12 @@
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -30626,12 +30607,12 @@
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -30679,12 +30660,12 @@
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -30732,12 +30713,12 @@
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -30785,12 +30766,12 @@
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -30838,12 +30819,12 @@
       <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -30891,12 +30872,12 @@
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -30944,12 +30925,12 @@
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -31001,12 +30982,12 @@
       </c>
       <c r="K544" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M544" t="inlineStr">
         <is>
-          <t>3 days, 3:10:46.578914</t>
+          <t>2 days, 4:29:06.935944</t>
         </is>
       </c>
     </row>
@@ -31054,12 +31035,12 @@
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -31107,12 +31088,12 @@
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -31160,12 +31141,12 @@
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -31213,12 +31194,12 @@
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -31266,12 +31247,12 @@
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -31319,12 +31300,12 @@
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -31372,12 +31353,12 @@
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -31425,12 +31406,12 @@
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>
@@ -31478,440 +31459,12 @@
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>06/04/26 01:34 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>EMERGENCY CREW ON SITE</t>
-        </is>
-      </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>MINTWOOD PL NW</t>
-        </is>
-      </c>
-      <c r="C554" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="E554" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 26358206</t>
-        </is>
-      </c>
-      <c r="G554" t="inlineStr">
-        <is>
-          <t>05/14/26 05:00 pm</t>
-        </is>
-      </c>
-      <c r="H554" t="inlineStr">
-        <is>
-          <t>05/19/26 05:00 pm</t>
-        </is>
-      </c>
-      <c r="I554" t="inlineStr">
-        <is>
-          <t>06/05/26 05:00 pm</t>
-        </is>
-      </c>
-      <c r="J554" t="inlineStr"/>
-      <c r="K554" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L554" t="inlineStr">
-        <is>
-          <t>06/04/26 01:34 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>FMCC - PCKG 20</t>
-        </is>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>QUINCY PL NW</t>
-        </is>
-      </c>
-      <c r="C555" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="D555" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="E555" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 26358188</t>
-        </is>
-      </c>
-      <c r="G555" t="inlineStr">
-        <is>
-          <t>05/14/26 04:38 pm</t>
-        </is>
-      </c>
-      <c r="H555" t="inlineStr">
-        <is>
-          <t>05/19/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="I555" t="inlineStr">
-        <is>
-          <t>06/05/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="J555" t="inlineStr"/>
-      <c r="K555" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L555" t="inlineStr">
-        <is>
-          <t>06/04/26 01:34 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>FMCC - PCKG 20</t>
-        </is>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>4TH ST NW</t>
-        </is>
-      </c>
-      <c r="C556" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="D556" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="E556" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 26358187</t>
-        </is>
-      </c>
-      <c r="G556" t="inlineStr">
-        <is>
-          <t>05/14/26 04:38 pm</t>
-        </is>
-      </c>
-      <c r="H556" t="inlineStr">
-        <is>
-          <t>05/19/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="I556" t="inlineStr">
-        <is>
-          <t>06/05/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="J556" t="inlineStr"/>
-      <c r="K556" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L556" t="inlineStr">
-        <is>
-          <t>06/04/26 01:34 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>FMCC - PCKG 20</t>
-        </is>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>SAVANNAH ST SE</t>
-        </is>
-      </c>
-      <c r="C557" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="D557" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 26358186</t>
-        </is>
-      </c>
-      <c r="G557" t="inlineStr">
-        <is>
-          <t>05/14/26 04:38 pm</t>
-        </is>
-      </c>
-      <c r="H557" t="inlineStr">
-        <is>
-          <t>05/19/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="I557" t="inlineStr">
-        <is>
-          <t>06/05/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="J557" t="inlineStr"/>
-      <c r="K557" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L557" t="inlineStr">
-        <is>
-          <t>06/04/26 01:34 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>FMCC - PCKG 20</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>4TH ST NW</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="D558" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="E558" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 26358185</t>
-        </is>
-      </c>
-      <c r="G558" t="inlineStr">
-        <is>
-          <t>05/14/26 04:38 pm</t>
-        </is>
-      </c>
-      <c r="H558" t="inlineStr">
-        <is>
-          <t>05/19/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="I558" t="inlineStr">
-        <is>
-          <t>06/05/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="J558" t="inlineStr"/>
-      <c r="K558" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L558" t="inlineStr">
-        <is>
-          <t>06/04/26 01:34 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>FMCC - PCKG 20</t>
-        </is>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>4TH ST NW</t>
-        </is>
-      </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="D559" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="E559" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 26358184</t>
-        </is>
-      </c>
-      <c r="G559" t="inlineStr">
-        <is>
-          <t>05/14/26 04:38 pm</t>
-        </is>
-      </c>
-      <c r="H559" t="inlineStr">
-        <is>
-          <t>05/19/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="I559" t="inlineStr">
-        <is>
-          <t>06/05/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="J559" t="inlineStr"/>
-      <c r="K559" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L559" t="inlineStr">
-        <is>
-          <t>06/04/26 01:34 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>CANCEL: WE ALREADY HAD A TICKET FOR THIS LOCATION ...</t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>13TH ST NE</t>
-        </is>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="D560" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="E560" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 26358183</t>
-        </is>
-      </c>
-      <c r="G560" t="inlineStr">
-        <is>
-          <t>05/15/26 07:13 am</t>
-        </is>
-      </c>
-      <c r="H560" t="inlineStr">
-        <is>
-          <t>05/19/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="I560" t="inlineStr">
-        <is>
-          <t>06/05/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="J560" t="inlineStr">
-        <is>
-          <t>PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
-        </is>
-      </c>
-      <c r="K560" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M560" t="inlineStr">
-        <is>
-          <t>3:10:46.578408</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>FMCC - PCKG 20</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>3RD ST NW</t>
-        </is>
-      </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="E561" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 26358182</t>
-        </is>
-      </c>
-      <c r="G561" t="inlineStr">
-        <is>
-          <t>05/14/26 04:38 pm</t>
-        </is>
-      </c>
-      <c r="H561" t="inlineStr">
-        <is>
-          <t>05/19/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="I561" t="inlineStr">
-        <is>
-          <t>06/05/26 04:45 pm</t>
-        </is>
-      </c>
-      <c r="J561" t="inlineStr"/>
-      <c r="K561" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L561" t="inlineStr">
-        <is>
-          <t>06/04/26 01:34 PM</t>
+          <t>06/05/26 12:15 PM</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -551,12 +551,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>22 days, 18:44:06.950893</t>
+          <t>21 days, 18:30:13.821808</t>
         </is>
       </c>
     </row>
@@ -608,12 +608,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>20 days, 0:29:06.950836</t>
+          <t>19 days, 0:15:13.821749</t>
         </is>
       </c>
     </row>
@@ -665,12 +665,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>20 days, 0:29:06.950795</t>
+          <t>19 days, 0:15:13.821708</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>20 days, 0:29:06.950764</t>
+          <t>19 days, 0:15:13.821678</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>20 days, 0:14:06.950720</t>
+          <t>19 days, 0:00:13.821633</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>20 days, 0:14:06.950680</t>
+          <t>19 days, 0:00:13.821590</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>20 days, 0:14:06.950652</t>
+          <t>19 days, 0:00:13.821560</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>20 days, 0:14:06.950613</t>
+          <t>19 days, 0:00:13.821521</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>20 days, 0:14:06.950573</t>
+          <t>19 days, 0:00:13.821480</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>20 days, 0:14:06.950537</t>
+          <t>19 days, 0:00:13.821444</t>
         </is>
       </c>
     </row>
@@ -1116,17 +1116,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>COMDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>20 days, 0:14:06.950509</t>
+          <t>19 days, 0:00:13.821415</t>
         </is>
       </c>
     </row>
@@ -1173,17 +1173,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>COMDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>20 days, 0:14:06.950482</t>
+          <t>19 days, 0:00:13.821387</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950449</t>
+          <t>18 days, 20:45:13.821353</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950415</t>
+          <t>18 days, 20:45:13.821319</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950382</t>
+          <t>18 days, 20:45:13.821267</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950351</t>
+          <t>18 days, 20:45:13.821236</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950320</t>
+          <t>18 days, 20:45:13.821204</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950271</t>
+          <t>18 days, 20:45:13.821172</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950239</t>
+          <t>18 days, 20:45:13.821140</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950207</t>
+          <t>18 days, 20:45:13.821110</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950175</t>
+          <t>18 days, 20:45:13.821077</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950145</t>
+          <t>18 days, 20:45:13.821047</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950114</t>
+          <t>18 days, 20:45:13.821016</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950084</t>
+          <t>18 days, 20:45:13.820985</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950053</t>
+          <t>18 days, 20:45:13.820955</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.950023</t>
+          <t>18 days, 20:45:13.820925</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>19 days, 20:59:06.949992</t>
+          <t>18 days, 20:45:13.820895</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>19 days, 3:14:06.949962</t>
+          <t>18 days, 3:00:13.820864</t>
         </is>
       </c>
     </row>
@@ -2153,12 +2153,12 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>19 days, 2:14:06.949788</t>
+          <t>18 days, 2:00:13.820689</t>
         </is>
       </c>
     </row>
@@ -2437,17 +2437,17 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19 days, 1:59:06.949756</t>
+          <t>18 days, 1:45:13.820659</t>
         </is>
       </c>
     </row>
@@ -2495,12 +2495,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19 days, 0:59:06.949725</t>
+          <t>18 days, 0:45:13.820626</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>19 days, 0:14:06.949696</t>
+          <t>18 days, 0:00:13.820597</t>
         </is>
       </c>
     </row>
@@ -2601,12 +2601,12 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -2760,12 +2760,12 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -2818,12 +2818,12 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -2876,12 +2876,12 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -2934,12 +2934,12 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -2992,12 +2992,12 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3050,12 +3050,12 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3108,12 +3108,12 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3166,12 +3166,12 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3282,12 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3335,12 +3335,12 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>17 days, 1:59:06.949175</t>
+          <t>16 days, 1:45:13.820115</t>
         </is>
       </c>
     </row>
@@ -3445,12 +3445,12 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3498,12 +3498,12 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3604,12 +3604,12 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3657,12 +3657,12 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3763,12 +3763,12 @@
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3816,12 +3816,12 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -3975,12 +3975,12 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4028,12 +4028,12 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4081,12 +4081,12 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4134,12 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4187,12 +4187,12 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4240,12 +4240,12 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4293,12 +4293,12 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4346,12 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4452,12 +4452,12 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4505,12 +4505,12 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4558,12 +4558,12 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4664,12 +4664,12 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4770,12 +4770,12 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4876,12 +4876,12 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4934,12 +4934,12 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -4987,12 +4987,12 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5040,12 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -5093,12 +5093,12 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -5146,12 +5146,12 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -5199,12 +5199,12 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -5252,12 +5252,12 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -5305,12 +5305,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -5358,12 +5358,12 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -5464,12 +5464,12 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -5570,12 +5570,12 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -5680,12 +5680,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.948087</t>
+          <t>15 days, 18:30:13.819040</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.948056</t>
+          <t>15 days, 18:30:13.819008</t>
         </is>
       </c>
     </row>
@@ -5794,12 +5794,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.948025</t>
+          <t>15 days, 18:30:13.818977</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947999</t>
+          <t>15 days, 18:30:13.818950</t>
         </is>
       </c>
     </row>
@@ -5908,12 +5908,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947972</t>
+          <t>15 days, 18:30:13.818924</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947946</t>
+          <t>15 days, 18:30:13.818898</t>
         </is>
       </c>
     </row>
@@ -6022,12 +6022,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947921</t>
+          <t>15 days, 18:30:13.818871</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947895</t>
+          <t>15 days, 18:30:13.818845</t>
         </is>
       </c>
     </row>
@@ -6136,12 +6136,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947866</t>
+          <t>15 days, 18:30:13.818815</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947840</t>
+          <t>15 days, 18:30:13.818790</t>
         </is>
       </c>
     </row>
@@ -6250,12 +6250,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947814</t>
+          <t>15 days, 18:30:13.818764</t>
         </is>
       </c>
     </row>
@@ -6307,12 +6307,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947789</t>
+          <t>15 days, 18:30:13.818737</t>
         </is>
       </c>
     </row>
@@ -6364,12 +6364,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947763</t>
+          <t>15 days, 18:30:13.818711</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947734</t>
+          <t>15 days, 18:30:13.818682</t>
         </is>
       </c>
     </row>
@@ -6488,12 +6488,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947704</t>
+          <t>15 days, 18:30:13.818653</t>
         </is>
       </c>
     </row>
@@ -6550,12 +6550,12 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947675</t>
+          <t>15 days, 18:30:13.818624</t>
         </is>
       </c>
     </row>
@@ -6612,12 +6612,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>16 days, 18:44:06.947645</t>
+          <t>15 days, 18:30:13.818594</t>
         </is>
       </c>
     </row>
@@ -6670,12 +6670,12 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -6728,12 +6728,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -6786,12 +6786,12 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -6844,12 +6844,12 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -6902,12 +6902,12 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -6960,12 +6960,12 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7018,12 +7018,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7076,12 +7076,12 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7134,12 +7134,12 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7192,12 +7192,12 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7250,12 +7250,12 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7308,12 +7308,12 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7366,12 +7366,12 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7482,12 +7482,12 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7540,12 +7540,12 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7598,12 +7598,12 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7656,12 +7656,12 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7714,12 +7714,12 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7772,12 +7772,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7821,12 +7821,12 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7870,12 +7870,12 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -7972,12 +7972,12 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -8082,12 +8082,12 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>15 days, 23:14:06.946949</t>
+          <t>14 days, 23:00:13.817893</t>
         </is>
       </c>
     </row>
@@ -8139,12 +8139,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>15 days, 23:14:06.946917</t>
+          <t>14 days, 23:00:13.817861</t>
         </is>
       </c>
     </row>
@@ -8196,12 +8196,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>15 days, 23:14:06.946886</t>
+          <t>14 days, 23:00:13.817831</t>
         </is>
       </c>
     </row>
@@ -8253,12 +8253,12 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>15 days, 23:14:06.946858</t>
+          <t>14 days, 23:00:13.817801</t>
         </is>
       </c>
     </row>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>15 days, 23:14:06.946831</t>
+          <t>14 days, 23:00:13.817775</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>15 days, 22:44:06.946799</t>
+          <t>14 days, 22:30:13.817742</t>
         </is>
       </c>
     </row>
@@ -8424,12 +8424,12 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>15 days, 22:44:06.946767</t>
+          <t>14 days, 22:30:13.817710</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -8530,12 +8530,12 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -8636,12 +8636,12 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -8742,12 +8742,12 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -8795,12 +8795,12 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -8848,12 +8848,12 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9007,12 +9007,12 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9060,12 +9060,12 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9113,12 +9113,12 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9166,12 +9166,12 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9219,12 +9219,12 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9272,12 +9272,12 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9325,12 +9325,12 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9431,12 +9431,12 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9537,12 +9537,12 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9590,12 +9590,12 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9643,12 +9643,12 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9696,12 +9696,12 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9749,12 +9749,12 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9802,12 +9802,12 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9855,12 +9855,12 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9908,12 +9908,12 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10014,12 +10014,12 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10067,12 +10067,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10120,12 +10120,12 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10173,12 +10173,12 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10226,12 +10226,12 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10332,12 +10332,12 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10389,12 +10389,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>15 days, 20:29:06.945779</t>
+          <t>14 days, 20:15:13.816727</t>
         </is>
       </c>
     </row>
@@ -10442,12 +10442,12 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10495,12 +10495,12 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10548,12 +10548,12 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10601,12 +10601,12 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10654,12 +10654,12 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10707,12 +10707,12 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10760,12 +10760,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10813,12 +10813,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10866,12 +10866,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10919,12 +10919,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -10972,12 +10972,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11025,12 +11025,12 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11078,12 +11078,12 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11131,12 +11131,12 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11184,12 +11184,12 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11290,12 +11290,12 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11343,12 +11343,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11396,12 +11396,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11449,12 +11449,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11502,12 +11502,12 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11555,12 +11555,12 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11608,12 +11608,12 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11661,12 +11661,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11714,12 +11714,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11767,12 +11767,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11820,12 +11820,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11873,12 +11873,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11926,12 +11926,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -11979,12 +11979,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12032,12 +12032,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12085,12 +12085,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12138,12 +12138,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12191,12 +12191,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12244,12 +12244,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12297,12 +12297,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12350,12 +12350,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12403,12 +12403,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12456,12 +12456,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12509,12 +12509,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12624,12 +12624,12 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>11 days, 2:44:06.944704</t>
+          <t>10 days, 2:30:13.815626</t>
         </is>
       </c>
     </row>
@@ -12686,12 +12686,12 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>11 days, 2:29:06.944672</t>
+          <t>10 days, 2:15:13.815593</t>
         </is>
       </c>
     </row>
@@ -12748,12 +12748,12 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>11 days, 2:29:06.944641</t>
+          <t>10 days, 2:15:13.815561</t>
         </is>
       </c>
     </row>
@@ -12806,12 +12806,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12859,12 +12859,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12912,12 +12912,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -12965,12 +12965,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -13018,12 +13018,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -13076,12 +13076,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -13129,12 +13129,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -13182,12 +13182,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -13235,12 +13235,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -13292,12 +13292,12 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>9 days, 19:29:06.944369</t>
+          <t>8 days, 19:15:13.815273</t>
         </is>
       </c>
     </row>
@@ -13345,12 +13345,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -13398,12 +13398,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -13451,12 +13451,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -13509,12 +13509,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -13571,12 +13571,12 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.944208</t>
+          <t>8 days, 18:30:13.815120</t>
         </is>
       </c>
     </row>
@@ -13633,12 +13633,12 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.944178</t>
+          <t>8 days, 18:30:13.815089</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.944150</t>
+          <t>8 days, 18:30:13.815060</t>
         </is>
       </c>
     </row>
@@ -13753,12 +13753,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -13811,12 +13811,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.944067</t>
+          <t>8 days, 18:30:13.814978</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -13989,12 +13989,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -14047,12 +14047,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -14105,12 +14105,12 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -14167,12 +14167,12 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.943935</t>
+          <t>8 days, 18:30:13.814842</t>
         </is>
       </c>
     </row>
@@ -14225,12 +14225,12 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -14283,12 +14283,12 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -14341,12 +14341,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -14403,12 +14403,12 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.943830</t>
+          <t>8 days, 18:30:13.814736</t>
         </is>
       </c>
     </row>
@@ -14461,12 +14461,12 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -14519,12 +14519,12 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -14577,12 +14577,12 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -14639,12 +14639,12 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.943733</t>
+          <t>8 days, 18:30:13.814634</t>
         </is>
       </c>
     </row>
@@ -14701,12 +14701,12 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.943705</t>
+          <t>8 days, 18:30:13.814606</t>
         </is>
       </c>
     </row>
@@ -14763,12 +14763,12 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.943678</t>
+          <t>8 days, 18:30:13.814576</t>
         </is>
       </c>
     </row>
@@ -14821,12 +14821,12 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -14879,12 +14879,12 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -14941,12 +14941,12 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.943602</t>
+          <t>8 days, 18:30:13.814499</t>
         </is>
       </c>
     </row>
@@ -14999,12 +14999,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -15061,12 +15061,12 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.943548</t>
+          <t>8 days, 18:30:13.814446</t>
         </is>
       </c>
     </row>
@@ -15119,12 +15119,12 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -15177,12 +15177,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -15235,12 +15235,12 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -15293,12 +15293,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -15351,12 +15351,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -15409,12 +15409,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -15467,12 +15467,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -15525,12 +15525,12 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -15583,12 +15583,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -15645,12 +15645,12 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.943291</t>
+          <t>8 days, 18:30:13.814182</t>
         </is>
       </c>
     </row>
@@ -15707,12 +15707,12 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.943263</t>
+          <t>8 days, 18:30:13.814154</t>
         </is>
       </c>
     </row>
@@ -15765,12 +15765,12 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -15823,12 +15823,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -15885,12 +15885,12 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.943177</t>
+          <t>8 days, 18:30:13.814070</t>
         </is>
       </c>
     </row>
@@ -15947,12 +15947,12 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.943147</t>
+          <t>8 days, 18:30:13.814039</t>
         </is>
       </c>
     </row>
@@ -16005,12 +16005,12 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -16067,12 +16067,12 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.943095</t>
+          <t>8 days, 18:30:13.813988</t>
         </is>
       </c>
     </row>
@@ -16125,12 +16125,12 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -16183,12 +16183,12 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -16245,12 +16245,12 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.943021</t>
+          <t>8 days, 18:30:13.813915</t>
         </is>
       </c>
     </row>
@@ -16303,12 +16303,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -16361,12 +16361,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -16419,12 +16419,12 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -16477,12 +16477,12 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -16535,12 +16535,12 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -16593,12 +16593,12 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -16651,12 +16651,12 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -16709,12 +16709,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -16771,12 +16771,12 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942803</t>
+          <t>8 days, 18:30:13.813694</t>
         </is>
       </c>
     </row>
@@ -16833,12 +16833,12 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942775</t>
+          <t>8 days, 18:30:13.813665</t>
         </is>
       </c>
     </row>
@@ -16891,12 +16891,12 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -16949,12 +16949,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -17011,12 +17011,12 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942699</t>
+          <t>8 days, 18:30:13.813588</t>
         </is>
       </c>
     </row>
@@ -17073,12 +17073,12 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942670</t>
+          <t>8 days, 18:30:13.813560</t>
         </is>
       </c>
     </row>
@@ -17135,12 +17135,12 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942642</t>
+          <t>8 days, 18:30:13.813532</t>
         </is>
       </c>
     </row>
@@ -17193,12 +17193,12 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -17255,12 +17255,12 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942591</t>
+          <t>8 days, 18:30:13.813480</t>
         </is>
       </c>
     </row>
@@ -17317,12 +17317,12 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942562</t>
+          <t>8 days, 18:30:13.813452</t>
         </is>
       </c>
     </row>
@@ -17375,12 +17375,12 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -17433,12 +17433,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -17495,12 +17495,12 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942489</t>
+          <t>8 days, 18:30:13.813377</t>
         </is>
       </c>
     </row>
@@ -17553,12 +17553,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -17611,12 +17611,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -17673,12 +17673,12 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942418</t>
+          <t>8 days, 18:30:13.813283</t>
         </is>
       </c>
     </row>
@@ -17735,12 +17735,12 @@
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942389</t>
+          <t>8 days, 18:30:13.813252</t>
         </is>
       </c>
     </row>
@@ -17793,12 +17793,12 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -17855,12 +17855,12 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942339</t>
+          <t>8 days, 18:30:13.813201</t>
         </is>
       </c>
     </row>
@@ -17913,12 +17913,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -17971,12 +17971,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -18033,12 +18033,12 @@
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942239</t>
+          <t>8 days, 18:30:13.813122</t>
         </is>
       </c>
     </row>
@@ -18095,12 +18095,12 @@
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942208</t>
+          <t>8 days, 18:30:13.813095</t>
         </is>
       </c>
     </row>
@@ -18153,12 +18153,12 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -18215,12 +18215,12 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942160</t>
+          <t>8 days, 18:30:13.813048</t>
         </is>
       </c>
     </row>
@@ -18277,12 +18277,12 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942131</t>
+          <t>8 days, 18:30:13.813020</t>
         </is>
       </c>
     </row>
@@ -18335,12 +18335,12 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -18397,12 +18397,12 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942077</t>
+          <t>8 days, 18:30:13.812967</t>
         </is>
       </c>
     </row>
@@ -18455,12 +18455,12 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -18517,12 +18517,12 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.942025</t>
+          <t>8 days, 18:30:13.812915</t>
         </is>
       </c>
     </row>
@@ -18575,12 +18575,12 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -18637,12 +18637,12 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.941977</t>
+          <t>8 days, 18:30:13.812867</t>
         </is>
       </c>
     </row>
@@ -18699,12 +18699,12 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>9 days, 18:44:06.941950</t>
+          <t>8 days, 18:30:13.812841</t>
         </is>
       </c>
     </row>
@@ -18757,12 +18757,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -18815,12 +18815,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -18873,12 +18873,12 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -18931,12 +18931,12 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -18989,12 +18989,12 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19047,12 +19047,12 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19105,12 +19105,12 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19163,12 +19163,12 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19221,12 +19221,12 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19279,12 +19279,12 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19337,12 +19337,12 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19395,12 +19395,12 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19453,12 +19453,12 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19511,12 +19511,12 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19569,12 +19569,12 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19627,12 +19627,12 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19685,12 +19685,12 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19743,12 +19743,12 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19801,12 +19801,12 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19859,12 +19859,12 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19917,12 +19917,12 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -19975,12 +19975,12 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20033,12 +20033,12 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20091,12 +20091,12 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20149,12 +20149,12 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20207,12 +20207,12 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -20262,19 +20262,15 @@
           <t>06/16/26 07:00 am</t>
         </is>
       </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>WASA02 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M352" t="inlineStr">
-        <is>
-          <t>9 days, 18:44:06.941221</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20327,12 +20323,12 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20385,12 +20381,12 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20443,12 +20439,12 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20501,12 +20497,12 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20559,12 +20555,12 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20617,12 +20613,12 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20675,12 +20671,12 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20702,7 +20698,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -20730,19 +20726,15 @@
           <t>06/16/26 07:00 am</t>
         </is>
       </c>
-      <c r="J360" t="inlineStr">
-        <is>
-          <t>WASA02 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>9 days, 18:44:06.941027</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20795,12 +20787,12 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20853,12 +20845,12 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20911,12 +20903,12 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -20969,12 +20961,12 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21026,12 +21018,12 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>9 days, 4:29:06.940913</t>
+          <t>8 days, 4:15:13.811807</t>
         </is>
       </c>
     </row>
@@ -21079,12 +21071,12 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21137,12 +21129,12 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21195,12 +21187,12 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21253,12 +21245,12 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21311,12 +21303,12 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21369,12 +21361,12 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21427,12 +21419,12 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21484,12 +21476,12 @@
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>8 days, 21:44:06.940697</t>
+          <t>7 days, 21:30:13.811588</t>
         </is>
       </c>
     </row>
@@ -21537,12 +21529,12 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21590,12 +21582,12 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21648,12 +21640,12 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21706,12 +21698,12 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21764,12 +21756,12 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21822,12 +21814,12 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21880,12 +21872,12 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -21937,12 +21929,12 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>6 days, 1:14:06.940476</t>
+          <t>5 days, 1:00:13.811361</t>
         </is>
       </c>
     </row>
@@ -21990,12 +21982,12 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22043,12 +22035,12 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22096,12 +22088,12 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22149,12 +22141,12 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22202,12 +22194,12 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22255,12 +22247,12 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22308,12 +22300,12 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22365,12 +22357,12 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>5 days, 21:44:06.940250</t>
+          <t>4 days, 21:30:13.811129</t>
         </is>
       </c>
     </row>
@@ -22418,12 +22410,12 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22471,12 +22463,12 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22524,12 +22516,12 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22577,12 +22569,12 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22630,12 +22622,12 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22683,12 +22675,12 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22736,12 +22728,12 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22789,12 +22781,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22842,12 +22834,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22895,12 +22887,12 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -22948,12 +22940,12 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23001,12 +22993,12 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23054,12 +23046,12 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23107,12 +23099,12 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23160,12 +23152,12 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23213,12 +23205,12 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23266,12 +23258,12 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23319,12 +23311,12 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23372,12 +23364,12 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23425,12 +23417,12 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23478,12 +23470,12 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23523,12 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23588,12 +23580,12 @@
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>5 days, 21:14:06.939670</t>
+          <t>4 days, 21:00:13.810543</t>
         </is>
       </c>
     </row>
@@ -23645,12 +23637,12 @@
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>5 days, 20:14:06.939645</t>
+          <t>4 days, 20:00:13.810518</t>
         </is>
       </c>
     </row>
@@ -23698,12 +23690,12 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23751,12 +23743,12 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23804,12 +23796,12 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23857,12 +23849,12 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23910,12 +23902,12 @@
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -23963,12 +23955,12 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24016,12 +24008,12 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24073,12 +24065,12 @@
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>5 days, 0:14:06.939438</t>
+          <t>4 days, 0:00:13.810286</t>
         </is>
       </c>
     </row>
@@ -24130,12 +24122,12 @@
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>5 days, 0:14:06.939405</t>
+          <t>4 days, 0:00:13.810252</t>
         </is>
       </c>
     </row>
@@ -24187,12 +24179,12 @@
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>5 days, 0:14:06.939369</t>
+          <t>4 days, 0:00:13.810217</t>
         </is>
       </c>
     </row>
@@ -24244,12 +24236,12 @@
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>5 days, 0:14:06.939336</t>
+          <t>4 days, 0:00:13.810181</t>
         </is>
       </c>
     </row>
@@ -24297,12 +24289,12 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24350,12 +24342,12 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24403,12 +24395,12 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24456,12 +24448,12 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24509,12 +24501,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24562,12 +24554,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24615,12 +24607,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24672,12 +24664,12 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>4 days, 22:59:06.939109</t>
+          <t>3 days, 22:45:13.809968</t>
         </is>
       </c>
     </row>
@@ -24725,12 +24717,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24778,12 +24770,12 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24831,12 +24823,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24884,12 +24876,12 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24937,12 +24929,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -24990,12 +24982,12 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25043,12 +25035,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25100,12 +25092,12 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>4 days, 18:44:06.938899</t>
+          <t>3 days, 18:30:13.809752</t>
         </is>
       </c>
     </row>
@@ -25157,12 +25149,12 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>4 days, 18:44:06.938861</t>
+          <t>3 days, 18:30:13.809714</t>
         </is>
       </c>
     </row>
@@ -25210,12 +25202,12 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25263,12 +25255,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25316,12 +25308,12 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25374,12 +25366,12 @@
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25432,12 +25424,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25490,12 +25482,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25548,12 +25540,12 @@
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25606,12 +25598,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25664,12 +25656,12 @@
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25722,12 +25714,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25780,12 +25772,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25838,12 +25830,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25896,12 +25888,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -25954,12 +25946,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26012,12 +26004,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26070,12 +26062,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26128,12 +26120,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26186,12 +26178,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26244,12 +26236,12 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26302,12 +26294,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26360,12 +26352,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26418,12 +26410,12 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26476,12 +26468,12 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26534,12 +26526,12 @@
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26592,12 +26584,12 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26650,12 +26642,12 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26708,12 +26700,12 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26766,12 +26758,12 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26824,12 +26816,12 @@
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26882,12 +26874,12 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26940,12 +26932,12 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -26998,12 +26990,12 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27056,12 +27048,12 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27114,12 +27106,12 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27172,12 +27164,12 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27230,12 +27222,12 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27288,12 +27280,12 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27346,12 +27338,12 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27404,12 +27396,12 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27462,12 +27454,12 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27520,12 +27512,12 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27573,12 +27565,12 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27626,12 +27618,12 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27679,12 +27671,12 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27737,12 +27729,12 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27794,12 +27786,12 @@
       </c>
       <c r="K487" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>3 days, 3:44:06.937622</t>
+          <t>2 days, 3:30:13.808430</t>
         </is>
       </c>
     </row>
@@ -27852,12 +27844,12 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27910,12 +27902,12 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -27968,12 +27960,12 @@
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28021,12 +28013,12 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28079,12 +28071,12 @@
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28137,12 +28129,12 @@
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28194,12 +28186,12 @@
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>3 days, 3:44:06.937441</t>
+          <t>2 days, 3:30:13.808235</t>
         </is>
       </c>
     </row>
@@ -28252,12 +28244,12 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28310,12 +28302,12 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28368,12 +28360,12 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28426,12 +28418,12 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28484,12 +28476,12 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28542,12 +28534,12 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28599,12 +28591,12 @@
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>3 days, 3:44:06.937253</t>
+          <t>2 days, 3:30:13.808057</t>
         </is>
       </c>
     </row>
@@ -28652,12 +28644,12 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28710,12 +28702,12 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28763,12 +28755,12 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28816,12 +28808,12 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28869,12 +28861,12 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28927,12 +28919,12 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -28980,12 +28972,12 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29033,12 +29025,12 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29091,12 +29083,12 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29149,12 +29141,12 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29207,12 +29199,12 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29265,12 +29257,12 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29323,12 +29315,12 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29381,12 +29373,12 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29439,12 +29431,12 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29497,12 +29489,12 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29555,12 +29547,12 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29613,12 +29605,12 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29671,12 +29663,12 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29729,12 +29721,12 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29787,12 +29779,12 @@
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29845,12 +29837,12 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29903,12 +29895,12 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -29961,12 +29953,12 @@
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -30019,12 +30011,12 @@
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -30077,12 +30069,12 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -30130,12 +30122,12 @@
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M528" t="inlineStr">
         <is>
-          <t>2 days, 4:44:06.936379</t>
+          <t>1 day, 4:30:13.807095</t>
         </is>
       </c>
     </row>
@@ -30183,12 +30175,12 @@
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M529" t="inlineStr">
         <is>
-          <t>2 days, 4:44:06.936346</t>
+          <t>1 day, 4:30:13.807059</t>
         </is>
       </c>
     </row>
@@ -30236,12 +30228,12 @@
       </c>
       <c r="K530" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M530" t="inlineStr">
         <is>
-          <t>2 days, 4:44:06.936312</t>
+          <t>1 day, 4:30:13.807022</t>
         </is>
       </c>
     </row>
@@ -30289,12 +30281,12 @@
       </c>
       <c r="K531" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M531" t="inlineStr">
         <is>
-          <t>2 days, 4:44:06.936271</t>
+          <t>1 day, 4:30:13.806990</t>
         </is>
       </c>
     </row>
@@ -30338,12 +30330,12 @@
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -30391,12 +30383,12 @@
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M533" t="inlineStr">
         <is>
-          <t>2 days, 4:44:06.936210</t>
+          <t>1 day, 4:30:13.806925</t>
         </is>
       </c>
     </row>
@@ -30448,12 +30440,12 @@
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M534" t="inlineStr">
         <is>
-          <t>2 days, 4:29:06.936183</t>
+          <t>1 day, 4:15:13.806898</t>
         </is>
       </c>
     </row>
@@ -30501,12 +30493,12 @@
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -30554,12 +30546,12 @@
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -30607,12 +30599,12 @@
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -30660,12 +30652,12 @@
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -30713,12 +30705,12 @@
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -30766,12 +30758,12 @@
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -30819,12 +30811,12 @@
       <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -30872,12 +30864,12 @@
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -30925,12 +30917,12 @@
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -30982,12 +30974,12 @@
       </c>
       <c r="K544" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M544" t="inlineStr">
         <is>
-          <t>2 days, 4:29:06.935944</t>
+          <t>1 day, 4:15:13.806646</t>
         </is>
       </c>
     </row>
@@ -31035,12 +31027,12 @@
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -31088,12 +31080,12 @@
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -31141,12 +31133,12 @@
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -31194,12 +31186,12 @@
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -31247,12 +31239,12 @@
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -31300,12 +31292,12 @@
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -31353,12 +31345,12 @@
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -31406,12 +31398,12 @@
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>
@@ -31459,12 +31451,12 @@
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>06/05/26 12:15 PM</t>
+          <t>06/06/26 12:29 PM</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -546,12 +546,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>23 days, 18:01:11.956280</t>
+          <t>22 days, 17:32:22.368210</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -652,12 +652,12 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 days, 23:31:11.956120</t>
+          <t>21 days, 23:02:22.368053</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 days, 23:31:11.956077</t>
+          <t>21 days, 23:02:22.367964</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22 days, 23:31:11.956040</t>
+          <t>21 days, 23:02:22.367917</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>22 days, 23:31:11.955962</t>
+          <t>21 days, 23:02:22.367880</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>22 days, 23:31:11.955922</t>
+          <t>21 days, 23:02:22.367841</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>22 days, 23:31:11.955887</t>
+          <t>21 days, 23:02:22.367805</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>22 days, 23:31:11.955852</t>
+          <t>21 days, 23:02:22.367768</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>22 days, 23:31:11.955818</t>
+          <t>21 days, 23:02:22.367735</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>22 days, 23:31:11.955783</t>
+          <t>21 days, 23:02:22.367699</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>22 days, 23:31:11.955749</t>
+          <t>21 days, 23:02:22.367665</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>22 days, 23:31:11.955713</t>
+          <t>21 days, 23:02:22.367631</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>22 days, 23:31:11.955680</t>
+          <t>21 days, 23:02:22.367599</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>22 days, 23:31:11.955647</t>
+          <t>21 days, 23:02:22.367567</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>19 days, 23:31:11.955511</t>
+          <t>18 days, 23:02:22.367422</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>19 days, 23:31:11.955476</t>
+          <t>18 days, 23:02:22.367387</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>19 days, 23:31:11.955437</t>
+          <t>18 days, 23:02:22.367349</t>
         </is>
       </c>
     </row>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>19 days, 23:31:11.955401</t>
+          <t>18 days, 23:02:22.367315</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>19 days, 23:31:11.955365</t>
+          <t>18 days, 23:02:22.367279</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>19 days, 23:31:11.955332</t>
+          <t>18 days, 23:02:22.367247</t>
         </is>
       </c>
     </row>
@@ -1963,12 +1963,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>19 days, 23:31:11.955300</t>
+          <t>18 days, 23:02:22.367212</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>19 days, 23:31:11.955269</t>
+          <t>18 days, 23:02:22.367179</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>19 days, 23:31:11.955236</t>
+          <t>18 days, 23:02:22.367147</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>19 days, 23:31:11.955206</t>
+          <t>18 days, 23:02:22.367116</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>19 days, 23:31:11.955176</t>
+          <t>18 days, 23:02:22.367086</t>
         </is>
       </c>
     </row>
@@ -2248,12 +2248,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>19 days, 23:31:11.955146</t>
+          <t>18 days, 23:02:22.367055</t>
         </is>
       </c>
     </row>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>19 days, 23:31:11.955113</t>
+          <t>18 days, 23:02:22.367025</t>
         </is>
       </c>
     </row>
@@ -2362,12 +2362,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.955073</t>
+          <t>18 days, 2:32:22.366958</t>
         </is>
       </c>
     </row>
@@ -2419,12 +2419,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.955013</t>
+          <t>18 days, 2:32:22.366916</t>
         </is>
       </c>
     </row>
@@ -2476,12 +2476,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954965</t>
+          <t>18 days, 2:32:22.366877</t>
         </is>
       </c>
     </row>
@@ -2533,12 +2533,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954925</t>
+          <t>18 days, 2:32:22.366839</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954886</t>
+          <t>18 days, 2:32:22.366801</t>
         </is>
       </c>
     </row>
@@ -2647,12 +2647,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954851</t>
+          <t>18 days, 2:32:22.366766</t>
         </is>
       </c>
     </row>
@@ -2704,12 +2704,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954812</t>
+          <t>18 days, 2:32:22.366726</t>
         </is>
       </c>
     </row>
@@ -2761,12 +2761,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954773</t>
+          <t>18 days, 2:32:22.366688</t>
         </is>
       </c>
     </row>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954736</t>
+          <t>18 days, 2:32:22.366653</t>
         </is>
       </c>
     </row>
@@ -2875,12 +2875,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954698</t>
+          <t>18 days, 2:32:22.366615</t>
         </is>
       </c>
     </row>
@@ -2932,12 +2932,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954661</t>
+          <t>18 days, 2:32:22.366578</t>
         </is>
       </c>
     </row>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954624</t>
+          <t>18 days, 2:32:22.366541</t>
         </is>
       </c>
     </row>
@@ -3046,12 +3046,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954586</t>
+          <t>18 days, 2:32:22.366504</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954548</t>
+          <t>18 days, 2:32:22.366467</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954511</t>
+          <t>18 days, 2:32:22.366430</t>
         </is>
       </c>
     </row>
@@ -3217,12 +3217,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954472</t>
+          <t>18 days, 2:32:22.366384</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954434</t>
+          <t>18 days, 2:32:22.366345</t>
         </is>
       </c>
     </row>
@@ -3331,12 +3331,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954395</t>
+          <t>18 days, 2:32:22.366302</t>
         </is>
       </c>
     </row>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954354</t>
+          <t>18 days, 2:32:22.366264</t>
         </is>
       </c>
     </row>
@@ -3445,12 +3445,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954315</t>
+          <t>18 days, 2:32:22.366227</t>
         </is>
       </c>
     </row>
@@ -3502,12 +3502,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>19 days, 3:01:11.954276</t>
+          <t>18 days, 2:32:22.366190</t>
         </is>
       </c>
     </row>
@@ -3559,12 +3559,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>19 days, 0:16:11.954238</t>
+          <t>17 days, 23:47:22.366151</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>19 days, 0:16:11.954199</t>
+          <t>17 days, 23:47:22.366112</t>
         </is>
       </c>
     </row>
@@ -3673,12 +3673,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>19 days, 0:16:11.954162</t>
+          <t>17 days, 23:47:22.366074</t>
         </is>
       </c>
     </row>
@@ -3730,12 +3730,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>19 days, 0:16:11.954124</t>
+          <t>17 days, 23:47:22.366035</t>
         </is>
       </c>
     </row>
@@ -3787,12 +3787,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>19 days, 0:16:11.954092</t>
+          <t>17 days, 23:47:22.365979</t>
         </is>
       </c>
     </row>
@@ -3844,12 +3844,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>19 days, 0:01:11.954055</t>
+          <t>17 days, 23:32:22.365939</t>
         </is>
       </c>
     </row>
@@ -3901,12 +3901,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>19 days, 0:01:11.953996</t>
+          <t>17 days, 23:32:22.365898</t>
         </is>
       </c>
     </row>
@@ -3958,12 +3958,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953952</t>
+          <t>17 days, 23:17:22.365858</t>
         </is>
       </c>
     </row>
@@ -4015,12 +4015,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953914</t>
+          <t>17 days, 23:17:22.365818</t>
         </is>
       </c>
     </row>
@@ -4072,12 +4072,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953873</t>
+          <t>17 days, 23:17:22.365778</t>
         </is>
       </c>
     </row>
@@ -4129,12 +4129,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953835</t>
+          <t>17 days, 23:17:22.365740</t>
         </is>
       </c>
     </row>
@@ -4186,12 +4186,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953798</t>
+          <t>17 days, 23:17:22.365702</t>
         </is>
       </c>
     </row>
@@ -4243,12 +4243,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953759</t>
+          <t>17 days, 23:17:22.365666</t>
         </is>
       </c>
     </row>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953722</t>
+          <t>17 days, 23:17:22.365629</t>
         </is>
       </c>
     </row>
@@ -4357,12 +4357,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953686</t>
+          <t>17 days, 23:17:22.365593</t>
         </is>
       </c>
     </row>
@@ -4414,12 +4414,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953648</t>
+          <t>17 days, 23:17:22.365558</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4471,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953610</t>
+          <t>17 days, 23:17:22.365518</t>
         </is>
       </c>
     </row>
@@ -4528,12 +4528,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953574</t>
+          <t>17 days, 23:17:22.365484</t>
         </is>
       </c>
     </row>
@@ -4585,12 +4585,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953535</t>
+          <t>17 days, 23:17:22.365446</t>
         </is>
       </c>
     </row>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953497</t>
+          <t>17 days, 23:17:22.365410</t>
         </is>
       </c>
     </row>
@@ -4699,12 +4699,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953458</t>
+          <t>17 days, 23:17:22.365373</t>
         </is>
       </c>
     </row>
@@ -4756,12 +4756,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953419</t>
+          <t>17 days, 23:17:22.365335</t>
         </is>
       </c>
     </row>
@@ -4813,12 +4813,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953379</t>
+          <t>17 days, 23:17:22.365295</t>
         </is>
       </c>
     </row>
@@ -4870,12 +4870,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953341</t>
+          <t>17 days, 23:17:22.365258</t>
         </is>
       </c>
     </row>
@@ -4927,12 +4927,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953303</t>
+          <t>17 days, 23:17:22.365219</t>
         </is>
       </c>
     </row>
@@ -4984,12 +4984,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953264</t>
+          <t>17 days, 23:17:22.365180</t>
         </is>
       </c>
     </row>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953226</t>
+          <t>17 days, 23:17:22.365139</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953188</t>
+          <t>17 days, 23:17:22.365103</t>
         </is>
       </c>
     </row>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953151</t>
+          <t>17 days, 23:17:22.365067</t>
         </is>
       </c>
     </row>
@@ -5212,12 +5212,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953114</t>
+          <t>17 days, 23:17:22.365031</t>
         </is>
       </c>
     </row>
@@ -5269,12 +5269,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953077</t>
+          <t>17 days, 23:17:22.364974</t>
         </is>
       </c>
     </row>
@@ -5326,12 +5326,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.953040</t>
+          <t>17 days, 23:17:22.364932</t>
         </is>
       </c>
     </row>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.952978</t>
+          <t>17 days, 23:17:22.364895</t>
         </is>
       </c>
     </row>
@@ -5440,12 +5440,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.952941</t>
+          <t>17 days, 23:17:22.364862</t>
         </is>
       </c>
     </row>
@@ -5497,12 +5497,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.952904</t>
+          <t>17 days, 23:17:22.364826</t>
         </is>
       </c>
     </row>
@@ -5554,12 +5554,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.952868</t>
+          <t>17 days, 23:17:22.364792</t>
         </is>
       </c>
     </row>
@@ -5611,12 +5611,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.952828</t>
+          <t>17 days, 23:17:22.364750</t>
         </is>
       </c>
     </row>
@@ -5668,12 +5668,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>18 days, 23:46:11.952791</t>
+          <t>17 days, 23:17:22.364717</t>
         </is>
       </c>
     </row>
@@ -5725,12 +5725,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952756</t>
+          <t>17 days, 23:02:22.364684</t>
         </is>
       </c>
     </row>
@@ -5782,12 +5782,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952723</t>
+          <t>17 days, 23:02:22.364653</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952689</t>
+          <t>17 days, 23:02:22.364621</t>
         </is>
       </c>
     </row>
@@ -5896,12 +5896,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952645</t>
+          <t>17 days, 23:02:22.364585</t>
         </is>
       </c>
     </row>
@@ -5953,12 +5953,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952606</t>
+          <t>17 days, 23:02:22.364552</t>
         </is>
       </c>
     </row>
@@ -6010,12 +6010,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952572</t>
+          <t>17 days, 23:02:22.364520</t>
         </is>
       </c>
     </row>
@@ -6067,12 +6067,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952537</t>
+          <t>17 days, 23:02:22.364488</t>
         </is>
       </c>
     </row>
@@ -6124,12 +6124,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952503</t>
+          <t>17 days, 23:02:22.364456</t>
         </is>
       </c>
     </row>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952471</t>
+          <t>17 days, 23:02:22.364421</t>
         </is>
       </c>
     </row>
@@ -6238,12 +6238,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952437</t>
+          <t>17 days, 23:02:22.364390</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952403</t>
+          <t>17 days, 23:02:22.364359</t>
         </is>
       </c>
     </row>
@@ -6352,12 +6352,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952371</t>
+          <t>17 days, 23:02:22.364323</t>
         </is>
       </c>
     </row>
@@ -6409,12 +6409,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952339</t>
+          <t>17 days, 23:02:22.364293</t>
         </is>
       </c>
     </row>
@@ -6461,17 +6461,17 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>PEPCODC - Not complete/In progress &amp; WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC - Not complete/In progress &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952298</t>
+          <t>17 days, 23:02:22.364256</t>
         </is>
       </c>
     </row>
@@ -6518,17 +6518,17 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952257</t>
+          <t>17 days, 23:02:22.364217</t>
         </is>
       </c>
     </row>
@@ -6575,17 +6575,17 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>PEPCODC - Not complete/In progress &amp; WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC - Not complete/In progress &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952217</t>
+          <t>17 days, 23:02:22.364181</t>
         </is>
       </c>
     </row>
@@ -6632,17 +6632,17 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952177</t>
+          <t>17 days, 23:02:22.364143</t>
         </is>
       </c>
     </row>
@@ -6689,17 +6689,17 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952137</t>
+          <t>17 days, 23:02:22.364104</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952098</t>
+          <t>17 days, 23:02:22.364061</t>
         </is>
       </c>
     </row>
@@ -6803,17 +6803,17 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.952057</t>
+          <t>17 days, 23:02:22.363988</t>
         </is>
       </c>
     </row>
@@ -6860,17 +6860,17 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.951986</t>
+          <t>17 days, 23:02:22.363936</t>
         </is>
       </c>
     </row>
@@ -6922,12 +6922,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.951941</t>
+          <t>17 days, 23:02:22.363896</t>
         </is>
       </c>
     </row>
@@ -6974,17 +6974,17 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>18 days, 23:31:11.951900</t>
+          <t>17 days, 23:02:22.363853</t>
         </is>
       </c>
     </row>
@@ -7036,12 +7036,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>18 days, 23:16:11.951857</t>
+          <t>17 days, 22:47:22.363810</t>
         </is>
       </c>
     </row>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>18 days, 23:16:11.951817</t>
+          <t>17 days, 22:47:22.363772</t>
         </is>
       </c>
     </row>
@@ -7150,12 +7150,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>18 days, 23:16:11.951778</t>
+          <t>17 days, 22:47:22.363736</t>
         </is>
       </c>
     </row>
@@ -7207,12 +7207,12 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>18 days, 23:16:11.951738</t>
+          <t>17 days, 22:47:22.363696</t>
         </is>
       </c>
     </row>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>18 days, 23:16:11.951699</t>
+          <t>17 days, 22:47:22.363659</t>
         </is>
       </c>
     </row>
@@ -7321,12 +7321,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>18 days, 23:16:11.951657</t>
+          <t>17 days, 22:47:22.363615</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>18 days, 23:16:11.951612</t>
+          <t>17 days, 22:47:22.363573</t>
         </is>
       </c>
     </row>
@@ -7435,12 +7435,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>18 days, 23:16:11.951570</t>
+          <t>17 days, 22:47:22.363533</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>18 days, 23:16:11.951525</t>
+          <t>17 days, 22:47:22.363489</t>
         </is>
       </c>
     </row>
@@ -7549,12 +7549,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>18 days, 23:16:11.951480</t>
+          <t>17 days, 22:47:22.363446</t>
         </is>
       </c>
     </row>
@@ -7606,12 +7606,12 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>18 days, 23:16:11.951437</t>
+          <t>17 days, 22:47:22.363404</t>
         </is>
       </c>
     </row>
@@ -7663,12 +7663,12 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>18 days, 23:16:11.951393</t>
+          <t>17 days, 22:47:22.363361</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>18 days, 23:01:11.951355</t>
+          <t>17 days, 22:32:22.363325</t>
         </is>
       </c>
     </row>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>18 days, 23:01:11.951318</t>
+          <t>17 days, 22:32:22.363290</t>
         </is>
       </c>
     </row>
@@ -7829,17 +7829,17 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>18 days, 23:01:11.951284</t>
+          <t>17 days, 22:32:22.363258</t>
         </is>
       </c>
     </row>
@@ -7891,12 +7891,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>18 days, 22:46:11.951246</t>
+          <t>17 days, 22:17:22.363217</t>
         </is>
       </c>
     </row>
@@ -7949,12 +7949,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8007,12 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8123,12 +8123,12 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8181,12 +8181,12 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8297,12 +8297,12 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8413,12 +8413,12 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8471,12 +8471,12 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8529,12 +8529,12 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8587,12 +8587,12 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8645,12 +8645,12 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8761,12 +8761,12 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8877,12 +8877,12 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8935,12 +8935,12 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -8993,12 +8993,12 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -9051,12 +9051,12 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -9109,12 +9109,12 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -9220,12 +9220,12 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -9277,12 +9277,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>17 days, 22:46:11.950484</t>
+          <t>16 days, 22:17:22.362464</t>
         </is>
       </c>
     </row>
@@ -9330,12 +9330,12 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -9383,12 +9383,12 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>17 days, 18:01:11.950381</t>
+          <t>16 days, 17:32:22.362367</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>17 days, 18:01:11.950345</t>
+          <t>16 days, 17:32:22.362331</t>
         </is>
       </c>
     </row>
@@ -9542,12 +9542,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>17 days, 18:01:11.950306</t>
+          <t>16 days, 17:32:22.362295</t>
         </is>
       </c>
     </row>
@@ -9595,12 +9595,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>17 days, 18:01:11.950271</t>
+          <t>16 days, 17:32:22.362256</t>
         </is>
       </c>
     </row>
@@ -9648,12 +9648,12 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>17 days, 18:01:11.950227</t>
+          <t>16 days, 17:32:22.362214</t>
         </is>
       </c>
     </row>
@@ -9705,12 +9705,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>17 days, 3:16:11.950185</t>
+          <t>16 days, 2:47:22.362174</t>
         </is>
       </c>
     </row>
@@ -9758,12 +9758,12 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -9815,12 +9815,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>16 days, 23:01:11.950107</t>
+          <t>15 days, 22:32:22.362101</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -9925,12 +9925,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>16 days, 20:01:11.950014</t>
+          <t>15 days, 19:32:22.362030</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>16 days, 20:01:11.949972</t>
+          <t>15 days, 19:32:22.361951</t>
         </is>
       </c>
     </row>
@@ -10040,12 +10040,12 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10146,12 +10146,12 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10199,12 +10199,12 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10252,12 +10252,12 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10305,12 +10305,12 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10363,12 +10363,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10421,12 +10421,12 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10479,12 +10479,12 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10537,12 +10537,12 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10590,12 +10590,12 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10647,12 +10647,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>16 days, 3:01:11.949569</t>
+          <t>15 days, 2:32:22.361559</t>
         </is>
       </c>
     </row>
@@ -10700,12 +10700,12 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10753,12 +10753,12 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10806,12 +10806,12 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10859,12 +10859,12 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10912,12 +10912,12 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -10965,12 +10965,12 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11018,12 +11018,12 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11071,12 +11071,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11177,12 +11177,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11230,12 +11230,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11283,12 +11283,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11336,12 +11336,12 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11389,12 +11389,12 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11442,12 +11442,12 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11495,12 +11495,12 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11548,12 +11548,12 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11601,12 +11601,12 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11654,12 +11654,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11707,12 +11707,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11765,12 +11765,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11823,12 +11823,12 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11876,12 +11876,12 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11929,12 +11929,12 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -11982,12 +11982,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12035,12 +12035,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12088,12 +12088,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12141,12 +12141,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12194,12 +12194,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12247,12 +12247,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12300,12 +12300,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12406,12 +12406,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12459,12 +12459,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12512,12 +12512,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12565,12 +12565,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12618,12 +12618,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12671,12 +12671,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12724,12 +12724,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12777,12 +12777,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12883,12 +12883,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12936,12 +12936,12 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -12989,12 +12989,12 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13042,12 +13042,12 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13095,12 +13095,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13148,12 +13148,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13201,12 +13201,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13254,12 +13254,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13307,12 +13307,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13360,12 +13360,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13413,12 +13413,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13466,12 +13466,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13519,12 +13519,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13572,12 +13572,12 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13625,12 +13625,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13678,12 +13678,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13731,12 +13731,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13784,12 +13784,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13837,12 +13837,12 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13890,12 +13890,12 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13943,12 +13943,12 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -13996,12 +13996,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14049,12 +14049,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14102,12 +14102,12 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14155,12 +14155,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14208,12 +14208,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14261,12 +14261,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14314,12 +14314,12 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14367,12 +14367,12 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14420,12 +14420,12 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14473,12 +14473,12 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14526,12 +14526,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14579,12 +14579,12 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14632,12 +14632,12 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14685,12 +14685,12 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14738,12 +14738,12 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14791,12 +14791,12 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14897,12 +14897,12 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -14950,12 +14950,12 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15003,12 +15003,12 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15056,12 +15056,12 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15109,12 +15109,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15162,12 +15162,12 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15215,12 +15215,12 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15268,12 +15268,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15321,12 +15321,12 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15374,12 +15374,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15427,12 +15427,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15480,12 +15480,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15533,12 +15533,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15586,12 +15586,12 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15692,12 +15692,12 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15745,12 +15745,12 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15798,12 +15798,12 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15851,12 +15851,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15904,12 +15904,12 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -15957,12 +15957,12 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16015,12 +16015,12 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16073,12 +16073,12 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16135,12 +16135,12 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>15 days, 22:16:11.946557</t>
+          <t>14 days, 21:47:22.358587</t>
         </is>
       </c>
     </row>
@@ -16188,12 +16188,12 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16241,12 +16241,12 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16294,12 +16294,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16347,12 +16347,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16400,12 +16400,12 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16453,12 +16453,12 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16506,12 +16506,12 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16559,12 +16559,12 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16612,12 +16612,12 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16665,12 +16665,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16718,12 +16718,12 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16771,12 +16771,12 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16824,12 +16824,12 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16877,12 +16877,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16930,12 +16930,12 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -16983,12 +16983,12 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -17032,12 +17032,12 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -17085,12 +17085,12 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -17143,12 +17143,12 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -17205,12 +17205,12 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>11 days, 22:31:11.945864</t>
+          <t>10 days, 22:02:22.357914</t>
         </is>
       </c>
     </row>
@@ -17267,12 +17267,12 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>11 days, 22:31:11.945820</t>
+          <t>10 days, 22:02:22.357871</t>
         </is>
       </c>
     </row>
@@ -17325,12 +17325,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -17378,12 +17378,12 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -17431,12 +17431,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -17484,12 +17484,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -17537,12 +17537,12 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -17590,12 +17590,12 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -17647,12 +17647,12 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>11 days, 0:46:11.945603</t>
+          <t>10 days, 0:17:22.357653</t>
         </is>
       </c>
     </row>
@@ -17704,12 +17704,12 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>11 days, 0:46:11.945563</t>
+          <t>10 days, 0:17:22.357611</t>
         </is>
       </c>
     </row>
@@ -17761,12 +17761,12 @@
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>11 days, 0:46:11.945528</t>
+          <t>10 days, 0:17:22.357579</t>
         </is>
       </c>
     </row>
@@ -17819,12 +17819,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -17877,12 +17877,12 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -17935,12 +17935,12 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -17993,12 +17993,12 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -18051,12 +18051,12 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -18109,12 +18109,12 @@
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -18167,12 +18167,12 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -18225,12 +18225,12 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -18283,12 +18283,12 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -18341,12 +18341,12 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -18399,12 +18399,12 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -18452,12 +18452,12 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -18510,12 +18510,12 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -18568,12 +18568,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -18626,12 +18626,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -18683,12 +18683,12 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>10 days, 18:01:11.945002</t>
+          <t>9 days, 17:32:22.357084</t>
         </is>
       </c>
     </row>
@@ -18736,12 +18736,12 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -18793,12 +18793,12 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944929</t>
+          <t>8 days, 21:02:22.356989</t>
         </is>
       </c>
     </row>
@@ -18855,12 +18855,12 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944893</t>
+          <t>8 days, 21:02:22.356952</t>
         </is>
       </c>
     </row>
@@ -18912,12 +18912,12 @@
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944852</t>
+          <t>8 days, 21:02:22.356909</t>
         </is>
       </c>
     </row>
@@ -18974,12 +18974,12 @@
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944817</t>
+          <t>8 days, 21:02:22.356875</t>
         </is>
       </c>
     </row>
@@ -19036,12 +19036,12 @@
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944786</t>
+          <t>8 days, 21:02:22.356844</t>
         </is>
       </c>
     </row>
@@ -19098,12 +19098,12 @@
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944753</t>
+          <t>8 days, 21:02:22.356812</t>
         </is>
       </c>
     </row>
@@ -19160,12 +19160,12 @@
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944719</t>
+          <t>8 days, 21:02:22.356781</t>
         </is>
       </c>
     </row>
@@ -19217,12 +19217,12 @@
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944688</t>
+          <t>8 days, 21:02:22.356753</t>
         </is>
       </c>
     </row>
@@ -19274,12 +19274,12 @@
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944656</t>
+          <t>8 days, 21:02:22.356722</t>
         </is>
       </c>
     </row>
@@ -19336,12 +19336,12 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944621</t>
+          <t>8 days, 21:02:22.356689</t>
         </is>
       </c>
     </row>
@@ -19393,12 +19393,12 @@
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944589</t>
+          <t>8 days, 21:02:22.356654</t>
         </is>
       </c>
     </row>
@@ -19455,12 +19455,12 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944554</t>
+          <t>8 days, 21:02:22.356621</t>
         </is>
       </c>
     </row>
@@ -19512,12 +19512,12 @@
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944523</t>
+          <t>8 days, 21:02:22.356592</t>
         </is>
       </c>
     </row>
@@ -19569,12 +19569,12 @@
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944488</t>
+          <t>8 days, 21:02:22.356558</t>
         </is>
       </c>
     </row>
@@ -19622,12 +19622,12 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -19679,12 +19679,12 @@
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944420</t>
+          <t>8 days, 21:02:22.356492</t>
         </is>
       </c>
     </row>
@@ -19741,12 +19741,12 @@
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944385</t>
+          <t>8 days, 21:02:22.356458</t>
         </is>
       </c>
     </row>
@@ -19803,12 +19803,12 @@
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944351</t>
+          <t>8 days, 21:02:22.356426</t>
         </is>
       </c>
     </row>
@@ -19860,12 +19860,12 @@
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944320</t>
+          <t>8 days, 21:02:22.356397</t>
         </is>
       </c>
     </row>
@@ -19922,12 +19922,12 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944287</t>
+          <t>8 days, 21:02:22.356366</t>
         </is>
       </c>
     </row>
@@ -19979,12 +19979,12 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944252</t>
+          <t>8 days, 21:02:22.356326</t>
         </is>
       </c>
     </row>
@@ -20041,12 +20041,12 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944219</t>
+          <t>8 days, 21:02:22.356294</t>
         </is>
       </c>
     </row>
@@ -20103,12 +20103,12 @@
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944184</t>
+          <t>8 days, 21:02:22.356261</t>
         </is>
       </c>
     </row>
@@ -20165,12 +20165,12 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944151</t>
+          <t>8 days, 21:02:22.356228</t>
         </is>
       </c>
     </row>
@@ -20227,12 +20227,12 @@
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944119</t>
+          <t>8 days, 21:02:22.356195</t>
         </is>
       </c>
     </row>
@@ -20289,12 +20289,12 @@
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944086</t>
+          <t>8 days, 21:02:22.356163</t>
         </is>
       </c>
     </row>
@@ -20346,12 +20346,12 @@
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944052</t>
+          <t>8 days, 21:02:22.356128</t>
         </is>
       </c>
     </row>
@@ -20408,12 +20408,12 @@
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.944000</t>
+          <t>8 days, 21:02:22.356098</t>
         </is>
       </c>
     </row>
@@ -20470,12 +20470,12 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943963</t>
+          <t>8 days, 21:02:22.356066</t>
         </is>
       </c>
     </row>
@@ -20527,12 +20527,12 @@
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943931</t>
+          <t>8 days, 21:02:22.356037</t>
         </is>
       </c>
     </row>
@@ -20580,12 +20580,12 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -20637,12 +20637,12 @@
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943864</t>
+          <t>8 days, 21:02:22.355939</t>
         </is>
       </c>
     </row>
@@ -20699,12 +20699,12 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943831</t>
+          <t>8 days, 21:02:22.355906</t>
         </is>
       </c>
     </row>
@@ -20756,12 +20756,12 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943801</t>
+          <t>8 days, 21:02:22.355876</t>
         </is>
       </c>
     </row>
@@ -20818,12 +20818,12 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943768</t>
+          <t>8 days, 21:02:22.355844</t>
         </is>
       </c>
     </row>
@@ -20880,12 +20880,12 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943737</t>
+          <t>8 days, 21:02:22.355813</t>
         </is>
       </c>
     </row>
@@ -20942,12 +20942,12 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943707</t>
+          <t>8 days, 21:02:22.355783</t>
         </is>
       </c>
     </row>
@@ -20999,12 +20999,12 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943677</t>
+          <t>8 days, 21:02:22.355753</t>
         </is>
       </c>
     </row>
@@ -21061,12 +21061,12 @@
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943645</t>
+          <t>8 days, 21:02:22.355723</t>
         </is>
       </c>
     </row>
@@ -21118,12 +21118,12 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943615</t>
+          <t>8 days, 21:02:22.355693</t>
         </is>
       </c>
     </row>
@@ -21175,12 +21175,12 @@
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943585</t>
+          <t>8 days, 21:02:22.355659</t>
         </is>
       </c>
     </row>
@@ -21232,12 +21232,12 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943553</t>
+          <t>8 days, 21:02:22.355628</t>
         </is>
       </c>
     </row>
@@ -21294,12 +21294,12 @@
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943521</t>
+          <t>8 days, 21:02:22.355597</t>
         </is>
       </c>
     </row>
@@ -21351,12 +21351,12 @@
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943490</t>
+          <t>8 days, 21:02:22.355566</t>
         </is>
       </c>
     </row>
@@ -21413,12 +21413,12 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943456</t>
+          <t>8 days, 21:02:22.355535</t>
         </is>
       </c>
     </row>
@@ -21475,12 +21475,12 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943425</t>
+          <t>8 days, 21:02:22.355505</t>
         </is>
       </c>
     </row>
@@ -21537,12 +21537,12 @@
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943395</t>
+          <t>8 days, 21:02:22.355475</t>
         </is>
       </c>
     </row>
@@ -21594,12 +21594,12 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943361</t>
+          <t>8 days, 21:02:22.355442</t>
         </is>
       </c>
     </row>
@@ -21656,12 +21656,12 @@
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943329</t>
+          <t>8 days, 21:02:22.355413</t>
         </is>
       </c>
     </row>
@@ -21718,12 +21718,12 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>9 days, 21:31:11.943289</t>
+          <t>8 days, 21:02:22.355382</t>
         </is>
       </c>
     </row>
@@ -21775,12 +21775,12 @@
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.943254</t>
+          <t>8 days, 20:47:22.355344</t>
         </is>
       </c>
     </row>
@@ -21832,12 +21832,12 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.943219</t>
+          <t>8 days, 20:47:22.355311</t>
         </is>
       </c>
     </row>
@@ -21894,12 +21894,12 @@
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.943185</t>
+          <t>8 days, 20:47:22.355278</t>
         </is>
       </c>
     </row>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.943154</t>
+          <t>8 days, 20:47:22.355249</t>
         </is>
       </c>
     </row>
@@ -22018,12 +22018,12 @@
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.943122</t>
+          <t>8 days, 20:47:22.355218</t>
         </is>
       </c>
     </row>
@@ -22080,12 +22080,12 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.943090</t>
+          <t>8 days, 20:47:22.355187</t>
         </is>
       </c>
     </row>
@@ -22133,12 +22133,12 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -22195,12 +22195,12 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.943009</t>
+          <t>8 days, 20:47:22.355127</t>
         </is>
       </c>
     </row>
@@ -22257,12 +22257,12 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942966</t>
+          <t>8 days, 20:47:22.355083</t>
         </is>
       </c>
     </row>
@@ -22314,12 +22314,12 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942931</t>
+          <t>8 days, 20:47:22.355049</t>
         </is>
       </c>
     </row>
@@ -22376,12 +22376,12 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942900</t>
+          <t>8 days, 20:47:22.354995</t>
         </is>
       </c>
     </row>
@@ -22438,12 +22438,12 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942865</t>
+          <t>8 days, 20:47:22.354953</t>
         </is>
       </c>
     </row>
@@ -22500,12 +22500,12 @@
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942833</t>
+          <t>8 days, 20:47:22.354919</t>
         </is>
       </c>
     </row>
@@ -22562,12 +22562,12 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942801</t>
+          <t>8 days, 20:47:22.354887</t>
         </is>
       </c>
     </row>
@@ -22619,12 +22619,12 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942770</t>
+          <t>8 days, 20:47:22.354858</t>
         </is>
       </c>
     </row>
@@ -22672,12 +22672,12 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -22734,12 +22734,12 @@
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942700</t>
+          <t>8 days, 20:47:22.354790</t>
         </is>
       </c>
     </row>
@@ -22787,12 +22787,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -22849,12 +22849,12 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942629</t>
+          <t>8 days, 20:47:22.354719</t>
         </is>
       </c>
     </row>
@@ -22906,12 +22906,12 @@
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942592</t>
+          <t>8 days, 20:47:22.354682</t>
         </is>
       </c>
     </row>
@@ -22968,12 +22968,12 @@
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942559</t>
+          <t>8 days, 20:47:22.354645</t>
         </is>
       </c>
     </row>
@@ -23025,12 +23025,12 @@
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942526</t>
+          <t>8 days, 20:47:22.354615</t>
         </is>
       </c>
     </row>
@@ -23082,12 +23082,12 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942490</t>
+          <t>8 days, 20:47:22.354580</t>
         </is>
       </c>
     </row>
@@ -23144,12 +23144,12 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942457</t>
+          <t>8 days, 20:47:22.354548</t>
         </is>
       </c>
     </row>
@@ -23206,12 +23206,12 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942423</t>
+          <t>8 days, 20:47:22.354515</t>
         </is>
       </c>
     </row>
@@ -23268,12 +23268,12 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942388</t>
+          <t>8 days, 20:47:22.354480</t>
         </is>
       </c>
     </row>
@@ -23330,12 +23330,12 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942357</t>
+          <t>8 days, 20:47:22.354450</t>
         </is>
       </c>
     </row>
@@ -23387,12 +23387,12 @@
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942326</t>
+          <t>8 days, 20:47:22.354419</t>
         </is>
       </c>
     </row>
@@ -23444,12 +23444,12 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942292</t>
+          <t>8 days, 20:47:22.354386</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942258</t>
+          <t>8 days, 20:47:22.354347</t>
         </is>
       </c>
     </row>
@@ -23558,12 +23558,12 @@
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942221</t>
+          <t>8 days, 20:47:22.354305</t>
         </is>
       </c>
     </row>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>9 days, 21:16:11.942184</t>
+          <t>8 days, 20:47:22.354272</t>
         </is>
       </c>
     </row>
@@ -23673,12 +23673,12 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -23735,12 +23735,12 @@
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>9 days, 21:01:11.942101</t>
+          <t>8 days, 20:32:22.354186</t>
         </is>
       </c>
     </row>
@@ -23797,12 +23797,12 @@
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>9 days, 21:01:11.942065</t>
+          <t>8 days, 20:32:22.354152</t>
         </is>
       </c>
     </row>
@@ -23859,12 +23859,12 @@
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>9 days, 21:01:11.942005</t>
+          <t>8 days, 20:32:22.354119</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>9 days, 21:01:11.941958</t>
+          <t>8 days, 20:32:22.354080</t>
         </is>
       </c>
     </row>
@@ -23979,12 +23979,12 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>9 days, 21:01:11.941879</t>
+          <t>8 days, 20:32:22.353970</t>
         </is>
       </c>
     </row>
@@ -24099,12 +24099,12 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24157,12 +24157,12 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24215,12 +24215,12 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24273,12 +24273,12 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24331,12 +24331,12 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24389,12 +24389,12 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24447,12 +24447,12 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24505,12 +24505,12 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24563,12 +24563,12 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24621,12 +24621,12 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24679,12 +24679,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24737,12 +24737,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24795,12 +24795,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24857,12 +24857,12 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>9 days, 21:01:11.941387</t>
+          <t>8 days, 20:32:22.353478</t>
         </is>
       </c>
     </row>
@@ -24915,12 +24915,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -24973,12 +24973,12 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25031,12 +25031,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25089,12 +25089,12 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25147,12 +25147,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25205,12 +25205,12 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25263,12 +25263,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25321,12 +25321,12 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25379,12 +25379,12 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25437,12 +25437,12 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25495,12 +25495,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25553,12 +25553,12 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25615,12 +25615,12 @@
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>9 days, 21:01:11.941003</t>
+          <t>8 days, 20:32:22.353112</t>
         </is>
       </c>
     </row>
@@ -25673,12 +25673,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25731,12 +25731,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25793,12 +25793,12 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>9 days, 21:01:11.940904</t>
+          <t>8 days, 20:32:22.352998</t>
         </is>
       </c>
     </row>
@@ -25851,12 +25851,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -25913,12 +25913,12 @@
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>9 days, 21:01:11.940839</t>
+          <t>8 days, 20:32:22.352918</t>
         </is>
       </c>
     </row>
@@ -25971,12 +25971,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26029,12 +26029,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26087,12 +26087,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26145,12 +26145,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26203,12 +26203,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26261,12 +26261,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26314,12 +26314,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26372,12 +26372,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26425,12 +26425,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26482,12 +26482,12 @@
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>5 days, 23:46:11.940522</t>
+          <t>4 days, 23:17:22.352607</t>
         </is>
       </c>
     </row>
@@ -26535,12 +26535,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26588,12 +26588,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26641,12 +26641,12 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26694,12 +26694,12 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26747,12 +26747,12 @@
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26800,12 +26800,12 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26853,12 +26853,12 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26906,12 +26906,12 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -26959,12 +26959,12 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27012,12 +27012,12 @@
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27065,12 +27065,12 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27118,12 +27118,12 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27171,12 +27171,12 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27224,12 +27224,12 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27277,12 +27277,12 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27330,12 +27330,12 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27383,12 +27383,12 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27436,12 +27436,12 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27489,12 +27489,12 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27542,12 +27542,12 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27595,12 +27595,12 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27648,12 +27648,12 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27701,12 +27701,12 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27754,12 +27754,12 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27807,12 +27807,12 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27865,12 +27865,12 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27918,12 +27918,12 @@
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -27976,12 +27976,12 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28029,12 +28029,12 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28087,12 +28087,12 @@
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28136,12 +28136,12 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28189,12 +28189,12 @@
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>5 days, 0:16:11.939451</t>
+          <t>3 days, 23:47:22.351549</t>
         </is>
       </c>
     </row>
@@ -28242,12 +28242,12 @@
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>4 days, 23:31:11.939415</t>
+          <t>3 days, 23:02:22.351515</t>
         </is>
       </c>
     </row>
@@ -28295,12 +28295,12 @@
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28348,12 +28348,12 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28401,12 +28401,12 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28454,12 +28454,12 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28507,12 +28507,12 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28560,12 +28560,12 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28613,12 +28613,12 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28666,12 +28666,12 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28719,12 +28719,12 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28772,12 +28772,12 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28825,12 +28825,12 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28878,12 +28878,12 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28931,12 +28931,12 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -28984,12 +28984,12 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29037,12 +29037,12 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29090,12 +29090,12 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29143,12 +29143,12 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29196,12 +29196,12 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29249,12 +29249,12 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29302,12 +29302,12 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29355,12 +29355,12 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29408,12 +29408,12 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29461,12 +29461,12 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29514,12 +29514,12 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29567,12 +29567,12 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29620,12 +29620,12 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29673,12 +29673,12 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29726,12 +29726,12 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29779,12 +29779,12 @@
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29832,12 +29832,12 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29885,12 +29885,12 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29938,12 +29938,12 @@
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -29991,12 +29991,12 @@
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30044,12 +30044,12 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30097,12 +30097,12 @@
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30150,12 +30150,12 @@
       <c r="J529" t="inlineStr"/>
       <c r="K529" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30203,12 +30203,12 @@
       <c r="J530" t="inlineStr"/>
       <c r="K530" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30256,12 +30256,12 @@
       <c r="J531" t="inlineStr"/>
       <c r="K531" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30309,12 +30309,12 @@
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30362,12 +30362,12 @@
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30415,12 +30415,12 @@
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30468,12 +30468,12 @@
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30521,12 +30521,12 @@
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30579,12 +30579,12 @@
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30632,12 +30632,12 @@
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30685,12 +30685,12 @@
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30738,12 +30738,12 @@
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30791,12 +30791,12 @@
       <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30844,12 +30844,12 @@
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30897,12 +30897,12 @@
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -30950,12 +30950,12 @@
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31003,12 +31003,12 @@
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31056,12 +31056,12 @@
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31109,12 +31109,12 @@
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31162,12 +31162,12 @@
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31215,12 +31215,12 @@
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31268,12 +31268,12 @@
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31321,12 +31321,12 @@
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31374,12 +31374,12 @@
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31427,12 +31427,12 @@
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31480,12 +31480,12 @@
       <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31533,12 +31533,12 @@
       <c r="J555" t="inlineStr"/>
       <c r="K555" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31586,12 +31586,12 @@
       <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31639,12 +31639,12 @@
       <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31692,12 +31692,12 @@
       <c r="J558" t="inlineStr"/>
       <c r="K558" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31745,12 +31745,12 @@
       <c r="J559" t="inlineStr"/>
       <c r="K559" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31798,12 +31798,12 @@
       <c r="J560" t="inlineStr"/>
       <c r="K560" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31851,12 +31851,12 @@
       <c r="J561" t="inlineStr"/>
       <c r="K561" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31904,12 +31904,12 @@
       <c r="J562" t="inlineStr"/>
       <c r="K562" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -31957,12 +31957,12 @@
       <c r="J563" t="inlineStr"/>
       <c r="K563" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32014,12 +32014,12 @@
       </c>
       <c r="K564" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M564" t="inlineStr">
         <is>
-          <t>2 days, 18:01:11.937260</t>
+          <t>1 day, 17:32:22.349357</t>
         </is>
       </c>
     </row>
@@ -32071,12 +32071,12 @@
       </c>
       <c r="K565" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M565" t="inlineStr">
         <is>
-          <t>2 days, 18:01:11.937223</t>
+          <t>1 day, 17:32:22.349320</t>
         </is>
       </c>
     </row>
@@ -32124,12 +32124,12 @@
       <c r="J566" t="inlineStr"/>
       <c r="K566" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32177,12 +32177,12 @@
       <c r="J567" t="inlineStr"/>
       <c r="K567" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32230,12 +32230,12 @@
       <c r="J568" t="inlineStr"/>
       <c r="K568" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32283,12 +32283,12 @@
       <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32336,12 +32336,12 @@
       <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32389,12 +32389,12 @@
       <c r="J571" t="inlineStr"/>
       <c r="K571" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32442,12 +32442,12 @@
       <c r="J572" t="inlineStr"/>
       <c r="K572" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32495,12 +32495,12 @@
       <c r="J573" t="inlineStr"/>
       <c r="K573" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L573" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32548,12 +32548,12 @@
       <c r="J574" t="inlineStr"/>
       <c r="K574" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L574" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32601,12 +32601,12 @@
       <c r="J575" t="inlineStr"/>
       <c r="K575" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32654,12 +32654,12 @@
       <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L576" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32707,12 +32707,12 @@
       <c r="J577" t="inlineStr"/>
       <c r="K577" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L577" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32760,12 +32760,12 @@
       <c r="J578" t="inlineStr"/>
       <c r="K578" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L578" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32813,12 +32813,12 @@
       <c r="J579" t="inlineStr"/>
       <c r="K579" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32866,12 +32866,12 @@
       <c r="J580" t="inlineStr"/>
       <c r="K580" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L580" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32919,12 +32919,12 @@
       <c r="J581" t="inlineStr"/>
       <c r="K581" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L581" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -32972,12 +32972,12 @@
       <c r="J582" t="inlineStr"/>
       <c r="K582" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L582" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33025,12 +33025,12 @@
       <c r="J583" t="inlineStr"/>
       <c r="K583" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L583" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33078,12 +33078,12 @@
       <c r="J584" t="inlineStr"/>
       <c r="K584" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33131,12 +33131,12 @@
       <c r="J585" t="inlineStr"/>
       <c r="K585" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L585" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33184,12 +33184,12 @@
       <c r="J586" t="inlineStr"/>
       <c r="K586" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L586" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33237,12 +33237,12 @@
       <c r="J587" t="inlineStr"/>
       <c r="K587" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L587" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33286,12 +33286,12 @@
       <c r="J588" t="inlineStr"/>
       <c r="K588" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33335,12 +33335,12 @@
       <c r="J589" t="inlineStr"/>
       <c r="K589" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L589" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33384,12 +33384,12 @@
       <c r="J590" t="inlineStr"/>
       <c r="K590" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L590" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33437,12 +33437,12 @@
       <c r="J591" t="inlineStr"/>
       <c r="K591" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L591" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33490,12 +33490,12 @@
       <c r="J592" t="inlineStr"/>
       <c r="K592" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L592" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33543,12 +33543,12 @@
       <c r="J593" t="inlineStr"/>
       <c r="K593" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L593" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33596,12 +33596,12 @@
       <c r="J594" t="inlineStr"/>
       <c r="K594" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L594" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33649,12 +33649,12 @@
       <c r="J595" t="inlineStr"/>
       <c r="K595" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33702,12 +33702,12 @@
       <c r="J596" t="inlineStr"/>
       <c r="K596" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L596" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33755,12 +33755,12 @@
       <c r="J597" t="inlineStr"/>
       <c r="K597" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33812,12 +33812,12 @@
       </c>
       <c r="K598" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>1 day, 22:01:11.936197</t>
+          <t>21:32:22.348311</t>
         </is>
       </c>
     </row>
@@ -33869,12 +33869,12 @@
       </c>
       <c r="K599" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>1 day, 22:01:11.936157</t>
+          <t>21:32:22.348265</t>
         </is>
       </c>
     </row>
@@ -33922,12 +33922,12 @@
       <c r="J600" t="inlineStr"/>
       <c r="K600" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -33975,12 +33975,12 @@
       <c r="J601" t="inlineStr"/>
       <c r="K601" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34028,12 +34028,12 @@
       <c r="J602" t="inlineStr"/>
       <c r="K602" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34081,12 +34081,12 @@
       <c r="J603" t="inlineStr"/>
       <c r="K603" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34134,12 +34134,12 @@
       <c r="J604" t="inlineStr"/>
       <c r="K604" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34187,12 +34187,12 @@
       <c r="J605" t="inlineStr"/>
       <c r="K605" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34240,12 +34240,12 @@
       <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34293,12 +34293,12 @@
       <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34346,12 +34346,12 @@
       <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34399,12 +34399,12 @@
       <c r="J609" t="inlineStr"/>
       <c r="K609" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34452,12 +34452,12 @@
       <c r="J610" t="inlineStr"/>
       <c r="K610" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34505,12 +34505,12 @@
       <c r="J611" t="inlineStr"/>
       <c r="K611" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34558,12 +34558,12 @@
       <c r="J612" t="inlineStr"/>
       <c r="K612" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L612" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34611,12 +34611,12 @@
       <c r="J613" t="inlineStr"/>
       <c r="K613" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34664,12 +34664,12 @@
       <c r="J614" t="inlineStr"/>
       <c r="K614" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L614" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34717,12 +34717,12 @@
       <c r="J615" t="inlineStr"/>
       <c r="K615" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34770,12 +34770,12 @@
       <c r="J616" t="inlineStr"/>
       <c r="K616" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34823,12 +34823,12 @@
       <c r="J617" t="inlineStr"/>
       <c r="K617" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34876,12 +34876,12 @@
       <c r="J618" t="inlineStr"/>
       <c r="K618" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34929,12 +34929,12 @@
       <c r="J619" t="inlineStr"/>
       <c r="K619" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -34982,12 +34982,12 @@
       <c r="J620" t="inlineStr"/>
       <c r="K620" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35035,12 +35035,12 @@
       <c r="J621" t="inlineStr"/>
       <c r="K621" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35088,12 +35088,12 @@
       <c r="J622" t="inlineStr"/>
       <c r="K622" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35141,12 +35141,12 @@
       <c r="J623" t="inlineStr"/>
       <c r="K623" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35194,12 +35194,12 @@
       <c r="J624" t="inlineStr"/>
       <c r="K624" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35247,12 +35247,12 @@
       <c r="J625" t="inlineStr"/>
       <c r="K625" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35300,12 +35300,12 @@
       <c r="J626" t="inlineStr"/>
       <c r="K626" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L626" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35353,12 +35353,12 @@
       <c r="J627" t="inlineStr"/>
       <c r="K627" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L627" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35406,12 +35406,12 @@
       <c r="J628" t="inlineStr"/>
       <c r="K628" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35459,12 +35459,12 @@
       <c r="J629" t="inlineStr"/>
       <c r="K629" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L629" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35512,12 +35512,12 @@
       <c r="J630" t="inlineStr"/>
       <c r="K630" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35565,12 +35565,12 @@
       <c r="J631" t="inlineStr"/>
       <c r="K631" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35618,12 +35618,12 @@
       <c r="J632" t="inlineStr"/>
       <c r="K632" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L632" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35671,12 +35671,12 @@
       <c r="J633" t="inlineStr"/>
       <c r="K633" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35724,12 +35724,12 @@
       <c r="J634" t="inlineStr"/>
       <c r="K634" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L634" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35777,12 +35777,12 @@
       <c r="J635" t="inlineStr"/>
       <c r="K635" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L635" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35830,12 +35830,12 @@
       <c r="J636" t="inlineStr"/>
       <c r="K636" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L636" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35883,12 +35883,12 @@
       <c r="J637" t="inlineStr"/>
       <c r="K637" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L637" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35936,12 +35936,12 @@
       <c r="J638" t="inlineStr"/>
       <c r="K638" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L638" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -35989,12 +35989,12 @@
       <c r="J639" t="inlineStr"/>
       <c r="K639" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L639" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36042,12 +36042,12 @@
       <c r="J640" t="inlineStr"/>
       <c r="K640" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L640" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36095,12 +36095,12 @@
       <c r="J641" t="inlineStr"/>
       <c r="K641" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L641" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36148,12 +36148,12 @@
       <c r="J642" t="inlineStr"/>
       <c r="K642" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36201,12 +36201,12 @@
       <c r="J643" t="inlineStr"/>
       <c r="K643" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L643" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36254,12 +36254,12 @@
       <c r="J644" t="inlineStr"/>
       <c r="K644" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L644" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36307,12 +36307,12 @@
       <c r="J645" t="inlineStr"/>
       <c r="K645" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L645" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36360,12 +36360,12 @@
       <c r="J646" t="inlineStr"/>
       <c r="K646" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36413,12 +36413,12 @@
       <c r="J647" t="inlineStr"/>
       <c r="K647" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36466,12 +36466,12 @@
       <c r="J648" t="inlineStr"/>
       <c r="K648" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L648" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36519,12 +36519,12 @@
       <c r="J649" t="inlineStr"/>
       <c r="K649" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L649" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36572,12 +36572,12 @@
       <c r="J650" t="inlineStr"/>
       <c r="K650" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L650" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36625,12 +36625,12 @@
       <c r="J651" t="inlineStr"/>
       <c r="K651" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L651" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36678,12 +36678,12 @@
       <c r="J652" t="inlineStr"/>
       <c r="K652" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L652" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36731,12 +36731,12 @@
       <c r="J653" t="inlineStr"/>
       <c r="K653" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>
@@ -36784,12 +36784,12 @@
       <c r="J654" t="inlineStr"/>
       <c r="K654" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L654" t="inlineStr">
         <is>
-          <t>06/19/26 12:58 PM</t>
+          <t>06/20/26 01:27 PM</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -542,12 +542,12 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -595,12 +595,12 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -652,12 +652,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.538091</t>
+          <t>18 days, 4:34:19.105133</t>
         </is>
       </c>
     </row>
@@ -709,12 +709,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.538040</t>
+          <t>18 days, 4:34:19.105076</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.538003</t>
+          <t>18 days, 4:34:19.105031</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537968</t>
+          <t>18 days, 4:34:19.104990</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537933</t>
+          <t>18 days, 4:34:19.104950</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537899</t>
+          <t>18 days, 4:34:19.104912</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537866</t>
+          <t>18 days, 4:34:19.104875</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537835</t>
+          <t>18 days, 4:34:19.104836</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537802</t>
+          <t>18 days, 4:34:19.104797</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537770</t>
+          <t>18 days, 4:34:19.104733</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537739</t>
+          <t>18 days, 4:34:19.104690</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537707</t>
+          <t>18 days, 4:34:19.104651</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537674</t>
+          <t>18 days, 4:34:19.104613</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537642</t>
+          <t>18 days, 4:34:19.104576</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537610</t>
+          <t>18 days, 4:34:19.104537</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537578</t>
+          <t>18 days, 4:34:19.104500</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537547</t>
+          <t>18 days, 4:34:19.104464</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>19 days, 4:34:53.537516</t>
+          <t>18 days, 4:34:19.104428</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>18 days, 22:49:53.537485</t>
+          <t>17 days, 22:49:19.104392</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>18 days, 22:49:53.537454</t>
+          <t>17 days, 22:49:19.104355</t>
         </is>
       </c>
     </row>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>18 days, 22:49:53.537422</t>
+          <t>17 days, 22:49:19.104318</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>18 days, 22:49:53.537390</t>
+          <t>17 days, 22:49:19.104282</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>18 days, 22:49:53.537358</t>
+          <t>17 days, 22:49:19.104245</t>
         </is>
       </c>
     </row>
@@ -1963,12 +1963,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>18 days, 22:49:53.537324</t>
+          <t>17 days, 22:49:19.104210</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>18 days, 22:49:53.537293</t>
+          <t>17 days, 22:49:19.104175</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>18 days, 22:34:53.537244</t>
+          <t>17 days, 22:34:19.104136</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>18 days, 22:34:53.537212</t>
+          <t>17 days, 22:34:19.104099</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>18 days, 22:34:53.537180</t>
+          <t>17 days, 22:34:19.104062</t>
         </is>
       </c>
     </row>
@@ -2248,12 +2248,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>18 days, 22:34:53.537147</t>
+          <t>17 days, 22:34:19.104026</t>
         </is>
       </c>
     </row>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>18 days, 22:34:53.537119</t>
+          <t>17 days, 22:34:19.103991</t>
         </is>
       </c>
     </row>
@@ -2362,12 +2362,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>18 days, 22:34:53.537084</t>
+          <t>17 days, 22:34:19.103953</t>
         </is>
       </c>
     </row>
@@ -2419,12 +2419,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>18 days, 22:34:53.537053</t>
+          <t>17 days, 22:34:19.103917</t>
         </is>
       </c>
     </row>
@@ -2476,12 +2476,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>18 days, 22:34:53.537026</t>
+          <t>17 days, 22:34:19.103884</t>
         </is>
       </c>
     </row>
@@ -2529,12 +2529,12 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -2591,12 +2591,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>18 days, 22:04:53.536956</t>
+          <t>17 days, 22:04:19.103804</t>
         </is>
       </c>
     </row>
@@ -2648,12 +2648,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>18 days, 20:04:53.536921</t>
+          <t>17 days, 20:04:19.103745</t>
         </is>
       </c>
     </row>
@@ -2705,12 +2705,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>18 days, 18:34:53.536883</t>
+          <t>17 days, 18:34:19.103697</t>
         </is>
       </c>
     </row>
@@ -2758,12 +2758,12 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -2811,12 +2811,12 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -2868,12 +2868,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>18 days, 1:34:53.536789</t>
+          <t>17 days, 1:34:19.103592</t>
         </is>
       </c>
     </row>
@@ -2925,12 +2925,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>18 days, 1:34:53.536756</t>
+          <t>17 days, 1:34:19.103555</t>
         </is>
       </c>
     </row>
@@ -2982,12 +2982,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>18 days, 1:34:53.536725</t>
+          <t>17 days, 1:34:19.103519</t>
         </is>
       </c>
     </row>
@@ -3040,12 +3040,12 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -3098,12 +3098,12 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3156,12 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -3214,12 +3214,12 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -3272,12 +3272,12 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -3330,12 +3330,12 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -3388,12 +3388,12 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -3445,12 +3445,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>18 days, 0:04:53.536510</t>
+          <t>17 days, 0:04:19.103267</t>
         </is>
       </c>
     </row>
@@ -3502,12 +3502,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>18 days, 0:04:53.536477</t>
+          <t>17 days, 0:04:19.103227</t>
         </is>
       </c>
     </row>
@@ -3559,12 +3559,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>18 days, 0:04:53.536445</t>
+          <t>17 days, 0:04:19.103181</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>18 days, 0:04:53.536413</t>
+          <t>17 days, 0:04:19.103143</t>
         </is>
       </c>
     </row>
@@ -3673,12 +3673,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>18 days, 0:04:53.536382</t>
+          <t>17 days, 0:04:19.103105</t>
         </is>
       </c>
     </row>
@@ -3730,12 +3730,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>18 days, 0:04:53.536349</t>
+          <t>17 days, 0:04:19.103067</t>
         </is>
       </c>
     </row>
@@ -3787,12 +3787,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>18 days, 0:04:53.536318</t>
+          <t>17 days, 0:04:19.103029</t>
         </is>
       </c>
     </row>
@@ -3844,12 +3844,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>18 days, 0:04:53.536287</t>
+          <t>17 days, 0:04:19.102992</t>
         </is>
       </c>
     </row>
@@ -3901,12 +3901,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>18 days, 0:04:53.536234</t>
+          <t>17 days, 0:04:19.102955</t>
         </is>
       </c>
     </row>
@@ -3958,12 +3958,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>18 days, 0:04:53.536205</t>
+          <t>17 days, 0:04:19.102921</t>
         </is>
       </c>
     </row>
@@ -4015,12 +4015,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>18 days, 0:04:53.536177</t>
+          <t>17 days, 0:04:19.102889</t>
         </is>
       </c>
     </row>
@@ -4072,12 +4072,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>17 days, 21:19:53.536149</t>
+          <t>16 days, 21:19:19.102855</t>
         </is>
       </c>
     </row>
@@ -4129,12 +4129,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>17 days, 21:19:53.536119</t>
+          <t>16 days, 21:19:19.102821</t>
         </is>
       </c>
     </row>
@@ -4186,12 +4186,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>17 days, 21:19:53.536090</t>
+          <t>16 days, 21:19:19.102787</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -4302,12 +4302,12 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -4360,12 +4360,12 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -4418,12 +4418,12 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -4476,12 +4476,12 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -4534,12 +4534,12 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -4650,12 +4650,12 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4708,12 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -4882,12 +4882,12 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -4940,12 +4940,12 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -4998,12 +4998,12 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5114,12 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5346,12 +5346,12 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5404,12 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5462,12 +5462,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5520,12 +5520,12 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5573,12 +5573,12 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>17 days, 19:49:53.535426</t>
+          <t>16 days, 19:49:19.102013</t>
         </is>
       </c>
     </row>
@@ -5688,12 +5688,12 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5746,12 +5746,12 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5808,12 +5808,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>17 days, 3:34:53.535349</t>
+          <t>16 days, 3:34:19.101920</t>
         </is>
       </c>
     </row>
@@ -5866,12 +5866,12 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -6040,12 +6040,12 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -6156,12 +6156,12 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -6214,12 +6214,12 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -6272,12 +6272,12 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -6387,12 +6387,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>17 days, 3:19:53.535098</t>
+          <t>16 days, 3:19:19.101598</t>
         </is>
       </c>
     </row>
@@ -6444,12 +6444,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>17 days, 3:19:53.535064</t>
+          <t>16 days, 3:19:19.101555</t>
         </is>
       </c>
     </row>
@@ -6501,12 +6501,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>17 days, 3:19:53.535037</t>
+          <t>16 days, 3:19:19.101521</t>
         </is>
       </c>
     </row>
@@ -6558,12 +6558,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>17 days, 3:19:53.535007</t>
+          <t>16 days, 3:19:19.101487</t>
         </is>
       </c>
     </row>
@@ -6615,12 +6615,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>17 days, 3:19:53.534976</t>
+          <t>16 days, 3:19:19.101450</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6665,19 +6665,15 @@
           <t>08/18/26 03:45 pm</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>WASA02 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>17 days, 3:19:53.534946</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -6729,12 +6725,12 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>17 days, 3:19:53.534917</t>
+          <t>16 days, 3:19:19.101385</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6752,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6779,19 +6775,15 @@
           <t>08/18/26 03:45 pm</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>WASA02 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>17 days, 3:19:53.534887</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -6839,12 +6831,12 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -6892,12 +6884,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6937,12 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -7002,12 +6994,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>17 days, 3:04:53.534788</t>
+          <t>16 days, 3:04:19.101239</t>
         </is>
       </c>
     </row>
@@ -7059,12 +7051,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>17 days, 3:04:53.534760</t>
+          <t>16 days, 3:04:19.101205</t>
         </is>
       </c>
     </row>
@@ -7116,12 +7108,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>17 days, 3:04:53.534731</t>
+          <t>16 days, 3:04:19.101173</t>
         </is>
       </c>
     </row>
@@ -7173,12 +7165,12 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>17 days, 3:04:53.534703</t>
+          <t>16 days, 3:04:19.101142</t>
         </is>
       </c>
     </row>
@@ -7230,12 +7222,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>17 days, 3:04:53.534676</t>
+          <t>16 days, 3:04:19.101111</t>
         </is>
       </c>
     </row>
@@ -7287,12 +7279,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>17 days, 3:04:53.534650</t>
+          <t>16 days, 3:04:19.101082</t>
         </is>
       </c>
     </row>
@@ -7344,12 +7336,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>17 days, 3:04:53.534624</t>
+          <t>16 days, 3:04:19.101052</t>
         </is>
       </c>
     </row>
@@ -7401,12 +7393,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>17 days, 3:04:53.534598</t>
+          <t>16 days, 3:04:19.101023</t>
         </is>
       </c>
     </row>
@@ -7458,12 +7450,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>17 days, 3:04:53.534568</t>
+          <t>16 days, 3:04:19.100989</t>
         </is>
       </c>
     </row>
@@ -7515,12 +7507,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>17 days, 3:04:53.534542</t>
+          <t>16 days, 3:04:19.100960</t>
         </is>
       </c>
     </row>
@@ -7572,12 +7564,12 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>17 days, 3:04:53.534516</t>
+          <t>16 days, 3:04:19.100930</t>
         </is>
       </c>
     </row>
@@ -7629,12 +7621,12 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>17 days, 3:04:53.534486</t>
+          <t>16 days, 3:04:19.100897</t>
         </is>
       </c>
     </row>
@@ -7686,12 +7678,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534458</t>
+          <t>16 days, 2:49:19.100866</t>
         </is>
       </c>
     </row>
@@ -7743,12 +7735,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534431</t>
+          <t>16 days, 2:49:19.100836</t>
         </is>
       </c>
     </row>
@@ -7800,12 +7792,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534404</t>
+          <t>16 days, 2:49:19.100805</t>
         </is>
       </c>
     </row>
@@ -7857,12 +7849,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534375</t>
+          <t>16 days, 2:49:19.100774</t>
         </is>
       </c>
     </row>
@@ -7914,12 +7906,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534345</t>
+          <t>16 days, 2:49:19.100718</t>
         </is>
       </c>
     </row>
@@ -7971,12 +7963,12 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534318</t>
+          <t>16 days, 2:49:19.100686</t>
         </is>
       </c>
     </row>
@@ -8028,12 +8020,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534292</t>
+          <t>16 days, 2:49:19.100655</t>
         </is>
       </c>
     </row>
@@ -8085,12 +8077,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534249</t>
+          <t>16 days, 2:49:19.100623</t>
         </is>
       </c>
     </row>
@@ -8142,12 +8134,12 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534221</t>
+          <t>16 days, 2:49:19.100593</t>
         </is>
       </c>
     </row>
@@ -8199,12 +8191,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534194</t>
+          <t>16 days, 2:49:19.100564</t>
         </is>
       </c>
     </row>
@@ -8256,12 +8248,12 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534168</t>
+          <t>16 days, 2:49:19.100535</t>
         </is>
       </c>
     </row>
@@ -8313,12 +8305,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534141</t>
+          <t>16 days, 2:49:19.100505</t>
         </is>
       </c>
     </row>
@@ -8370,12 +8362,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534116</t>
+          <t>16 days, 2:49:19.100476</t>
         </is>
       </c>
     </row>
@@ -8427,12 +8419,12 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534090</t>
+          <t>16 days, 2:49:19.100447</t>
         </is>
       </c>
     </row>
@@ -8484,12 +8476,12 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534065</t>
+          <t>16 days, 2:49:19.100418</t>
         </is>
       </c>
     </row>
@@ -8541,12 +8533,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>17 days, 2:49:53.534039</t>
+          <t>16 days, 2:49:19.100389</t>
         </is>
       </c>
     </row>
@@ -8598,12 +8590,12 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>17 days, 1:34:53.534010</t>
+          <t>16 days, 1:34:19.100356</t>
         </is>
       </c>
     </row>
@@ -8651,12 +8643,12 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -8709,12 +8701,12 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -8767,12 +8759,12 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -8825,12 +8817,12 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -8878,12 +8870,12 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8897,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8933,19 +8925,15 @@
           <t>08/18/26 08:00 am</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>WGL07 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>16 days, 19:34:53.533856</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8955,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8995,19 +8983,15 @@
           <t>08/18/26 08:00 am</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>WGL07 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>16 days, 19:34:53.533828</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9013,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9057,19 +9041,15 @@
           <t>08/18/26 08:00 am</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>WGL07 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>16 days, 19:34:53.533799</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -9122,12 +9102,12 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9129,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9177,19 +9157,15 @@
           <t>08/18/26 08:00 am</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>VDC - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>16 days, 19:34:53.533742</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -9242,12 +9218,12 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9245,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9297,19 +9273,15 @@
           <t>08/18/26 08:00 am</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>VDC - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>16 days, 19:34:53.533689</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9303,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9359,19 +9331,15 @@
           <t>08/18/26 08:00 am</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>VDC - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>16 days, 19:34:53.533658</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -9424,12 +9392,12 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -9486,12 +9454,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>16 days, 19:04:53.533595</t>
+          <t>15 days, 19:04:19.099918</t>
         </is>
       </c>
     </row>
@@ -9548,12 +9516,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>16 days, 19:04:53.533559</t>
+          <t>15 days, 19:04:19.099878</t>
         </is>
       </c>
     </row>
@@ -9610,12 +9578,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>16 days, 19:04:53.533525</t>
+          <t>15 days, 19:04:19.099838</t>
         </is>
       </c>
     </row>
@@ -9672,12 +9640,12 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>16 days, 19:04:53.533490</t>
+          <t>15 days, 19:04:19.099797</t>
         </is>
       </c>
     </row>
@@ -9734,12 +9702,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>16 days, 19:04:53.533455</t>
+          <t>15 days, 19:04:19.099738</t>
         </is>
       </c>
     </row>
@@ -9796,12 +9764,12 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>16 days, 19:04:53.533420</t>
+          <t>15 days, 19:04:19.099696</t>
         </is>
       </c>
     </row>
@@ -9858,12 +9826,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>16 days, 19:04:53.533384</t>
+          <t>15 days, 19:04:19.099657</t>
         </is>
       </c>
     </row>
@@ -9920,12 +9888,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>16 days, 19:04:53.533347</t>
+          <t>15 days, 19:04:19.099618</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9950,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>16 days, 19:04:53.533310</t>
+          <t>15 days, 19:04:19.099580</t>
         </is>
       </c>
     </row>
@@ -10044,12 +10012,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>16 days, 19:04:53.533274</t>
+          <t>15 days, 19:04:19.099540</t>
         </is>
       </c>
     </row>
@@ -10102,12 +10070,12 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10160,12 +10128,12 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10213,12 +10181,12 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10266,12 +10234,12 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10328,12 +10296,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>16 days, 3:04:53.533130</t>
+          <t>15 days, 3:04:19.099388</t>
         </is>
       </c>
     </row>
@@ -10386,12 +10354,12 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10444,12 +10412,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10502,12 +10470,12 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10560,12 +10528,12 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10618,12 +10586,12 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10676,12 +10644,12 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10734,12 +10702,12 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10792,12 +10760,12 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10850,12 +10818,12 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10908,12 +10876,12 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -10966,12 +10934,12 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11024,12 +10992,12 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11082,12 +11050,12 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11140,12 +11108,12 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11166,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11256,12 +11224,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11314,12 +11282,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11372,12 +11340,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11398,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11492,12 +11460,12 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>16 days, 2:49:53.532621</t>
+          <t>15 days, 2:49:19.098826</t>
         </is>
       </c>
     </row>
@@ -11554,12 +11522,12 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>16 days, 2:49:53.532588</t>
+          <t>15 days, 2:49:19.098786</t>
         </is>
       </c>
     </row>
@@ -11607,12 +11575,12 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11660,12 +11628,12 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11717,12 +11685,12 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>16 days, 2:04:53.532508</t>
+          <t>15 days, 2:04:19.098661</t>
         </is>
       </c>
     </row>
@@ -11774,12 +11742,12 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>15 days, 22:49:53.532478</t>
+          <t>14 days, 22:49:19.098623</t>
         </is>
       </c>
     </row>
@@ -11827,12 +11795,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11848,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11933,12 +11901,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -11986,12 +11954,12 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12039,12 +12007,12 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12092,12 +12060,12 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12150,12 +12118,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12208,12 +12176,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12266,12 +12234,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12324,12 +12292,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12382,12 +12350,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12444,12 +12412,12 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>15 days, 20:49:53.532149</t>
+          <t>14 days, 20:49:19.098261</t>
         </is>
       </c>
     </row>
@@ -12502,12 +12470,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12560,12 +12528,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12618,12 +12586,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12676,12 +12644,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12734,12 +12702,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12792,12 +12760,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12850,12 +12818,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12908,12 +12876,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -12966,12 +12934,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13024,12 +12992,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13082,12 +13050,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13140,12 +13108,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13198,12 +13166,12 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13256,12 +13224,12 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13314,12 +13282,12 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13372,12 +13340,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13430,12 +13398,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13488,12 +13456,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13546,12 +13514,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13603,12 +13571,12 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>15 days, 19:34:53.531597</t>
+          <t>14 days, 19:34:19.097614</t>
         </is>
       </c>
     </row>
@@ -13661,12 +13629,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13719,12 +13687,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13777,12 +13745,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13835,12 +13803,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13893,12 +13861,12 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -13951,12 +13919,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14009,12 +13977,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14067,12 +14035,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14125,12 +14093,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14183,12 +14151,12 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14241,12 +14209,12 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14299,12 +14267,12 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14357,12 +14325,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14415,12 +14383,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14473,12 +14441,12 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14531,12 +14499,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14589,12 +14557,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14647,12 +14615,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14705,12 +14673,12 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14763,12 +14731,12 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14821,12 +14789,12 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14879,12 +14847,12 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14937,12 +14905,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -14995,12 +14963,12 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15053,12 +15021,12 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15111,12 +15079,12 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15169,12 +15137,12 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15227,12 +15195,12 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15285,12 +15253,12 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15343,12 +15311,12 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15401,12 +15369,12 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15459,12 +15427,12 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15517,12 +15485,12 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15575,12 +15543,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15633,12 +15601,12 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15691,12 +15659,12 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15749,12 +15717,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15807,12 +15775,12 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15865,12 +15833,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15923,12 +15891,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -15981,12 +15949,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16039,12 +16007,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16097,12 +16065,12 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16155,12 +16123,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16213,12 +16181,12 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16271,12 +16239,12 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16329,12 +16297,12 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16387,12 +16355,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16445,12 +16413,12 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16503,12 +16471,12 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16561,12 +16529,12 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16619,12 +16587,12 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16677,12 +16645,12 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16735,12 +16703,12 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16793,12 +16761,12 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16851,12 +16819,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16909,12 +16877,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -16967,12 +16935,12 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -17024,12 +16992,12 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>15 days, 19:04:53.530210</t>
+          <t>14 days, 19:04:19.096048</t>
         </is>
       </c>
     </row>
@@ -17086,12 +17054,12 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>15 days, 19:04:53.530172</t>
+          <t>14 days, 19:04:19.096003</t>
         </is>
       </c>
     </row>
@@ -17148,12 +17116,12 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>15 days, 19:04:53.530138</t>
+          <t>14 days, 19:04:19.095965</t>
         </is>
       </c>
     </row>
@@ -17175,7 +17143,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -17203,19 +17171,15 @@
           <t>08/17/26 07:30 am</t>
         </is>
       </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>VDC - Not complete/In progress &amp; WGL07 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>15 days, 19:04:53.530104</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -17267,12 +17231,12 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>15 days, 19:04:53.530066</t>
+          <t>14 days, 19:04:19.095890</t>
         </is>
       </c>
     </row>
@@ -17320,12 +17284,12 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -17373,12 +17337,12 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -17426,12 +17390,12 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -17479,12 +17443,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -17532,12 +17496,12 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -17585,12 +17549,12 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -17638,12 +17602,12 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -17691,12 +17655,12 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -17744,12 +17708,12 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -17797,12 +17761,12 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -17854,12 +17818,12 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>15 days, 18:34:53.529799</t>
+          <t>14 days, 18:34:19.095560</t>
         </is>
       </c>
     </row>
@@ -17907,12 +17871,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -17965,12 +17929,12 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -18023,12 +17987,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -18081,12 +18045,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -18139,12 +18103,12 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -18197,12 +18161,12 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -18255,12 +18219,12 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -18313,12 +18277,12 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -18371,12 +18335,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -18429,12 +18393,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -18487,12 +18451,12 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -18545,12 +18509,12 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -18598,12 +18562,12 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -18655,12 +18619,12 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>15 days, 18:34:53.529482</t>
+          <t>14 days, 18:34:19.095192</t>
         </is>
       </c>
     </row>
@@ -18712,12 +18676,12 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>15 days, 18:34:53.529451</t>
+          <t>14 days, 18:34:19.095155</t>
         </is>
       </c>
     </row>
@@ -18769,12 +18733,12 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>15 days, 18:34:53.529419</t>
+          <t>14 days, 18:34:19.095120</t>
         </is>
       </c>
     </row>
@@ -18826,12 +18790,12 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>13 days, 4:19:53.529385</t>
+          <t>12 days, 4:19:19.095080</t>
         </is>
       </c>
     </row>
@@ -18883,12 +18847,12 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>13 days, 4:19:53.529351</t>
+          <t>12 days, 4:19:19.095041</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18900,12 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -18994,12 +18958,12 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19052,12 +19016,12 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19110,12 +19074,12 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19168,12 +19132,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19226,12 +19190,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19284,12 +19248,12 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19342,12 +19306,12 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19400,12 +19364,12 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19458,12 +19422,12 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19516,12 +19480,12 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19574,12 +19538,12 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19632,12 +19596,12 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19690,12 +19654,12 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19748,12 +19712,12 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19806,12 +19770,12 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19864,12 +19828,12 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19922,12 +19886,12 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -19980,12 +19944,12 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20038,12 +20002,12 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20096,12 +20060,12 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20154,12 +20118,12 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20212,12 +20176,12 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20270,12 +20234,12 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20328,12 +20292,12 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20386,12 +20350,12 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20444,12 +20408,12 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20502,12 +20466,12 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20560,12 +20524,12 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20618,12 +20582,12 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20676,12 +20640,12 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20734,12 +20698,12 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20792,12 +20756,12 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20850,12 +20814,12 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20908,12 +20872,12 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -20966,12 +20930,12 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21024,12 +20988,12 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21082,12 +21046,12 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21140,12 +21104,12 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21198,12 +21162,12 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21256,12 +21220,12 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21314,12 +21278,12 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21372,12 +21336,12 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21430,12 +21394,12 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21488,12 +21452,12 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21546,12 +21510,12 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21604,12 +21568,12 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21662,12 +21626,12 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21720,12 +21684,12 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21778,12 +21742,12 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21836,12 +21800,12 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21894,12 +21858,12 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -21952,12 +21916,12 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22010,12 +21974,12 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22068,12 +22032,12 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22126,12 +22090,12 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22184,12 +22148,12 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22242,12 +22206,12 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22300,12 +22264,12 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22358,12 +22322,12 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22416,12 +22380,12 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22474,12 +22438,12 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22532,12 +22496,12 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22585,12 +22549,12 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22638,12 +22602,12 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22691,12 +22655,12 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22749,12 +22713,12 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22802,12 +22766,12 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22855,12 +22819,12 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22908,12 +22872,12 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -22961,12 +22925,12 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23014,12 +22978,12 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23067,12 +23031,12 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23120,12 +23084,12 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23173,12 +23137,12 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23226,12 +23190,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23279,12 +23243,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23332,12 +23296,12 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23390,12 +23354,12 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23448,12 +23412,12 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23506,12 +23470,12 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23564,12 +23528,12 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23622,12 +23586,12 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23680,12 +23644,12 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23738,12 +23702,12 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23796,12 +23760,12 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23854,12 +23818,12 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23912,12 +23876,12 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -23970,12 +23934,12 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24028,12 +23992,12 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24086,12 +24050,12 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24144,12 +24108,12 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24202,12 +24166,12 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24260,12 +24224,12 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24318,12 +24282,12 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24376,12 +24340,12 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24434,12 +24398,12 @@
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24455,12 @@
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>12 days, 20:49:53.526836</t>
+          <t>11 days, 20:49:19.092137</t>
         </is>
       </c>
     </row>
@@ -24548,12 +24512,12 @@
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>12 days, 20:49:53.526805</t>
+          <t>11 days, 20:49:19.092101</t>
         </is>
       </c>
     </row>
@@ -24605,12 +24569,12 @@
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>12 days, 20:49:53.526776</t>
+          <t>11 days, 20:49:19.092067</t>
         </is>
       </c>
     </row>
@@ -24658,12 +24622,12 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24711,12 +24675,12 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24764,12 +24728,12 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24821,12 +24785,12 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>12 days, 20:49:53.526685</t>
+          <t>11 days, 20:49:19.091956</t>
         </is>
       </c>
     </row>
@@ -24874,12 +24838,12 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24927,12 +24891,12 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -24985,12 +24949,12 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25038,12 +25002,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25091,12 +25055,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25149,12 +25113,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25207,12 +25171,12 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25265,12 +25229,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25323,12 +25287,12 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25376,12 +25340,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25429,12 +25393,12 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25482,12 +25446,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25535,12 +25499,12 @@
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>10 days, 21:19:53.526348</t>
+          <t>9 days, 21:19:19.091543</t>
         </is>
       </c>
     </row>
@@ -25588,12 +25552,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25641,12 +25605,12 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25690,12 +25654,12 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25739,12 +25703,12 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25788,12 +25752,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25837,12 +25801,12 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25886,12 +25850,12 @@
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25939,12 +25903,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -25992,12 +25956,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26050,12 +26014,12 @@
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26108,12 +26072,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26161,12 +26125,12 @@
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26214,12 +26178,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26267,12 +26231,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26320,12 +26284,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26373,12 +26337,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26431,12 +26395,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26489,12 +26453,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26547,12 +26511,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26605,12 +26569,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26663,12 +26627,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26721,12 +26685,12 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26779,12 +26743,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26837,12 +26801,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26890,12 +26854,12 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -26943,12 +26907,12 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27001,12 +26965,12 @@
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27059,12 +27023,12 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27117,12 +27081,12 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27175,12 +27139,12 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27233,12 +27197,12 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27291,12 +27255,12 @@
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27349,12 +27313,12 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27407,12 +27371,12 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27465,12 +27429,12 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27523,12 +27487,12 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27581,12 +27545,12 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27639,12 +27603,12 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27697,12 +27661,12 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27755,12 +27719,12 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27813,12 +27777,12 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27871,12 +27835,12 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27929,12 +27893,12 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -27982,12 +27946,12 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28035,12 +27999,12 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28088,12 +28052,12 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28141,12 +28105,12 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28194,12 +28158,12 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28247,12 +28211,12 @@
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28304,12 +28268,12 @@
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>5 days, 2:49:53.525010</t>
+          <t>4 days, 2:49:19.090042</t>
         </is>
       </c>
     </row>
@@ -28357,12 +28321,12 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28410,12 +28374,12 @@
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28463,12 +28427,12 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28520,12 +28484,12 @@
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>5 days, 2:34:53.524904</t>
+          <t>4 days, 2:34:19.089920</t>
         </is>
       </c>
     </row>
@@ -28573,12 +28537,12 @@
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28626,12 +28590,12 @@
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28679,12 +28643,12 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28732,12 +28696,12 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28785,12 +28749,12 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28838,12 +28802,12 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28891,12 +28855,12 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28944,12 +28908,12 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -28997,12 +28961,12 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29055,12 +29019,12 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29113,12 +29077,12 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29171,12 +29135,12 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29229,12 +29193,12 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29287,12 +29251,12 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29345,12 +29309,12 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29403,12 +29367,12 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29461,12 +29425,12 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29519,12 +29483,12 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29577,12 +29541,12 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29635,12 +29599,12 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29693,12 +29657,12 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29751,12 +29715,12 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29809,12 +29773,12 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29867,12 +29831,12 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29925,12 +29889,12 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -29983,12 +29947,12 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30041,12 +30005,12 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30099,12 +30063,12 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30157,12 +30121,12 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30215,12 +30179,12 @@
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30273,12 +30237,12 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30331,12 +30295,12 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30389,12 +30353,12 @@
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30447,12 +30411,12 @@
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30505,12 +30469,12 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30563,12 +30527,12 @@
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30621,12 +30585,12 @@
       <c r="J529" t="inlineStr"/>
       <c r="K529" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30679,12 +30643,12 @@
       <c r="J530" t="inlineStr"/>
       <c r="K530" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30737,12 +30701,12 @@
       <c r="J531" t="inlineStr"/>
       <c r="K531" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30795,12 +30759,12 @@
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30853,12 +30817,12 @@
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30911,12 +30875,12 @@
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -30969,12 +30933,12 @@
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31027,12 +30991,12 @@
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31085,12 +31049,12 @@
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31143,12 +31107,12 @@
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31201,12 +31165,12 @@
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31259,12 +31223,12 @@
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31317,12 +31281,12 @@
       <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31375,12 +31339,12 @@
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31433,12 +31397,12 @@
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31491,12 +31455,12 @@
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31549,12 +31513,12 @@
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31607,12 +31571,12 @@
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31669,12 +31633,12 @@
       </c>
       <c r="K547" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M547" t="inlineStr">
         <is>
-          <t>4 days, 3:49:53.523607</t>
+          <t>3 days, 3:49:19.088396</t>
         </is>
       </c>
     </row>
@@ -31722,12 +31686,12 @@
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31775,12 +31739,12 @@
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31828,12 +31792,12 @@
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31881,12 +31845,12 @@
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31934,12 +31898,12 @@
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -31987,12 +31951,12 @@
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32040,12 +32004,12 @@
       <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32093,12 +32057,12 @@
       <c r="J555" t="inlineStr"/>
       <c r="K555" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32146,12 +32110,12 @@
       <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32199,12 +32163,12 @@
       <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32252,12 +32216,12 @@
       <c r="J558" t="inlineStr"/>
       <c r="K558" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32305,12 +32269,12 @@
       <c r="J559" t="inlineStr"/>
       <c r="K559" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32358,12 +32322,12 @@
       <c r="J560" t="inlineStr"/>
       <c r="K560" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32411,12 +32375,12 @@
       <c r="J561" t="inlineStr"/>
       <c r="K561" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32464,12 +32428,12 @@
       <c r="J562" t="inlineStr"/>
       <c r="K562" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32517,12 +32481,12 @@
       <c r="J563" t="inlineStr"/>
       <c r="K563" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32570,12 +32534,12 @@
       <c r="J564" t="inlineStr"/>
       <c r="K564" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32623,12 +32587,12 @@
       <c r="J565" t="inlineStr"/>
       <c r="K565" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32676,12 +32640,12 @@
       <c r="J566" t="inlineStr"/>
       <c r="K566" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32734,12 +32698,12 @@
       <c r="J567" t="inlineStr"/>
       <c r="K567" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32792,12 +32756,12 @@
       <c r="J568" t="inlineStr"/>
       <c r="K568" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32850,12 +32814,12 @@
       <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32908,12 +32872,12 @@
       <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -32966,12 +32930,12 @@
       <c r="J571" t="inlineStr"/>
       <c r="K571" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33024,12 +32988,12 @@
       <c r="J572" t="inlineStr"/>
       <c r="K572" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33082,12 +33046,12 @@
       <c r="J573" t="inlineStr"/>
       <c r="K573" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L573" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33140,12 +33104,12 @@
       <c r="J574" t="inlineStr"/>
       <c r="K574" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L574" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33198,12 +33162,12 @@
       <c r="J575" t="inlineStr"/>
       <c r="K575" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33256,12 +33220,12 @@
       <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L576" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33314,12 +33278,12 @@
       <c r="J577" t="inlineStr"/>
       <c r="K577" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L577" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33372,12 +33336,12 @@
       <c r="J578" t="inlineStr"/>
       <c r="K578" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L578" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33430,12 +33394,12 @@
       <c r="J579" t="inlineStr"/>
       <c r="K579" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33483,12 +33447,12 @@
       <c r="J580" t="inlineStr"/>
       <c r="K580" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L580" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33536,12 +33500,12 @@
       <c r="J581" t="inlineStr"/>
       <c r="K581" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L581" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33589,12 +33553,12 @@
       <c r="J582" t="inlineStr"/>
       <c r="K582" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L582" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33642,12 +33606,12 @@
       <c r="J583" t="inlineStr"/>
       <c r="K583" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L583" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33695,12 +33659,12 @@
       <c r="J584" t="inlineStr"/>
       <c r="K584" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33748,12 +33712,12 @@
       <c r="J585" t="inlineStr"/>
       <c r="K585" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L585" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33801,12 +33765,12 @@
       <c r="J586" t="inlineStr"/>
       <c r="K586" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L586" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33854,12 +33818,12 @@
       <c r="J587" t="inlineStr"/>
       <c r="K587" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L587" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33907,12 +33871,12 @@
       <c r="J588" t="inlineStr"/>
       <c r="K588" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -33960,12 +33924,12 @@
       <c r="J589" t="inlineStr"/>
       <c r="K589" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L589" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34013,12 +33977,12 @@
       <c r="J590" t="inlineStr"/>
       <c r="K590" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L590" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34066,12 +34030,12 @@
       <c r="J591" t="inlineStr"/>
       <c r="K591" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L591" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34119,12 +34083,12 @@
       <c r="J592" t="inlineStr"/>
       <c r="K592" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L592" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34176,12 +34140,12 @@
       </c>
       <c r="K593" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M593" t="inlineStr">
         <is>
-          <t>2 days, 23:04:53.522487</t>
+          <t>1 day, 23:04:19.087105</t>
         </is>
       </c>
     </row>
@@ -34229,12 +34193,12 @@
       <c r="J594" t="inlineStr"/>
       <c r="K594" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L594" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34282,12 +34246,12 @@
       <c r="J595" t="inlineStr"/>
       <c r="K595" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34335,12 +34299,12 @@
       <c r="J596" t="inlineStr"/>
       <c r="K596" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L596" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34388,12 +34352,12 @@
       <c r="J597" t="inlineStr"/>
       <c r="K597" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34441,12 +34405,12 @@
       <c r="J598" t="inlineStr"/>
       <c r="K598" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34494,12 +34458,12 @@
       <c r="J599" t="inlineStr"/>
       <c r="K599" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34547,12 +34511,12 @@
       <c r="J600" t="inlineStr"/>
       <c r="K600" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34600,12 +34564,12 @@
       <c r="J601" t="inlineStr"/>
       <c r="K601" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34653,12 +34617,12 @@
       <c r="J602" t="inlineStr"/>
       <c r="K602" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34706,12 +34670,12 @@
       <c r="J603" t="inlineStr"/>
       <c r="K603" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34759,12 +34723,12 @@
       <c r="J604" t="inlineStr"/>
       <c r="K604" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34812,12 +34776,12 @@
       <c r="J605" t="inlineStr"/>
       <c r="K605" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34865,12 +34829,12 @@
       <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34923,12 +34887,12 @@
       <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -34981,12 +34945,12 @@
       <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35039,12 +35003,12 @@
       <c r="J609" t="inlineStr"/>
       <c r="K609" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35097,12 +35061,12 @@
       <c r="J610" t="inlineStr"/>
       <c r="K610" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35155,12 +35119,12 @@
       <c r="J611" t="inlineStr"/>
       <c r="K611" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35213,12 +35177,12 @@
       <c r="J612" t="inlineStr"/>
       <c r="K612" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L612" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35271,12 +35235,12 @@
       <c r="J613" t="inlineStr"/>
       <c r="K613" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35324,12 +35288,12 @@
       <c r="J614" t="inlineStr"/>
       <c r="K614" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L614" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35377,12 +35341,12 @@
       <c r="J615" t="inlineStr"/>
       <c r="K615" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35435,12 +35399,12 @@
       <c r="J616" t="inlineStr"/>
       <c r="K616" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35493,12 +35457,12 @@
       <c r="J617" t="inlineStr"/>
       <c r="K617" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35551,12 +35515,12 @@
       <c r="J618" t="inlineStr"/>
       <c r="K618" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35609,12 +35573,12 @@
       <c r="J619" t="inlineStr"/>
       <c r="K619" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35667,12 +35631,12 @@
       <c r="J620" t="inlineStr"/>
       <c r="K620" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35725,12 +35689,12 @@
       <c r="J621" t="inlineStr"/>
       <c r="K621" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35783,12 +35747,12 @@
       <c r="J622" t="inlineStr"/>
       <c r="K622" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35841,12 +35805,12 @@
       <c r="J623" t="inlineStr"/>
       <c r="K623" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35899,12 +35863,12 @@
       <c r="J624" t="inlineStr"/>
       <c r="K624" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -35957,12 +35921,12 @@
       <c r="J625" t="inlineStr"/>
       <c r="K625" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36015,12 +35979,12 @@
       <c r="J626" t="inlineStr"/>
       <c r="K626" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L626" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36068,12 +36032,12 @@
       <c r="J627" t="inlineStr"/>
       <c r="K627" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L627" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36121,12 +36085,12 @@
       <c r="J628" t="inlineStr"/>
       <c r="K628" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36174,12 +36138,12 @@
       <c r="J629" t="inlineStr"/>
       <c r="K629" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L629" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36227,12 +36191,12 @@
       <c r="J630" t="inlineStr"/>
       <c r="K630" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36280,12 +36244,12 @@
       <c r="J631" t="inlineStr"/>
       <c r="K631" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36333,12 +36297,12 @@
       <c r="J632" t="inlineStr"/>
       <c r="K632" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L632" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36386,12 +36350,12 @@
       <c r="J633" t="inlineStr"/>
       <c r="K633" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36439,12 +36403,12 @@
       <c r="J634" t="inlineStr"/>
       <c r="K634" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L634" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36492,12 +36456,12 @@
       <c r="J635" t="inlineStr"/>
       <c r="K635" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L635" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36545,12 +36509,12 @@
       <c r="J636" t="inlineStr"/>
       <c r="K636" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L636" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36598,12 +36562,12 @@
       <c r="J637" t="inlineStr"/>
       <c r="K637" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L637" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36651,12 +36615,12 @@
       <c r="J638" t="inlineStr"/>
       <c r="K638" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L638" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36704,12 +36668,12 @@
       <c r="J639" t="inlineStr"/>
       <c r="K639" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L639" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36757,12 +36721,12 @@
       <c r="J640" t="inlineStr"/>
       <c r="K640" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L640" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36810,12 +36774,12 @@
       <c r="J641" t="inlineStr"/>
       <c r="K641" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L641" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36863,12 +36827,12 @@
       <c r="J642" t="inlineStr"/>
       <c r="K642" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36916,12 +36880,12 @@
       <c r="J643" t="inlineStr"/>
       <c r="K643" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L643" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -36969,12 +36933,12 @@
       <c r="J644" t="inlineStr"/>
       <c r="K644" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L644" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -37022,12 +36986,12 @@
       <c r="J645" t="inlineStr"/>
       <c r="K645" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L645" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -37075,12 +37039,12 @@
       <c r="J646" t="inlineStr"/>
       <c r="K646" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -37128,12 +37092,12 @@
       <c r="J647" t="inlineStr"/>
       <c r="K647" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -37181,12 +37145,12 @@
       <c r="J648" t="inlineStr"/>
       <c r="K648" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L648" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -37234,12 +37198,12 @@
       <c r="J649" t="inlineStr"/>
       <c r="K649" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L649" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -37287,12 +37251,12 @@
       <c r="J650" t="inlineStr"/>
       <c r="K650" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L650" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -37340,12 +37304,12 @@
       <c r="J651" t="inlineStr"/>
       <c r="K651" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L651" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -37393,12 +37357,12 @@
       <c r="J652" t="inlineStr"/>
       <c r="K652" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L652" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>
@@ -37446,12 +37410,12 @@
       <c r="J653" t="inlineStr"/>
       <c r="K653" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
         <is>
-          <t>07/31/26 12:25 PM</t>
+          <t>08/01/26 12:25 PM</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M624"/>
+  <dimension ref="A1:M623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -542,12 +542,12 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -592,19 +592,15 @@
           <t>08/31/26 07:00 am</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>COMDC - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>21 days, 19:33:37.249049</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -656,12 +652,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248995</t>
+          <t>20 days, 18:54:26.938390</t>
         </is>
       </c>
     </row>
@@ -713,17 +709,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ATT01, COMDC, MCI03, PEPCODC, QGS06, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>ATT01, COMDC, MCI03, PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248947</t>
+          <t>20 days, 18:54:26.938329</t>
         </is>
       </c>
     </row>
@@ -775,17 +771,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ATT01, MCI03, PEPCODC, QGS06, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>ATT01, MCI03, PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248908</t>
+          <t>20 days, 18:54:26.938284</t>
         </is>
       </c>
     </row>
@@ -837,17 +833,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>MCI03, PEPCODC, QGS06, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>MCI03, PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248817</t>
+          <t>20 days, 18:54:26.938245</t>
         </is>
       </c>
     </row>
@@ -899,17 +895,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>MCI03, PEPCODC, QGS06, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>MCI03, PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248771</t>
+          <t>20 days, 18:54:26.938207</t>
         </is>
       </c>
     </row>
@@ -961,17 +957,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>MCI03, PEPCODC, QGS06, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>MCI03, PEPCODC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248733</t>
+          <t>20 days, 18:54:26.938170</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1024,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248700</t>
+          <t>20 days, 18:54:26.938138</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1086,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248662</t>
+          <t>20 days, 18:54:26.938099</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1148,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248628</t>
+          <t>20 days, 18:54:26.938065</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1210,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248593</t>
+          <t>20 days, 18:54:26.938031</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1272,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248557</t>
+          <t>20 days, 18:54:26.937994</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1334,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248522</t>
+          <t>20 days, 18:54:26.937958</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1396,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248488</t>
+          <t>20 days, 18:54:26.937924</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1458,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248457</t>
+          <t>20 days, 18:54:26.937889</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1520,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248426</t>
+          <t>20 days, 18:54:26.937856</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1582,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248395</t>
+          <t>20 days, 18:54:26.937824</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1644,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248363</t>
+          <t>20 days, 18:54:26.937790</t>
         </is>
       </c>
     </row>
@@ -1710,12 +1706,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248330</t>
+          <t>20 days, 18:54:26.937755</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1768,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248297</t>
+          <t>20 days, 18:54:26.937720</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1830,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248265</t>
+          <t>20 days, 18:54:26.937685</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1892,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248235</t>
+          <t>20 days, 18:54:26.937653</t>
         </is>
       </c>
     </row>
@@ -1958,12 +1954,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248205</t>
+          <t>20 days, 18:54:26.937621</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2016,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248175</t>
+          <t>20 days, 18:54:26.937591</t>
         </is>
       </c>
     </row>
@@ -2082,12 +2078,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248145</t>
+          <t>20 days, 18:54:26.937559</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2140,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248113</t>
+          <t>20 days, 18:54:26.937527</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2202,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248082</t>
+          <t>20 days, 18:54:26.937495</t>
         </is>
       </c>
     </row>
@@ -2268,12 +2264,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248051</t>
+          <t>20 days, 18:54:26.937435</t>
         </is>
       </c>
     </row>
@@ -2330,12 +2326,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.248017</t>
+          <t>20 days, 18:54:26.937395</t>
         </is>
       </c>
     </row>
@@ -2392,12 +2388,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247984</t>
+          <t>20 days, 18:54:26.937359</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2450,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247954</t>
+          <t>20 days, 18:54:26.937326</t>
         </is>
       </c>
     </row>
@@ -2516,12 +2512,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247923</t>
+          <t>20 days, 18:54:26.937295</t>
         </is>
       </c>
     </row>
@@ -2578,12 +2574,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247874</t>
+          <t>20 days, 18:54:26.937263</t>
         </is>
       </c>
     </row>
@@ -2640,12 +2636,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247833</t>
+          <t>20 days, 18:54:26.937230</t>
         </is>
       </c>
     </row>
@@ -2702,12 +2698,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247797</t>
+          <t>20 days, 18:54:26.937197</t>
         </is>
       </c>
     </row>
@@ -2764,12 +2760,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247762</t>
+          <t>20 days, 18:54:26.937166</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2822,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247727</t>
+          <t>20 days, 18:54:26.937134</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2884,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247694</t>
+          <t>20 days, 18:54:26.937102</t>
         </is>
       </c>
     </row>
@@ -2950,12 +2946,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247663</t>
+          <t>20 days, 18:54:26.937071</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3008,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247626</t>
+          <t>20 days, 18:54:26.937035</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3070,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247592</t>
+          <t>20 days, 18:54:26.937000</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3132,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247559</t>
+          <t>20 days, 18:54:26.936967</t>
         </is>
       </c>
     </row>
@@ -3198,12 +3194,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247526</t>
+          <t>20 days, 18:54:26.936935</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3256,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247493</t>
+          <t>20 days, 18:54:26.936901</t>
         </is>
       </c>
     </row>
@@ -3322,12 +3318,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247461</t>
+          <t>20 days, 18:54:26.936868</t>
         </is>
       </c>
     </row>
@@ -3384,12 +3380,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247428</t>
+          <t>20 days, 18:54:26.936833</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3442,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247395</t>
+          <t>20 days, 18:54:26.936796</t>
         </is>
       </c>
     </row>
@@ -3508,12 +3504,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247362</t>
+          <t>20 days, 18:54:26.936761</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3566,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247332</t>
+          <t>20 days, 18:54:26.936729</t>
         </is>
       </c>
     </row>
@@ -3632,12 +3628,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247301</t>
+          <t>20 days, 18:54:26.936696</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3690,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247270</t>
+          <t>20 days, 18:54:26.936663</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3752,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247234</t>
+          <t>20 days, 18:54:26.936624</t>
         </is>
       </c>
     </row>
@@ -3818,12 +3814,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247200</t>
+          <t>20 days, 18:54:26.936588</t>
         </is>
       </c>
     </row>
@@ -3880,12 +3876,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247165</t>
+          <t>20 days, 18:54:26.936554</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3938,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247131</t>
+          <t>20 days, 18:54:26.936518</t>
         </is>
       </c>
     </row>
@@ -4004,12 +4000,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247096</t>
+          <t>20 days, 18:54:26.936458</t>
         </is>
       </c>
     </row>
@@ -4066,12 +4062,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247062</t>
+          <t>20 days, 18:54:26.936420</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4124,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.247028</t>
+          <t>20 days, 18:54:26.936382</t>
         </is>
       </c>
     </row>
@@ -4190,12 +4186,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.246994</t>
+          <t>20 days, 18:54:26.936346</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4248,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.246958</t>
+          <t>20 days, 18:54:26.936307</t>
         </is>
       </c>
     </row>
@@ -4314,12 +4310,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.246924</t>
+          <t>20 days, 18:54:26.936273</t>
         </is>
       </c>
     </row>
@@ -4376,12 +4372,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.246872</t>
+          <t>20 days, 18:54:26.936236</t>
         </is>
       </c>
     </row>
@@ -4438,12 +4434,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.246833</t>
+          <t>20 days, 18:54:26.936201</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4496,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.246792</t>
+          <t>20 days, 18:54:26.936156</t>
         </is>
       </c>
     </row>
@@ -4562,12 +4558,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.246755</t>
+          <t>20 days, 18:54:26.936116</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4620,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>21 days, 19:33:37.246719</t>
+          <t>20 days, 18:54:26.936077</t>
         </is>
       </c>
     </row>
@@ -4681,12 +4677,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>19 days, 3:03:37.246688</t>
+          <t>18 days, 2:24:26.936043</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4734,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>19 days, 3:03:37.246657</t>
+          <t>18 days, 2:24:26.936011</t>
         </is>
       </c>
     </row>
@@ -4795,12 +4791,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>19 days, 3:03:37.246627</t>
+          <t>18 days, 2:24:26.935979</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4848,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>19 days, 3:03:37.246597</t>
+          <t>18 days, 2:24:26.935947</t>
         </is>
       </c>
     </row>
@@ -4909,12 +4905,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>19 days, 0:33:37.246562</t>
+          <t>17 days, 23:54:26.935909</t>
         </is>
       </c>
     </row>
@@ -4966,12 +4962,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>19 days, 0:33:37.246527</t>
+          <t>17 days, 23:54:26.935872</t>
         </is>
       </c>
     </row>
@@ -5018,17 +5014,17 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>APW03, PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>18 days, 23:48:37.246494</t>
+          <t>17 days, 23:09:26.935836</t>
         </is>
       </c>
     </row>
@@ -5075,17 +5071,17 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>APW03, PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>18 days, 23:48:37.246463</t>
+          <t>17 days, 23:09:26.935801</t>
         </is>
       </c>
     </row>
@@ -5132,17 +5128,17 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>APW03, PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>18 days, 23:48:37.246433</t>
+          <t>17 days, 23:09:26.935768</t>
         </is>
       </c>
     </row>
@@ -5189,17 +5185,17 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>APW03, PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>18 days, 23:48:37.246402</t>
+          <t>17 days, 23:09:26.935735</t>
         </is>
       </c>
     </row>
@@ -5246,17 +5242,17 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>APW03, PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>18 days, 23:48:37.246370</t>
+          <t>17 days, 23:09:26.935700</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5299,17 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>APW03, PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>18 days, 23:48:37.246338</t>
+          <t>17 days, 23:09:26.935665</t>
         </is>
       </c>
     </row>
@@ -5360,17 +5356,17 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>APW03, PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>18 days, 23:48:37.246305</t>
+          <t>17 days, 23:09:26.935631</t>
         </is>
       </c>
     </row>
@@ -5417,17 +5413,17 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>APW03, PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>18 days, 23:48:37.246274</t>
+          <t>17 days, 23:09:26.935597</t>
         </is>
       </c>
     </row>
@@ -5474,17 +5470,17 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>APW03, PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
+          <t>PEPCODC, VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>18 days, 23:48:37.246243</t>
+          <t>17 days, 23:09:26.935563</t>
         </is>
       </c>
     </row>
@@ -5536,12 +5532,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>18 days, 23:33:37.246210</t>
+          <t>17 days, 22:54:26.935529</t>
         </is>
       </c>
     </row>
@@ -5593,12 +5589,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>18 days, 23:33:37.246178</t>
+          <t>17 days, 22:54:26.935479</t>
         </is>
       </c>
     </row>
@@ -5650,12 +5646,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>18 days, 23:33:37.246147</t>
+          <t>17 days, 22:54:26.935439</t>
         </is>
       </c>
     </row>
@@ -5707,12 +5703,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>18 days, 23:33:37.246118</t>
+          <t>17 days, 22:54:26.935407</t>
         </is>
       </c>
     </row>
@@ -5764,12 +5760,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>18 days, 23:33:37.246087</t>
+          <t>17 days, 22:54:26.935375</t>
         </is>
       </c>
     </row>
@@ -5821,12 +5817,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.246053</t>
+          <t>17 days, 21:54:26.935340</t>
         </is>
       </c>
     </row>
@@ -5878,12 +5874,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.246020</t>
+          <t>17 days, 21:54:26.935303</t>
         </is>
       </c>
     </row>
@@ -5935,12 +5931,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245986</t>
+          <t>17 days, 21:54:26.935266</t>
         </is>
       </c>
     </row>
@@ -5992,12 +5988,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245952</t>
+          <t>17 days, 21:54:26.935231</t>
         </is>
       </c>
     </row>
@@ -6049,12 +6045,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245919</t>
+          <t>17 days, 21:54:26.935195</t>
         </is>
       </c>
     </row>
@@ -6106,12 +6102,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245863</t>
+          <t>17 days, 21:54:26.935161</t>
         </is>
       </c>
     </row>
@@ -6163,12 +6159,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245822</t>
+          <t>17 days, 21:54:26.935125</t>
         </is>
       </c>
     </row>
@@ -6220,12 +6216,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245785</t>
+          <t>17 days, 21:54:26.935089</t>
         </is>
       </c>
     </row>
@@ -6277,12 +6273,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245749</t>
+          <t>17 days, 21:54:26.935052</t>
         </is>
       </c>
     </row>
@@ -6334,12 +6330,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245715</t>
+          <t>17 days, 21:54:26.935017</t>
         </is>
       </c>
     </row>
@@ -6391,12 +6387,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245681</t>
+          <t>17 days, 21:54:26.934982</t>
         </is>
       </c>
     </row>
@@ -6448,12 +6444,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245648</t>
+          <t>17 days, 21:54:26.934947</t>
         </is>
       </c>
     </row>
@@ -6505,12 +6501,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245613</t>
+          <t>17 days, 21:54:26.934911</t>
         </is>
       </c>
     </row>
@@ -6562,12 +6558,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245580</t>
+          <t>17 days, 21:54:26.934876</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6615,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245546</t>
+          <t>17 days, 21:54:26.934841</t>
         </is>
       </c>
     </row>
@@ -6676,12 +6672,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245512</t>
+          <t>17 days, 21:54:26.934806</t>
         </is>
       </c>
     </row>
@@ -6733,12 +6729,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245477</t>
+          <t>17 days, 21:54:26.934771</t>
         </is>
       </c>
     </row>
@@ -6790,12 +6786,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245444</t>
+          <t>17 days, 21:54:26.934736</t>
         </is>
       </c>
     </row>
@@ -6847,12 +6843,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245410</t>
+          <t>17 days, 21:54:26.934700</t>
         </is>
       </c>
     </row>
@@ -6904,12 +6900,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245376</t>
+          <t>17 days, 21:54:26.934664</t>
         </is>
       </c>
     </row>
@@ -6961,12 +6957,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>18 days, 22:33:37.245343</t>
+          <t>17 days, 21:54:26.934629</t>
         </is>
       </c>
     </row>
@@ -7014,12 +7010,12 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7037,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7064,19 +7060,15 @@
           <t>08/28/26 07:00 am</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>COMDC - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>18 days, 19:33:37.245265</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -7128,12 +7120,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>18 days, 19:33:37.245228</t>
+          <t>17 days, 18:54:26.934511</t>
         </is>
       </c>
     </row>
@@ -7185,12 +7177,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>18 days, 0:33:37.245191</t>
+          <t>16 days, 23:54:26.934444</t>
         </is>
       </c>
     </row>
@@ -7247,12 +7239,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>17 days, 23:18:37.245156</t>
+          <t>16 days, 22:39:26.934395</t>
         </is>
       </c>
     </row>
@@ -7309,12 +7301,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>17 days, 23:03:37.245123</t>
+          <t>16 days, 22:24:26.934359</t>
         </is>
       </c>
     </row>
@@ -7362,12 +7354,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>17 days, 23:03:37.245090</t>
+          <t>16 days, 22:24:26.934325</t>
         </is>
       </c>
     </row>
@@ -7415,12 +7407,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>18 days, 0:18:37.245057</t>
+          <t>16 days, 23:39:26.934292</t>
         </is>
       </c>
     </row>
@@ -7468,12 +7460,12 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>17 days, 23:03:37.245021</t>
+          <t>16 days, 22:24:26.934255</t>
         </is>
       </c>
     </row>
@@ -7521,12 +7513,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>17 days, 23:03:37.244986</t>
+          <t>16 days, 22:24:26.934219</t>
         </is>
       </c>
     </row>
@@ -7574,12 +7566,12 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -7627,12 +7619,12 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7672,12 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -7733,12 +7725,12 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -7791,12 +7783,12 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -7849,12 +7841,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -7907,12 +7899,12 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -7964,12 +7956,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>16 days, 23:18:37.244698</t>
+          <t>15 days, 22:39:26.933965</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8013,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>16 days, 23:18:37.244664</t>
+          <t>15 days, 22:39:26.933931</t>
         </is>
       </c>
     </row>
@@ -8078,12 +8070,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>16 days, 23:18:37.244631</t>
+          <t>15 days, 22:39:26.933898</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8127,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>16 days, 23:18:37.244598</t>
+          <t>15 days, 22:39:26.933864</t>
         </is>
       </c>
     </row>
@@ -8192,12 +8184,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>16 days, 23:18:37.244564</t>
+          <t>15 days, 22:39:26.933830</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8241,12 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>16 days, 23:18:37.244532</t>
+          <t>15 days, 22:39:26.933799</t>
         </is>
       </c>
     </row>
@@ -8306,12 +8298,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>16 days, 23:18:37.244500</t>
+          <t>15 days, 22:39:26.933767</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8355,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>16 days, 23:18:37.244466</t>
+          <t>15 days, 22:39:26.933733</t>
         </is>
       </c>
     </row>
@@ -8420,12 +8412,12 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>16 days, 23:18:37.244434</t>
+          <t>15 days, 22:39:26.933702</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8469,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>16 days, 23:18:37.244400</t>
+          <t>15 days, 22:39:26.933669</t>
         </is>
       </c>
     </row>
@@ -8534,12 +8526,12 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>16 days, 23:18:37.244368</t>
+          <t>15 days, 22:39:26.933636</t>
         </is>
       </c>
     </row>
@@ -8586,17 +8578,17 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; TMN04, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; TMN04 - 24-hour delay &amp; VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>16 days, 23:03:37.244330</t>
+          <t>15 days, 22:24:26.933596</t>
         </is>
       </c>
     </row>
@@ -8643,17 +8635,17 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>16 days, 23:03:37.244294</t>
+          <t>15 days, 22:24:26.933557</t>
         </is>
       </c>
     </row>
@@ -8700,17 +8692,17 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>16 days, 23:03:37.244258</t>
+          <t>15 days, 22:24:26.933521</t>
         </is>
       </c>
     </row>
@@ -8757,17 +8749,17 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; TMN04, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; TMN04 - 24-hour delay &amp; VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>16 days, 23:03:37.244219</t>
+          <t>15 days, 22:24:26.933455</t>
         </is>
       </c>
     </row>
@@ -8814,17 +8806,17 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>16 days, 23:03:37.244184</t>
+          <t>15 days, 22:24:26.933415</t>
         </is>
       </c>
     </row>
@@ -8871,17 +8863,17 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>16 days, 23:03:37.244149</t>
+          <t>15 days, 22:24:26.933377</t>
         </is>
       </c>
     </row>
@@ -8928,17 +8920,17 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>VDC &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>16 days, 23:03:37.244116</t>
+          <t>15 days, 22:24:26.933341</t>
         </is>
       </c>
     </row>
@@ -8990,12 +8982,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>16 days, 22:48:37.244083</t>
+          <t>15 days, 22:09:26.933307</t>
         </is>
       </c>
     </row>
@@ -9047,12 +9039,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>16 days, 22:48:37.244050</t>
+          <t>15 days, 22:09:26.933271</t>
         </is>
       </c>
     </row>
@@ -9104,12 +9096,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>16 days, 22:48:37.244017</t>
+          <t>15 days, 22:09:26.933237</t>
         </is>
       </c>
     </row>
@@ -9161,12 +9153,12 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>16 days, 22:48:37.243985</t>
+          <t>15 days, 22:09:26.933203</t>
         </is>
       </c>
     </row>
@@ -9218,12 +9210,12 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>16 days, 22:48:37.243953</t>
+          <t>15 days, 22:09:26.933168</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9267,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>16 days, 22:48:37.243920</t>
+          <t>15 days, 22:09:26.933133</t>
         </is>
       </c>
     </row>
@@ -9332,12 +9324,12 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>16 days, 22:48:37.243867</t>
+          <t>15 days, 22:09:26.933099</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9381,12 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>16 days, 22:48:37.243829</t>
+          <t>15 days, 22:09:26.933065</t>
         </is>
       </c>
     </row>
@@ -9446,12 +9438,12 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>16 days, 22:48:37.243794</t>
+          <t>15 days, 22:09:26.933031</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9495,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>16 days, 22:48:37.243762</t>
+          <t>15 days, 22:09:26.932999</t>
         </is>
       </c>
     </row>
@@ -9560,12 +9552,12 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>15 days, 22:33:37.243730</t>
+          <t>14 days, 21:54:26.932965</t>
         </is>
       </c>
     </row>
@@ -9613,12 +9605,12 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -9666,12 +9658,12 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -9728,12 +9720,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>15 days, 19:33:37.243636</t>
+          <t>14 days, 18:54:26.932861</t>
         </is>
       </c>
     </row>
@@ -9786,12 +9778,12 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -9844,12 +9836,12 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -9902,12 +9894,12 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -9964,12 +9956,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>15 days, 19:33:37.243521</t>
+          <t>14 days, 18:54:26.932740</t>
         </is>
       </c>
     </row>
@@ -10022,12 +10014,12 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -10080,12 +10072,12 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -10138,12 +10130,12 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -10195,12 +10187,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>14 days, 23:48:37.243414</t>
+          <t>13 days, 23:09:26.932628</t>
         </is>
       </c>
     </row>
@@ -10222,7 +10214,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10245,19 +10237,15 @@
           <t>08/24/26 07:00 am</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>WASA02 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>14 days, 19:33:37.243377</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -10309,12 +10297,12 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>14 days, 19:33:37.243343</t>
+          <t>13 days, 18:54:26.932559</t>
         </is>
       </c>
     </row>
@@ -10366,12 +10354,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>14 days, 19:33:37.243308</t>
+          <t>13 days, 18:54:26.932520</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10381,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10416,19 +10404,15 @@
           <t>08/24/26 07:00 am</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>WASA02 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>14 days, 19:33:37.243271</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10434,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10473,19 +10457,15 @@
           <t>08/24/26 07:00 am</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>WASA02 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>14 days, 19:33:37.243232</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -10537,12 +10517,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>14 days, 19:33:37.243194</t>
+          <t>13 days, 18:54:26.932388</t>
         </is>
       </c>
     </row>
@@ -10590,12 +10570,12 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -10643,12 +10623,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10676,12 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -10749,12 +10729,12 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -10802,12 +10782,12 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -10855,12 +10835,12 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -10908,12 +10888,12 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -10961,12 +10941,12 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11014,12 +10994,12 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11067,12 +11047,12 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11120,12 +11100,12 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11173,12 +11153,12 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11226,12 +11206,12 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11279,12 +11259,12 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11332,12 +11312,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11365,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11438,12 +11418,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11491,12 +11471,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11544,12 +11524,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11597,12 +11577,12 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11650,12 +11630,12 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11703,12 +11683,12 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11756,12 +11736,12 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11809,12 +11789,12 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11862,12 +11842,12 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11915,12 +11895,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -11968,12 +11948,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12021,12 +12001,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12054,12 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12131,12 +12111,12 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>10 days, 23:33:37.242298</t>
+          <t>9 days, 22:54:26.931466</t>
         </is>
       </c>
     </row>
@@ -12158,7 +12138,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12181,19 +12161,15 @@
           <t>08/20/26 11:00 am</t>
         </is>
       </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>VDC &amp; WGL07 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>10 days, 23:33:37.242259</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12241,12 +12217,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12294,12 +12270,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12347,12 +12323,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12399,17 +12375,17 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>VDC &amp; WGL07 - Not complete/In progress</t>
+          <t>WGL07 - Dispute - Status Pending</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>10 days, 23:33:37.242131</t>
+          <t>9 days, 22:54:26.931300</t>
         </is>
       </c>
     </row>
@@ -12457,12 +12433,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12510,12 +12486,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12563,12 +12539,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12621,12 +12597,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12678,12 +12654,12 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>10 days, 21:03:37.241977</t>
+          <t>9 days, 20:24:26.931140</t>
         </is>
       </c>
     </row>
@@ -12735,12 +12711,12 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>10 days, 19:33:37.241936</t>
+          <t>9 days, 18:54:26.931098</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12764,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12841,12 +12817,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12894,12 +12870,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -12947,12 +12923,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13000,12 +12976,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13058,12 +13034,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13116,12 +13092,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13150,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13232,12 +13208,12 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13290,12 +13266,12 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13348,12 +13324,12 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13406,12 +13382,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13459,12 +13435,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13512,12 +13488,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13565,12 +13541,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13618,12 +13594,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13671,12 +13647,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13724,12 +13700,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13777,12 +13753,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13830,12 +13806,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13883,12 +13859,12 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13936,12 +13912,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -13989,12 +13965,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14016,7 +13992,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -14039,19 +14015,15 @@
           <t>08/19/26 09:45 am</t>
         </is>
       </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>WGL07 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>9 days, 22:18:37.241213</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14073,7 +14045,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -14096,19 +14068,15 @@
           <t>08/19/26 09:45 am</t>
         </is>
       </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>WGL07 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>9 days, 22:18:37.241177</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14098,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -14153,19 +14121,15 @@
           <t>08/19/26 09:45 am</t>
         </is>
       </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>WGL07 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>9 days, 22:18:37.241145</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14218,12 +14182,12 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14276,12 +14240,12 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14334,12 +14298,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14392,12 +14356,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14450,12 +14414,12 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14508,12 +14472,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14566,12 +14530,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14624,12 +14588,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14682,12 +14646,12 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14740,12 +14704,12 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14798,12 +14762,12 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14856,12 +14820,12 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14914,12 +14878,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -14972,12 +14936,12 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15030,12 +14994,12 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15088,12 +15052,12 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15146,12 +15110,12 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15204,12 +15168,12 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15262,12 +15226,12 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15320,12 +15284,12 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15378,12 +15342,12 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15436,12 +15400,12 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15494,12 +15458,12 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15547,12 +15511,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15600,12 +15564,12 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15658,12 +15622,12 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15716,12 +15680,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15743,7 +15707,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -15771,19 +15735,15 @@
           <t>08/18/26 04:00 pm</t>
         </is>
       </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>WGL07 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>9 days, 4:33:37.240302</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15836,12 +15796,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15894,12 +15854,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -15952,12 +15912,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16010,12 +15970,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16068,12 +16028,12 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16126,12 +16086,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16184,12 +16144,12 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16242,12 +16202,12 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16300,12 +16260,12 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16353,12 +16313,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16406,12 +16366,12 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16459,12 +16419,12 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16512,12 +16472,12 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16565,12 +16525,12 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16618,12 +16578,12 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16671,12 +16631,12 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16724,12 +16684,12 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16777,12 +16737,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16830,12 +16790,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16883,12 +16843,12 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16936,12 +16896,12 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -16989,12 +16949,12 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17042,12 +17002,12 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17095,12 +17055,12 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17148,12 +17108,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17201,12 +17161,12 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17254,12 +17214,12 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17307,12 +17267,12 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17360,12 +17320,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17413,12 +17373,12 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17466,12 +17426,12 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17519,12 +17479,12 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17532,12 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17625,12 +17585,12 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17678,12 +17638,12 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17731,12 +17691,12 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17784,12 +17744,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17837,12 +17797,12 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17890,12 +17850,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17943,12 +17903,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -17996,12 +17956,12 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18049,12 +18009,12 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18102,12 +18062,12 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18155,12 +18115,12 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18208,12 +18168,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18261,12 +18221,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18314,12 +18274,12 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18327,12 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18424,12 +18384,12 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>9 days, 2:33:37.238920</t>
+          <t>8 days, 1:54:26.928100</t>
         </is>
       </c>
     </row>
@@ -18477,12 +18437,12 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18535,12 +18495,12 @@
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18593,12 +18553,12 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18651,12 +18611,12 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18704,12 +18664,12 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18762,12 +18722,12 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18820,12 +18780,12 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18878,12 +18838,12 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18896,12 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -18994,12 +18954,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19052,12 +19012,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19110,12 +19070,12 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19168,12 +19128,12 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19226,12 +19186,12 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19288,12 +19248,12 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>8 days, 20:03:37.238450</t>
+          <t>7 days, 19:24:26.927652</t>
         </is>
       </c>
     </row>
@@ -19346,12 +19306,12 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19404,12 +19364,12 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19461,12 +19421,12 @@
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>8 days, 20:03:37.238343</t>
+          <t>7 days, 19:24:26.927543</t>
         </is>
       </c>
     </row>
@@ -19519,12 +19479,12 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19577,12 +19537,12 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19635,12 +19595,12 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19693,12 +19653,12 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19751,12 +19711,12 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19809,12 +19769,12 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19867,12 +19827,12 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19925,12 +19885,12 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -19978,12 +19938,12 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20031,12 +19991,12 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20084,12 +20044,12 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20137,12 +20097,12 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20190,12 +20150,12 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20243,12 +20203,12 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20296,12 +20256,12 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20349,12 +20309,12 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20402,12 +20362,12 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20455,12 +20415,12 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20508,12 +20468,12 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20561,12 +20521,12 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20619,12 +20579,12 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20677,12 +20637,12 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20735,12 +20695,12 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20793,12 +20753,12 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20851,12 +20811,12 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20909,12 +20869,12 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -20967,12 +20927,12 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21025,12 +20985,12 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21083,12 +21043,12 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21141,12 +21101,12 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21199,12 +21159,12 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21257,12 +21217,12 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21310,12 +21270,12 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21363,12 +21323,12 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21420,12 +21380,12 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>8 days, 3:03:37.237320</t>
+          <t>7 days, 2:24:26.926415</t>
         </is>
       </c>
     </row>
@@ -21473,12 +21433,12 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21526,12 +21486,12 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21579,12 +21539,12 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21632,12 +21592,12 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21685,12 +21645,12 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21738,12 +21698,12 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21791,12 +21751,12 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21849,12 +21809,12 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21907,12 +21867,12 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -21965,12 +21925,12 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22023,12 +21983,12 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22081,12 +22041,12 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22139,12 +22099,12 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22197,12 +22157,12 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22255,12 +22215,12 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22313,12 +22273,12 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22371,12 +22331,12 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22429,12 +22389,12 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22487,12 +22447,12 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22545,12 +22505,12 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22603,12 +22563,12 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22661,12 +22621,12 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22719,12 +22679,12 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22777,12 +22737,12 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22835,12 +22795,12 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22893,12 +22853,12 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -22951,12 +22911,12 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23009,12 +22969,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23067,12 +23027,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23125,12 +23085,12 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23183,12 +23143,12 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23241,12 +23201,12 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23294,12 +23254,12 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23352,12 +23312,12 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23410,12 +23370,12 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23468,12 +23428,12 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23526,12 +23486,12 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23584,12 +23544,12 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23642,12 +23602,12 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23700,12 +23660,12 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23758,12 +23718,12 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23816,12 +23776,12 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23874,12 +23834,12 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23932,12 +23892,12 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -23990,12 +23950,12 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24048,12 +24008,12 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24106,12 +24066,12 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24164,12 +24124,12 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24222,12 +24182,12 @@
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24280,12 +24240,12 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24338,12 +24298,12 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24396,12 +24356,12 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24454,12 +24414,12 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24512,12 +24472,12 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24570,12 +24530,12 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24628,12 +24588,12 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24686,12 +24646,12 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24744,12 +24704,12 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24802,12 +24762,12 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24860,12 +24820,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24918,12 +24878,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -24976,12 +24936,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25034,12 +24994,12 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25092,12 +25052,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25150,12 +25110,12 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25208,12 +25168,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25266,12 +25226,12 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25324,12 +25284,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25382,12 +25342,12 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25440,12 +25400,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25498,12 +25458,12 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25556,12 +25516,12 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25614,12 +25574,12 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25672,12 +25632,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25730,12 +25690,12 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25788,12 +25748,12 @@
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25846,12 +25806,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25904,12 +25864,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -25962,12 +25922,12 @@
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26020,12 +25980,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26078,12 +26038,12 @@
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26136,12 +26096,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26194,12 +26154,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26252,12 +26212,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26310,12 +26270,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26368,12 +26328,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26426,12 +26386,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26484,12 +26444,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26542,12 +26502,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26600,12 +26560,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26658,12 +26618,12 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26711,12 +26671,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26769,12 +26729,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26827,12 +26787,12 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26885,12 +26845,12 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -26942,12 +26902,12 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>7 days, 20:03:37.234638</t>
+          <t>6 days, 19:24:26.923658</t>
         </is>
       </c>
     </row>
@@ -26995,12 +26955,12 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27048,12 +27008,12 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27101,12 +27061,12 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27154,12 +27114,12 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27207,12 +27167,12 @@
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27260,12 +27220,12 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27313,12 +27273,12 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27366,12 +27326,12 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27419,12 +27379,12 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27472,12 +27432,12 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27529,12 +27489,12 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>7 days, 19:33:37.234338</t>
+          <t>6 days, 18:54:26.923315</t>
         </is>
       </c>
     </row>
@@ -27582,12 +27542,12 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27640,12 +27600,12 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27698,12 +27658,12 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27756,12 +27716,12 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27814,12 +27774,12 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27872,12 +27832,12 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27930,12 +27890,12 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -27988,12 +27948,12 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -28046,12 +28006,12 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -28104,12 +28064,12 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -28162,12 +28122,12 @@
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -28220,12 +28180,12 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -28273,12 +28233,12 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -28330,12 +28290,12 @@
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>7 days, 19:33:37.233984</t>
+          <t>6 days, 18:54:26.922943</t>
         </is>
       </c>
     </row>
@@ -28387,12 +28347,12 @@
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>7 days, 19:33:37.233947</t>
+          <t>6 days, 18:54:26.922905</t>
         </is>
       </c>
     </row>
@@ -28444,12 +28404,12 @@
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>7 days, 19:33:37.233912</t>
+          <t>6 days, 18:54:26.922869</t>
         </is>
       </c>
     </row>
@@ -28497,12 +28457,12 @@
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -28554,12 +28514,12 @@
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>5 days, 5:18:37.233819</t>
+          <t>4 days, 4:39:26.922796</t>
         </is>
       </c>
     </row>
@@ -28607,12 +28567,12 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -28665,12 +28625,12 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -28723,12 +28683,12 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -28781,12 +28741,12 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -28839,12 +28799,12 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -28897,12 +28857,12 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -28955,12 +28915,12 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29013,12 +28973,12 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29071,12 +29031,12 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29129,12 +29089,12 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29187,12 +29147,12 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29245,12 +29205,12 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29303,12 +29263,12 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29361,12 +29321,12 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29419,12 +29379,12 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29477,12 +29437,12 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29535,12 +29495,12 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29593,12 +29553,12 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29651,12 +29611,12 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29709,12 +29669,12 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29767,12 +29727,12 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29825,12 +29785,12 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29883,12 +29843,12 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29941,12 +29901,12 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -29999,12 +29959,12 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30057,12 +30017,12 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30115,12 +30075,12 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30173,12 +30133,12 @@
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30231,12 +30191,12 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30289,12 +30249,12 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30347,12 +30307,12 @@
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30405,12 +30365,12 @@
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30463,12 +30423,12 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30521,12 +30481,12 @@
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30579,12 +30539,12 @@
       <c r="J529" t="inlineStr"/>
       <c r="K529" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30637,12 +30597,12 @@
       <c r="J530" t="inlineStr"/>
       <c r="K530" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30695,12 +30655,12 @@
       <c r="J531" t="inlineStr"/>
       <c r="K531" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30753,12 +30713,12 @@
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30811,12 +30771,12 @@
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30869,12 +30829,12 @@
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30927,12 +30887,12 @@
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -30985,12 +30945,12 @@
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31043,12 +31003,12 @@
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31101,12 +31061,12 @@
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31159,12 +31119,12 @@
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31217,12 +31177,12 @@
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31275,12 +31235,12 @@
       <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31333,12 +31293,12 @@
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31391,12 +31351,12 @@
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31449,12 +31409,12 @@
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31507,12 +31467,12 @@
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31565,12 +31525,12 @@
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31623,12 +31583,12 @@
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31681,12 +31641,12 @@
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31739,12 +31699,12 @@
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31797,12 +31757,12 @@
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31855,12 +31815,12 @@
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31913,12 +31873,12 @@
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -31971,12 +31931,12 @@
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32029,12 +31989,12 @@
       <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32087,12 +32047,12 @@
       <c r="J555" t="inlineStr"/>
       <c r="K555" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32145,12 +32105,12 @@
       <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32203,12 +32163,12 @@
       <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32256,12 +32216,12 @@
       <c r="J558" t="inlineStr"/>
       <c r="K558" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32309,12 +32269,12 @@
       <c r="J559" t="inlineStr"/>
       <c r="K559" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32362,12 +32322,12 @@
       <c r="J560" t="inlineStr"/>
       <c r="K560" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32420,12 +32380,12 @@
       <c r="J561" t="inlineStr"/>
       <c r="K561" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32473,12 +32433,12 @@
       <c r="J562" t="inlineStr"/>
       <c r="K562" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32526,12 +32486,12 @@
       <c r="J563" t="inlineStr"/>
       <c r="K563" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32579,12 +32539,12 @@
       <c r="J564" t="inlineStr"/>
       <c r="K564" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32632,12 +32592,12 @@
       <c r="J565" t="inlineStr"/>
       <c r="K565" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32685,12 +32645,12 @@
       <c r="J566" t="inlineStr"/>
       <c r="K566" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32738,12 +32698,12 @@
       <c r="J567" t="inlineStr"/>
       <c r="K567" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32791,12 +32751,12 @@
       <c r="J568" t="inlineStr"/>
       <c r="K568" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32844,12 +32804,12 @@
       <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32897,12 +32857,12 @@
       <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -32950,12 +32910,12 @@
       <c r="J571" t="inlineStr"/>
       <c r="K571" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33003,12 +32963,12 @@
       <c r="J572" t="inlineStr"/>
       <c r="K572" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33061,12 +33021,12 @@
       <c r="J573" t="inlineStr"/>
       <c r="K573" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L573" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33119,12 +33079,12 @@
       <c r="J574" t="inlineStr"/>
       <c r="K574" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L574" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33177,12 +33137,12 @@
       <c r="J575" t="inlineStr"/>
       <c r="K575" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33235,12 +33195,12 @@
       <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L576" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33293,12 +33253,12 @@
       <c r="J577" t="inlineStr"/>
       <c r="K577" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L577" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33351,12 +33311,12 @@
       <c r="J578" t="inlineStr"/>
       <c r="K578" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L578" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33409,12 +33369,12 @@
       <c r="J579" t="inlineStr"/>
       <c r="K579" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33467,12 +33427,12 @@
       <c r="J580" t="inlineStr"/>
       <c r="K580" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L580" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33525,12 +33485,12 @@
       <c r="J581" t="inlineStr"/>
       <c r="K581" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L581" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33583,12 +33543,12 @@
       <c r="J582" t="inlineStr"/>
       <c r="K582" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L582" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33641,12 +33601,12 @@
       <c r="J583" t="inlineStr"/>
       <c r="K583" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L583" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33699,12 +33659,12 @@
       <c r="J584" t="inlineStr"/>
       <c r="K584" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33757,12 +33717,12 @@
       <c r="J585" t="inlineStr"/>
       <c r="K585" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L585" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33815,12 +33775,12 @@
       <c r="J586" t="inlineStr"/>
       <c r="K586" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L586" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33873,12 +33833,12 @@
       <c r="J587" t="inlineStr"/>
       <c r="K587" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L587" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33931,12 +33891,12 @@
       <c r="J588" t="inlineStr"/>
       <c r="K588" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -33989,12 +33949,12 @@
       <c r="J589" t="inlineStr"/>
       <c r="K589" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L589" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34047,12 +34007,12 @@
       <c r="J590" t="inlineStr"/>
       <c r="K590" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L590" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34105,12 +34065,12 @@
       <c r="J591" t="inlineStr"/>
       <c r="K591" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L591" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34162,12 +34122,12 @@
       </c>
       <c r="K592" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M592" t="inlineStr">
         <is>
-          <t>4 days, 21:48:37.231049</t>
+          <t>3 days, 21:09:26.919909</t>
         </is>
       </c>
     </row>
@@ -34219,12 +34179,12 @@
       </c>
       <c r="K593" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M593" t="inlineStr">
         <is>
-          <t>4 days, 21:48:37.231015</t>
+          <t>3 days, 21:09:26.919872</t>
         </is>
       </c>
     </row>
@@ -34276,12 +34236,12 @@
       </c>
       <c r="K594" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M594" t="inlineStr">
         <is>
-          <t>4 days, 21:48:37.230982</t>
+          <t>3 days, 21:09:26.919838</t>
         </is>
       </c>
     </row>
@@ -34329,12 +34289,12 @@
       <c r="J595" t="inlineStr"/>
       <c r="K595" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34382,12 +34342,12 @@
       <c r="J596" t="inlineStr"/>
       <c r="K596" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L596" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34435,12 +34395,12 @@
       <c r="J597" t="inlineStr"/>
       <c r="K597" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34492,12 +34452,12 @@
       </c>
       <c r="K598" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>4 days, 21:48:37.230840</t>
+          <t>3 days, 21:09:26.919725</t>
         </is>
       </c>
     </row>
@@ -34545,12 +34505,12 @@
       <c r="J599" t="inlineStr"/>
       <c r="K599" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34598,12 +34558,12 @@
       <c r="J600" t="inlineStr"/>
       <c r="K600" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34656,12 +34616,12 @@
       <c r="J601" t="inlineStr"/>
       <c r="K601" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34709,12 +34669,12 @@
       <c r="J602" t="inlineStr"/>
       <c r="K602" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34762,12 +34722,12 @@
       <c r="J603" t="inlineStr"/>
       <c r="K603" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34820,12 +34780,12 @@
       <c r="J604" t="inlineStr"/>
       <c r="K604" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34878,12 +34838,12 @@
       <c r="J605" t="inlineStr"/>
       <c r="K605" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34936,12 +34896,12 @@
       <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -34994,12 +34954,12 @@
       <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35047,12 +35007,12 @@
       <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35100,12 +35060,12 @@
       <c r="J609" t="inlineStr"/>
       <c r="K609" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35153,12 +35113,12 @@
       <c r="J610" t="inlineStr"/>
       <c r="K610" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35206,12 +35166,12 @@
       </c>
       <c r="K611" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M611" t="inlineStr">
         <is>
-          <t>2 days, 22:18:37.230454</t>
+          <t>1 day, 21:39:26.919301</t>
         </is>
       </c>
     </row>
@@ -35259,12 +35219,12 @@
       <c r="J612" t="inlineStr"/>
       <c r="K612" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L612" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35312,12 +35272,12 @@
       <c r="J613" t="inlineStr"/>
       <c r="K613" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35361,12 +35321,12 @@
       <c r="J614" t="inlineStr"/>
       <c r="K614" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L614" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35410,12 +35370,12 @@
       <c r="J615" t="inlineStr"/>
       <c r="K615" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35459,12 +35419,12 @@
       <c r="J616" t="inlineStr"/>
       <c r="K616" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35508,12 +35468,12 @@
       <c r="J617" t="inlineStr"/>
       <c r="K617" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35557,12 +35517,12 @@
       <c r="J618" t="inlineStr"/>
       <c r="K618" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35610,12 +35570,12 @@
       <c r="J619" t="inlineStr"/>
       <c r="K619" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35663,12 +35623,12 @@
       <c r="J620" t="inlineStr"/>
       <c r="K620" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35716,12 +35676,12 @@
       <c r="J621" t="inlineStr"/>
       <c r="K621" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35774,12 +35734,12 @@
       <c r="J622" t="inlineStr"/>
       <c r="K622" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>
@@ -35827,65 +35787,12 @@
       <c r="J623" t="inlineStr"/>
       <c r="K623" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
         <is>
-          <t>08/08/26 11:26 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>CANCEL: WORK COMPLETED</t>
-        </is>
-      </c>
-      <c r="B624" t="inlineStr">
-        <is>
-          <t>EVARTS ST NE</t>
-        </is>
-      </c>
-      <c r="C624" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="D624" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="E624" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 26539234</t>
-        </is>
-      </c>
-      <c r="G624" t="inlineStr">
-        <is>
-          <t>08/03/26 07:49 am</t>
-        </is>
-      </c>
-      <c r="H624" t="inlineStr">
-        <is>
-          <t>07/23/26 07:15 am</t>
-        </is>
-      </c>
-      <c r="I624" t="inlineStr">
-        <is>
-          <t>08/10/26 07:15 am</t>
-        </is>
-      </c>
-      <c r="J624" t="inlineStr"/>
-      <c r="K624" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L624" t="inlineStr">
-        <is>
-          <t>08/08/26 11:26 AM</t>
+          <t>08/09/26 12:05 PM</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -546,17 +546,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>20 days, 4:58:18.875486</t>
+          <t>19 days, 4:58:49.114054</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>20 days, 4:58:18.875420</t>
+          <t>19 days, 4:58:49.113988</t>
         </is>
       </c>
     </row>
@@ -670,17 +670,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>20 days, 4:58:18.875373</t>
+          <t>19 days, 4:58:49.113942</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>20 days, 4:58:18.875330</t>
+          <t>19 days, 4:58:49.113899</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; VDC, WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>20 days, 4:58:18.875289</t>
+          <t>19 days, 4:58:49.113861</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>COMDC, PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>COMDC, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>20 days, 4:58:18.875246</t>
+          <t>19 days, 4:58:49.113821</t>
         </is>
       </c>
     </row>
@@ -918,17 +918,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; PEPCODC, VDC, WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; WASA02 &amp; WGL07 - Not yet responded</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>20 days, 4:58:18.875207</t>
+          <t>19 days, 4:58:49.113782</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1137,19 +1137,15 @@
           <t>09/04/26 07:15 am</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>19 days, 19:58:18.875042</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1167,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1199,19 +1195,15 @@
           <t>09/04/26 07:15 am</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>19 days, 19:58:18.875003</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1255,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874965</t>
+          <t>18 days, 1:13:49.113553</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1312,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874927</t>
+          <t>18 days, 1:13:49.113513</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1369,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874892</t>
+          <t>18 days, 1:13:49.113476</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1426,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874857</t>
+          <t>18 days, 1:13:49.113440</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1483,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874823</t>
+          <t>18 days, 1:13:49.113386</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1540,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874791</t>
+          <t>18 days, 1:13:49.113345</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1597,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874755</t>
+          <t>18 days, 1:13:49.113310</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1654,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874721</t>
+          <t>18 days, 1:13:49.113275</t>
         </is>
       </c>
     </row>
@@ -1719,12 +1711,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874688</t>
+          <t>18 days, 1:13:49.113241</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1768,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874629</t>
+          <t>18 days, 1:13:49.113207</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1825,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874591</t>
+          <t>18 days, 1:13:49.113173</t>
         </is>
       </c>
     </row>
@@ -1890,12 +1882,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874556</t>
+          <t>18 days, 1:13:49.113140</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1939,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874524</t>
+          <t>18 days, 1:13:49.113109</t>
         </is>
       </c>
     </row>
@@ -2004,12 +1996,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874489</t>
+          <t>18 days, 1:13:49.113077</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2053,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874457</t>
+          <t>18 days, 1:13:49.113045</t>
         </is>
       </c>
     </row>
@@ -2118,12 +2110,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874425</t>
+          <t>18 days, 1:13:49.113013</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2167,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>19 days, 1:13:18.874391</t>
+          <t>18 days, 1:13:49.112979</t>
         </is>
       </c>
     </row>
@@ -2232,12 +2224,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>19 days, 0:43:18.874360</t>
+          <t>18 days, 0:43:49.112948</t>
         </is>
       </c>
     </row>
@@ -2289,12 +2281,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>19 days, 0:43:18.874327</t>
+          <t>18 days, 0:43:49.112917</t>
         </is>
       </c>
     </row>
@@ -2346,12 +2338,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19 days, 0:43:18.874295</t>
+          <t>18 days, 0:43:49.112885</t>
         </is>
       </c>
     </row>
@@ -2403,12 +2395,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>19 days, 0:43:18.874263</t>
+          <t>18 days, 0:43:49.112848</t>
         </is>
       </c>
     </row>
@@ -2460,12 +2452,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19 days, 0:43:18.874231</t>
+          <t>18 days, 0:43:49.112811</t>
         </is>
       </c>
     </row>
@@ -2517,12 +2509,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19 days, 0:43:18.874200</t>
+          <t>18 days, 0:43:49.112781</t>
         </is>
       </c>
     </row>
@@ -2574,12 +2566,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>19 days, 0:43:18.874169</t>
+          <t>18 days, 0:43:49.112749</t>
         </is>
       </c>
     </row>
@@ -2631,12 +2623,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>19 days, 0:43:18.874138</t>
+          <t>18 days, 0:43:49.112719</t>
         </is>
       </c>
     </row>
@@ -2688,12 +2680,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>19 days, 0:43:18.874107</t>
+          <t>18 days, 0:43:49.112689</t>
         </is>
       </c>
     </row>
@@ -2745,12 +2737,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>19 days, 0:43:18.874076</t>
+          <t>18 days, 0:43:49.112658</t>
         </is>
       </c>
     </row>
@@ -2802,12 +2794,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>19 days, 0:43:18.874045</t>
+          <t>18 days, 0:43:49.112627</t>
         </is>
       </c>
     </row>
@@ -2854,17 +2846,17 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>DCDOT01 - Not complete/In progress &amp; WASA02 &amp; WGL07 - Not yet responded</t>
+          <t>DCDOT01 - Not complete/In progress &amp; WASA02 - Not yet responded</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>18 days, 23:43:18.874009</t>
+          <t>17 days, 23:43:49.112591</t>
         </is>
       </c>
     </row>
@@ -2916,12 +2908,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>18 days, 23:43:18.873973</t>
+          <t>17 days, 23:43:49.112555</t>
         </is>
       </c>
     </row>
@@ -2973,12 +2965,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>18 days, 23:43:18.873940</t>
+          <t>17 days, 23:43:49.112521</t>
         </is>
       </c>
     </row>
@@ -3030,12 +3022,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>18 days, 23:43:18.873907</t>
+          <t>17 days, 23:43:49.112486</t>
         </is>
       </c>
     </row>
@@ -3087,12 +3079,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>18 days, 23:43:18.873872</t>
+          <t>17 days, 23:43:49.112453</t>
         </is>
       </c>
     </row>
@@ -3144,12 +3136,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873830</t>
+          <t>17 days, 23:13:49.112411</t>
         </is>
       </c>
     </row>
@@ -3201,12 +3193,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873789</t>
+          <t>17 days, 23:13:49.112347</t>
         </is>
       </c>
     </row>
@@ -3258,12 +3250,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873749</t>
+          <t>17 days, 23:13:49.112302</t>
         </is>
       </c>
     </row>
@@ -3315,12 +3307,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873707</t>
+          <t>17 days, 23:13:49.112261</t>
         </is>
       </c>
     </row>
@@ -3372,12 +3364,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873631</t>
+          <t>17 days, 23:13:49.112223</t>
         </is>
       </c>
     </row>
@@ -3429,12 +3421,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873584</t>
+          <t>17 days, 23:13:49.112185</t>
         </is>
       </c>
     </row>
@@ -3486,12 +3478,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873543</t>
+          <t>17 days, 23:13:49.112146</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3535,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873504</t>
+          <t>17 days, 23:13:49.112107</t>
         </is>
       </c>
     </row>
@@ -3600,12 +3592,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873464</t>
+          <t>17 days, 23:13:49.112068</t>
         </is>
       </c>
     </row>
@@ -3657,12 +3649,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873422</t>
+          <t>17 days, 23:13:49.112026</t>
         </is>
       </c>
     </row>
@@ -3714,12 +3706,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873379</t>
+          <t>17 days, 23:13:49.111986</t>
         </is>
       </c>
     </row>
@@ -3771,12 +3763,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873339</t>
+          <t>17 days, 23:13:49.111945</t>
         </is>
       </c>
     </row>
@@ -3828,12 +3820,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873297</t>
+          <t>17 days, 23:13:49.111904</t>
         </is>
       </c>
     </row>
@@ -3885,12 +3877,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873257</t>
+          <t>17 days, 23:13:49.111863</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3934,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873214</t>
+          <t>17 days, 23:13:49.111821</t>
         </is>
       </c>
     </row>
@@ -3999,12 +3991,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873171</t>
+          <t>17 days, 23:13:49.111778</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4048,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873127</t>
+          <t>17 days, 23:13:49.111735</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4105,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>18 days, 23:13:18.873083</t>
+          <t>17 days, 23:13:49.111692</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4158,12 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -4228,12 +4220,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.873010</t>
+          <t>17 days, 19:43:49.111621</t>
         </is>
       </c>
     </row>
@@ -4290,12 +4282,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872971</t>
+          <t>17 days, 19:43:49.111583</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4344,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872936</t>
+          <t>17 days, 19:43:49.111550</t>
         </is>
       </c>
     </row>
@@ -4414,12 +4406,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872904</t>
+          <t>17 days, 19:43:49.111517</t>
         </is>
       </c>
     </row>
@@ -4476,12 +4468,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872871</t>
+          <t>17 days, 19:43:49.111487</t>
         </is>
       </c>
     </row>
@@ -4538,12 +4530,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872837</t>
+          <t>17 days, 19:43:49.111455</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4592,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872802</t>
+          <t>17 days, 19:43:49.111420</t>
         </is>
       </c>
     </row>
@@ -4662,12 +4654,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872769</t>
+          <t>17 days, 19:43:49.111366</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4716,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872735</t>
+          <t>17 days, 19:43:49.111331</t>
         </is>
       </c>
     </row>
@@ -4786,12 +4778,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872703</t>
+          <t>17 days, 19:43:49.111298</t>
         </is>
       </c>
     </row>
@@ -4848,12 +4840,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872627</t>
+          <t>17 days, 19:43:49.111262</t>
         </is>
       </c>
     </row>
@@ -4910,12 +4902,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872584</t>
+          <t>17 days, 19:43:49.111231</t>
         </is>
       </c>
     </row>
@@ -4972,12 +4964,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872546</t>
+          <t>17 days, 19:43:49.111196</t>
         </is>
       </c>
     </row>
@@ -5034,12 +5026,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872511</t>
+          <t>17 days, 19:43:49.111163</t>
         </is>
       </c>
     </row>
@@ -5096,12 +5088,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872477</t>
+          <t>17 days, 19:43:49.111132</t>
         </is>
       </c>
     </row>
@@ -5158,12 +5150,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>18 days, 19:43:18.872444</t>
+          <t>17 days, 19:43:49.111100</t>
         </is>
       </c>
     </row>
@@ -5211,12 +5203,12 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5256,12 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -5317,12 +5309,12 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -5370,12 +5362,12 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -5423,12 +5415,12 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -5476,12 +5468,12 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5521,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -5586,12 +5578,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>16 days, 20:43:18.872180</t>
+          <t>15 days, 20:43:49.110842</t>
         </is>
       </c>
     </row>
@@ -5643,12 +5635,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>16 days, 20:43:18.872141</t>
+          <t>15 days, 20:43:49.110803</t>
         </is>
       </c>
     </row>
@@ -5700,12 +5692,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>16 days, 20:43:18.872104</t>
+          <t>15 days, 20:43:49.110767</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5749,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>16 days, 20:43:18.872068</t>
+          <t>15 days, 20:43:49.110731</t>
         </is>
       </c>
     </row>
@@ -5814,12 +5806,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>16 days, 20:43:18.872031</t>
+          <t>15 days, 20:43:49.110695</t>
         </is>
       </c>
     </row>
@@ -5871,12 +5863,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>16 days, 20:43:18.871996</t>
+          <t>15 days, 20:43:49.110659</t>
         </is>
       </c>
     </row>
@@ -5928,12 +5920,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>16 days, 20:43:18.871959</t>
+          <t>15 days, 20:43:49.110623</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5977,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>16 days, 20:43:18.871922</t>
+          <t>15 days, 20:43:49.110586</t>
         </is>
       </c>
     </row>
@@ -6042,12 +6034,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>16 days, 20:43:18.871886</t>
+          <t>15 days, 20:43:49.110549</t>
         </is>
       </c>
     </row>
@@ -6099,12 +6091,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>16 days, 19:43:18.871847</t>
+          <t>15 days, 19:43:49.110512</t>
         </is>
       </c>
     </row>
@@ -6156,12 +6148,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>16 days, 19:43:18.871811</t>
+          <t>15 days, 19:43:49.110477</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6205,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>16 days, 19:43:18.871776</t>
+          <t>15 days, 19:43:49.110442</t>
         </is>
       </c>
     </row>
@@ -6266,12 +6258,12 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -6319,12 +6311,12 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -6376,12 +6368,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>16 days, 1:58:18.871653</t>
+          <t>15 days, 1:58:49.110287</t>
         </is>
       </c>
     </row>
@@ -6433,12 +6425,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>16 days, 1:58:18.871603</t>
+          <t>15 days, 1:58:49.110246</t>
         </is>
       </c>
     </row>
@@ -6490,12 +6482,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>16 days, 1:58:18.871563</t>
+          <t>15 days, 1:58:49.110207</t>
         </is>
       </c>
     </row>
@@ -6547,12 +6539,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>16 days, 1:58:18.871526</t>
+          <t>15 days, 1:58:49.110170</t>
         </is>
       </c>
     </row>
@@ -6604,12 +6596,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>16 days, 1:58:18.871489</t>
+          <t>15 days, 1:58:49.110132</t>
         </is>
       </c>
     </row>
@@ -6661,12 +6653,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>16 days, 1:58:18.871451</t>
+          <t>15 days, 1:58:49.110096</t>
         </is>
       </c>
     </row>
@@ -6718,12 +6710,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>16 days, 1:58:18.871415</t>
+          <t>15 days, 1:58:49.110060</t>
         </is>
       </c>
     </row>
@@ -6771,12 +6763,12 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -6824,12 +6816,12 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6869,12 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -6930,12 +6922,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -6983,12 +6975,12 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7036,12 +7028,12 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7089,12 +7081,12 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7142,12 +7134,12 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7195,12 +7187,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7248,12 +7240,12 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7301,12 +7293,12 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7346,12 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7407,12 +7399,12 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7460,12 +7452,12 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7517,12 +7509,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>15 days, 23:13:18.870963</t>
+          <t>14 days, 23:13:49.109623</t>
         </is>
       </c>
     </row>
@@ -7570,12 +7562,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7623,12 +7615,12 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7676,12 +7668,12 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7729,12 +7721,12 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7782,12 +7774,12 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7827,12 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7888,12 +7880,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7941,12 +7933,12 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -7994,12 +7986,12 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8047,12 +8039,12 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8100,12 +8092,12 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8145,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8206,12 +8198,12 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8259,12 +8251,12 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8312,12 +8304,12 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8365,12 +8357,12 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8418,12 +8410,12 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8471,12 +8463,12 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8524,12 +8516,12 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8577,12 +8569,12 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8630,12 +8622,12 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8683,12 +8675,12 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8736,12 +8728,12 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -8793,12 +8785,12 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.870208</t>
+          <t>14 days, 19:43:49.108893</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8842,12 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.870173</t>
+          <t>14 days, 19:43:49.108859</t>
         </is>
       </c>
     </row>
@@ -8907,12 +8899,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.870140</t>
+          <t>14 days, 19:43:49.108825</t>
         </is>
       </c>
     </row>
@@ -8960,12 +8952,12 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -9013,12 +9005,12 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9058,12 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -9124,12 +9116,12 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -9182,12 +9174,12 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -9240,12 +9232,12 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -9298,12 +9290,12 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -9356,12 +9348,12 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -9414,12 +9406,12 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -9476,12 +9468,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869834</t>
+          <t>14 days, 19:43:49.108521</t>
         </is>
       </c>
     </row>
@@ -9538,12 +9530,12 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869798</t>
+          <t>14 days, 19:43:49.108487</t>
         </is>
       </c>
     </row>
@@ -9600,12 +9592,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869763</t>
+          <t>14 days, 19:43:49.108452</t>
         </is>
       </c>
     </row>
@@ -9662,12 +9654,12 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869730</t>
+          <t>14 days, 19:43:49.108419</t>
         </is>
       </c>
     </row>
@@ -9724,12 +9716,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869697</t>
+          <t>14 days, 19:43:49.108366</t>
         </is>
       </c>
     </row>
@@ -9786,12 +9778,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869624</t>
+          <t>14 days, 19:43:49.108332</t>
         </is>
       </c>
     </row>
@@ -9848,12 +9840,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869583</t>
+          <t>14 days, 19:43:49.108299</t>
         </is>
       </c>
     </row>
@@ -9910,12 +9902,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869548</t>
+          <t>14 days, 19:43:49.108268</t>
         </is>
       </c>
     </row>
@@ -9968,12 +9960,12 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -10030,12 +10022,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869481</t>
+          <t>14 days, 19:43:49.108203</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10084,12 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869445</t>
+          <t>14 days, 19:43:49.108168</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10146,12 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869407</t>
+          <t>14 days, 19:43:49.108135</t>
         </is>
       </c>
     </row>
@@ -10216,12 +10208,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869372</t>
+          <t>14 days, 19:43:49.108103</t>
         </is>
       </c>
     </row>
@@ -10278,12 +10270,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869341</t>
+          <t>14 days, 19:43:49.108073</t>
         </is>
       </c>
     </row>
@@ -10340,12 +10332,12 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869307</t>
+          <t>14 days, 19:43:49.108041</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10394,12 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869271</t>
+          <t>14 days, 19:43:49.108005</t>
         </is>
       </c>
     </row>
@@ -10464,12 +10456,12 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869237</t>
+          <t>14 days, 19:43:49.107971</t>
         </is>
       </c>
     </row>
@@ -10526,12 +10518,12 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869206</t>
+          <t>14 days, 19:43:49.107940</t>
         </is>
       </c>
     </row>
@@ -10588,12 +10580,12 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869174</t>
+          <t>14 days, 19:43:49.107909</t>
         </is>
       </c>
     </row>
@@ -10650,12 +10642,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869141</t>
+          <t>14 days, 19:43:49.107868</t>
         </is>
       </c>
     </row>
@@ -10712,12 +10704,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869106</t>
+          <t>14 days, 19:43:49.107833</t>
         </is>
       </c>
     </row>
@@ -10774,12 +10766,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869073</t>
+          <t>14 days, 19:43:49.107800</t>
         </is>
       </c>
     </row>
@@ -10836,12 +10828,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869040</t>
+          <t>14 days, 19:43:49.107767</t>
         </is>
       </c>
     </row>
@@ -10898,12 +10890,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.869009</t>
+          <t>14 days, 19:43:49.107736</t>
         </is>
       </c>
     </row>
@@ -10960,12 +10952,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868976</t>
+          <t>14 days, 19:43:49.107702</t>
         </is>
       </c>
     </row>
@@ -11022,12 +11014,12 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868945</t>
+          <t>14 days, 19:43:49.107671</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11076,12 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868912</t>
+          <t>14 days, 19:43:49.107639</t>
         </is>
       </c>
     </row>
@@ -11146,12 +11138,12 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868882</t>
+          <t>14 days, 19:43:49.107610</t>
         </is>
       </c>
     </row>
@@ -11204,12 +11196,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -11266,12 +11258,12 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868817</t>
+          <t>14 days, 19:43:49.107550</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11320,12 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868785</t>
+          <t>14 days, 19:43:49.107518</t>
         </is>
       </c>
     </row>
@@ -11390,12 +11382,12 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868750</t>
+          <t>14 days, 19:43:49.107484</t>
         </is>
       </c>
     </row>
@@ -11452,12 +11444,12 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868717</t>
+          <t>14 days, 19:43:49.107452</t>
         </is>
       </c>
     </row>
@@ -11514,12 +11506,12 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868684</t>
+          <t>14 days, 19:43:49.107420</t>
         </is>
       </c>
     </row>
@@ -11576,12 +11568,12 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868609</t>
+          <t>14 days, 19:43:49.107369</t>
         </is>
       </c>
     </row>
@@ -11638,12 +11630,12 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868569</t>
+          <t>14 days, 19:43:49.107335</t>
         </is>
       </c>
     </row>
@@ -11700,12 +11692,12 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868531</t>
+          <t>14 days, 19:43:49.107300</t>
         </is>
       </c>
     </row>
@@ -11762,12 +11754,12 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868497</t>
+          <t>14 days, 19:43:49.107267</t>
         </is>
       </c>
     </row>
@@ -11820,12 +11812,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -11878,12 +11870,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -11940,12 +11932,12 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868399</t>
+          <t>14 days, 19:43:49.107173</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11990,12 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12060,12 +12052,12 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868337</t>
+          <t>14 days, 19:43:49.107113</t>
         </is>
       </c>
     </row>
@@ -12118,12 +12110,12 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12180,12 +12172,12 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.868259</t>
+          <t>14 days, 19:43:49.107037</t>
         </is>
       </c>
     </row>
@@ -12238,12 +12230,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12296,12 +12288,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12354,12 +12346,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12412,12 +12404,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12470,12 +12462,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12528,12 +12520,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12586,12 +12578,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12644,12 +12636,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12702,12 +12694,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12764,12 +12756,12 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>15 days, 19:43:18.867926</t>
+          <t>14 days, 19:43:49.106703</t>
         </is>
       </c>
     </row>
@@ -12822,12 +12814,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12880,12 +12872,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12938,12 +12930,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -12991,12 +12983,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13044,12 +13036,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13097,12 +13089,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13150,12 +13142,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13207,12 +13199,12 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>13 days, 0:43:18.867681</t>
+          <t>12 days, 0:43:49.106463</t>
         </is>
       </c>
     </row>
@@ -13264,12 +13256,12 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>13 days, 0:43:18.867622</t>
+          <t>12 days, 0:43:49.106428</t>
         </is>
       </c>
     </row>
@@ -13317,12 +13309,12 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13370,12 +13362,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13423,12 +13415,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13468,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13521,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13582,12 +13574,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13635,12 +13627,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13688,12 +13680,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13741,12 +13733,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13794,12 +13786,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13847,12 +13839,12 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13900,12 +13892,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -13953,12 +13945,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14006,12 +13998,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14059,12 +14051,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14112,12 +14104,12 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14165,12 +14157,12 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14218,12 +14210,12 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14263,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14324,12 +14316,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14377,12 +14369,12 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14430,12 +14422,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14483,12 +14475,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14536,12 +14528,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14589,12 +14581,12 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14642,12 +14634,12 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14695,12 +14687,12 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14748,12 +14740,12 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14801,12 +14793,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14854,12 +14846,12 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14907,12 +14899,12 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -14960,12 +14952,12 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15013,12 +15005,12 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15058,12 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15119,12 +15111,12 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15172,12 +15164,12 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15225,12 +15217,12 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15282,12 +15274,12 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>12 days, 19:43:18.866518</t>
+          <t>11 days, 19:43:49.105238</t>
         </is>
       </c>
     </row>
@@ -15335,12 +15327,12 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15393,12 +15385,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15451,12 +15443,12 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15504,12 +15496,12 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>11 days, 23:13:18.866390</t>
+          <t>10 days, 23:13:49.105106</t>
         </is>
       </c>
     </row>
@@ -15557,12 +15549,12 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>12 days, 0:28:18.866357</t>
+          <t>11 days, 0:28:49.105072</t>
         </is>
       </c>
     </row>
@@ -15610,12 +15602,12 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>11 days, 23:13:18.866322</t>
+          <t>10 days, 23:13:49.105036</t>
         </is>
       </c>
     </row>
@@ -15663,12 +15655,12 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>11 days, 23:13:18.866282</t>
+          <t>10 days, 23:13:49.104994</t>
         </is>
       </c>
     </row>
@@ -15716,12 +15708,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15769,12 +15761,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15822,12 +15814,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15875,12 +15867,12 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15928,12 +15920,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -15981,12 +15973,12 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16034,12 +16026,12 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16091,12 +16083,12 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>10 days, 23:28:18.866039</t>
+          <t>9 days, 23:28:49.104752</t>
         </is>
       </c>
     </row>
@@ -16144,12 +16136,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16201,12 +16193,12 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>10 days, 23:28:18.865977</t>
+          <t>9 days, 23:28:49.104689</t>
         </is>
       </c>
     </row>
@@ -16254,12 +16246,12 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16307,12 +16299,12 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16360,12 +16352,12 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16413,12 +16405,12 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16466,12 +16458,12 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16519,12 +16511,12 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16572,12 +16564,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16625,12 +16617,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16678,12 +16670,12 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16731,12 +16723,12 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16784,12 +16776,12 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16837,12 +16829,12 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16882,12 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16943,12 +16935,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -16996,12 +16988,12 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17049,12 +17041,12 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17102,12 +17094,12 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17155,12 +17147,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17208,12 +17200,12 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17261,12 +17253,12 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17314,12 +17306,12 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17367,12 +17359,12 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17420,12 +17412,12 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17473,12 +17465,12 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17526,12 +17518,12 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17579,12 +17571,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17632,12 +17624,12 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17677,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17747,12 +17739,12 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>9 days, 19:43:18.865072</t>
+          <t>8 days, 19:43:49.103804</t>
         </is>
       </c>
     </row>
@@ -17805,12 +17797,12 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17863,12 +17855,12 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17921,12 +17913,12 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -17979,12 +17971,12 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18037,12 +18029,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18095,12 +18087,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18153,12 +18145,12 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18206,12 +18198,12 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18259,12 +18251,12 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18312,12 +18304,12 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18365,12 +18357,12 @@
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18418,12 +18410,12 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18471,12 +18463,12 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18524,12 +18516,12 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18577,12 +18569,12 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18630,12 +18622,12 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18683,12 +18675,12 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18736,12 +18728,12 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18789,12 +18781,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18842,12 +18834,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18895,12 +18887,12 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -18948,12 +18940,12 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19001,12 +18993,12 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19054,12 +19046,12 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19107,12 +19099,12 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19160,12 +19152,12 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19213,12 +19205,12 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19266,12 +19258,12 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19319,12 +19311,12 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19372,12 +19364,12 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19425,12 +19417,12 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19478,12 +19470,12 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19531,12 +19523,12 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19584,12 +19576,12 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19637,12 +19629,12 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19690,12 +19682,12 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19743,12 +19735,12 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19796,12 +19788,12 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19849,12 +19841,12 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19902,12 +19894,12 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -19955,12 +19947,12 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20008,12 +20000,12 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20061,12 +20053,12 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20118,12 +20110,12 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>4 days, 23:43:18.863751</t>
+          <t>3 days, 23:43:49.102514</t>
         </is>
       </c>
     </row>
@@ -20171,12 +20163,12 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20224,12 +20216,12 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20277,12 +20269,12 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20330,12 +20322,12 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20387,12 +20379,12 @@
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>4 days, 23:43:18.863562</t>
+          <t>3 days, 23:43:49.102277</t>
         </is>
       </c>
     </row>
@@ -20440,12 +20432,12 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20493,12 +20485,12 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20546,12 +20538,12 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20604,12 +20596,12 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20661,12 +20653,12 @@
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>4 days, 21:13:18.863399</t>
+          <t>3 days, 21:13:49.102112</t>
         </is>
       </c>
     </row>
@@ -20718,12 +20710,12 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>4 days, 19:43:18.863356</t>
+          <t>3 days, 19:43:49.102069</t>
         </is>
       </c>
     </row>
@@ -20771,12 +20763,12 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20824,12 +20816,12 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20877,12 +20869,12 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20930,12 +20922,12 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -20983,12 +20975,12 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21041,12 +21033,12 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21099,12 +21091,12 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21157,12 +21149,12 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21215,12 +21207,12 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21273,12 +21265,12 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21331,12 +21323,12 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21389,12 +21381,12 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21442,12 +21434,12 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21495,12 +21487,12 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21548,12 +21540,12 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21601,12 +21593,12 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21654,12 +21646,12 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21707,12 +21699,12 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21760,12 +21752,12 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21813,12 +21805,12 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21866,12 +21858,12 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21919,12 +21911,12 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -21972,12 +21964,12 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22025,12 +22017,12 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22078,12 +22070,12 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22131,12 +22123,12 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22184,12 +22176,12 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22237,12 +22229,12 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22290,12 +22282,12 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22343,12 +22335,12 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22396,12 +22388,12 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22449,12 +22441,12 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22502,12 +22494,12 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22555,12 +22547,12 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22608,12 +22600,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22661,12 +22653,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22714,12 +22706,12 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22767,12 +22759,12 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22820,12 +22812,12 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22873,12 +22865,12 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22926,12 +22918,12 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -22979,12 +22971,12 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23032,12 +23024,12 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23085,12 +23077,12 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23138,12 +23130,12 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23191,12 +23183,12 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23244,12 +23236,12 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23297,12 +23289,12 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23350,12 +23342,12 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23403,12 +23395,12 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23456,12 +23448,12 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23514,12 +23506,12 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23572,12 +23564,12 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23630,12 +23622,12 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23688,12 +23680,12 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23746,12 +23738,12 @@
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23804,12 +23796,12 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23862,12 +23854,12 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23920,12 +23912,12 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -23978,12 +23970,12 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24036,12 +24028,12 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24094,12 +24086,12 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24152,12 +24144,12 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24205,12 +24197,12 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24258,12 +24250,12 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24311,12 +24303,12 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24364,12 +24356,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24417,12 +24409,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24470,12 +24462,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24523,12 +24515,12 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24576,12 +24568,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24629,12 +24621,12 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24682,12 +24674,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24735,12 +24727,12 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24788,12 +24780,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24841,12 +24833,12 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24894,12 +24886,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -24947,12 +24939,12 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25000,12 +24992,12 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25053,12 +25045,12 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25106,12 +25098,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25159,12 +25151,12 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25212,12 +25204,12 @@
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25265,12 +25257,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25318,12 +25310,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25371,12 +25363,12 @@
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25424,12 +25416,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25477,12 +25469,12 @@
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25530,12 +25522,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25583,12 +25575,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25636,12 +25628,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25689,12 +25681,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25742,12 +25734,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25795,12 +25787,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25848,12 +25840,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25901,12 +25893,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -25954,12 +25946,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26007,12 +25999,12 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26060,12 +26052,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26113,12 +26105,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26166,12 +26158,12 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26219,12 +26211,12 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26276,12 +26268,12 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>3 days, 2:43:18.860385</t>
+          <t>2 days, 2:43:49.099186</t>
         </is>
       </c>
     </row>
@@ -26329,12 +26321,12 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26387,12 +26379,12 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26445,12 +26437,12 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26503,12 +26495,12 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26556,12 +26548,12 @@
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26614,12 +26606,12 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26672,12 +26664,12 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26730,12 +26722,12 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26788,12 +26780,12 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26846,12 +26838,12 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26904,12 +26896,12 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -26962,12 +26954,12 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27020,12 +27012,12 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27078,12 +27070,12 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27136,12 +27128,12 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27194,12 +27186,12 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27252,12 +27244,12 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27309,12 +27301,12 @@
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>2 days, 20:13:18.859848</t>
+          <t>1 day, 20:13:49.098669</t>
         </is>
       </c>
     </row>
@@ -27367,12 +27359,12 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27425,12 +27417,12 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27483,12 +27475,12 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27541,12 +27533,12 @@
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27599,12 +27591,12 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27657,12 +27649,12 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27715,12 +27707,12 @@
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27773,12 +27765,12 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27826,12 +27818,12 @@
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27879,12 +27871,12 @@
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27932,12 +27924,12 @@
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -27985,12 +27977,12 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28038,12 +28030,12 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28091,12 +28083,12 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28144,12 +28136,12 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28197,12 +28189,12 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28250,12 +28242,12 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28303,12 +28295,12 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28356,12 +28348,12 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28409,12 +28401,12 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28467,12 +28459,12 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28525,12 +28517,12 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28583,12 +28575,12 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28641,12 +28633,12 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28699,12 +28691,12 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28757,12 +28749,12 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28815,12 +28807,12 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28873,12 +28865,12 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28931,12 +28923,12 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -28989,12 +28981,12 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29047,12 +29039,12 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29105,12 +29097,12 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29158,12 +29150,12 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29211,12 +29203,12 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29268,12 +29260,12 @@
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M518" t="inlineStr">
         <is>
-          <t>2 days, 3:13:18.858768</t>
+          <t>1 day, 3:13:49.097608</t>
         </is>
       </c>
     </row>
@@ -29321,12 +29313,12 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29374,12 +29366,12 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29427,12 +29419,12 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29480,12 +29472,12 @@
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29533,12 +29525,12 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29586,12 +29578,12 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29639,12 +29631,12 @@
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29697,12 +29689,12 @@
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29755,12 +29747,12 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29813,12 +29805,12 @@
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29871,12 +29863,12 @@
       <c r="J529" t="inlineStr"/>
       <c r="K529" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29929,12 +29921,12 @@
       <c r="J530" t="inlineStr"/>
       <c r="K530" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -29987,12 +29979,12 @@
       <c r="J531" t="inlineStr"/>
       <c r="K531" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30045,12 +30037,12 @@
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30103,12 +30095,12 @@
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30161,12 +30153,12 @@
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30219,12 +30211,12 @@
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30277,12 +30269,12 @@
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30335,12 +30327,12 @@
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30393,12 +30385,12 @@
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30451,12 +30443,12 @@
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30509,12 +30501,12 @@
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30567,12 +30559,12 @@
       <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30625,12 +30617,12 @@
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30683,12 +30675,12 @@
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30741,12 +30733,12 @@
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30799,12 +30791,12 @@
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30857,12 +30849,12 @@
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30915,12 +30907,12 @@
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -30973,12 +30965,12 @@
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31031,12 +31023,12 @@
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31089,12 +31081,12 @@
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31142,12 +31134,12 @@
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31200,12 +31192,12 @@
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31258,12 +31250,12 @@
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31316,12 +31308,12 @@
       <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31374,12 +31366,12 @@
       <c r="J555" t="inlineStr"/>
       <c r="K555" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31432,12 +31424,12 @@
       <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31490,12 +31482,12 @@
       <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31548,12 +31540,12 @@
       <c r="J558" t="inlineStr"/>
       <c r="K558" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31606,12 +31598,12 @@
       <c r="J559" t="inlineStr"/>
       <c r="K559" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31664,12 +31656,12 @@
       <c r="J560" t="inlineStr"/>
       <c r="K560" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31722,12 +31714,12 @@
       <c r="J561" t="inlineStr"/>
       <c r="K561" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31780,12 +31772,12 @@
       <c r="J562" t="inlineStr"/>
       <c r="K562" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31838,12 +31830,12 @@
       <c r="J563" t="inlineStr"/>
       <c r="K563" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31896,12 +31888,12 @@
       <c r="J564" t="inlineStr"/>
       <c r="K564" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -31954,12 +31946,12 @@
       <c r="J565" t="inlineStr"/>
       <c r="K565" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32012,12 +32004,12 @@
       <c r="J566" t="inlineStr"/>
       <c r="K566" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32070,12 +32062,12 @@
       <c r="J567" t="inlineStr"/>
       <c r="K567" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32128,12 +32120,12 @@
       <c r="J568" t="inlineStr"/>
       <c r="K568" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32186,12 +32178,12 @@
       <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32244,12 +32236,12 @@
       <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32302,12 +32294,12 @@
       <c r="J571" t="inlineStr"/>
       <c r="K571" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32360,12 +32352,12 @@
       <c r="J572" t="inlineStr"/>
       <c r="K572" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32418,12 +32410,12 @@
       <c r="J573" t="inlineStr"/>
       <c r="K573" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L573" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32476,12 +32468,12 @@
       <c r="J574" t="inlineStr"/>
       <c r="K574" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L574" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32534,12 +32526,12 @@
       <c r="J575" t="inlineStr"/>
       <c r="K575" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32592,12 +32584,12 @@
       <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L576" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32650,12 +32642,12 @@
       <c r="J577" t="inlineStr"/>
       <c r="K577" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L577" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32708,12 +32700,12 @@
       <c r="J578" t="inlineStr"/>
       <c r="K578" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L578" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32766,12 +32758,12 @@
       <c r="J579" t="inlineStr"/>
       <c r="K579" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32824,12 +32816,12 @@
       <c r="J580" t="inlineStr"/>
       <c r="K580" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L580" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32882,12 +32874,12 @@
       <c r="J581" t="inlineStr"/>
       <c r="K581" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L581" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32940,12 +32932,12 @@
       <c r="J582" t="inlineStr"/>
       <c r="K582" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L582" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -32998,12 +32990,12 @@
       <c r="J583" t="inlineStr"/>
       <c r="K583" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L583" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33056,12 +33048,12 @@
       <c r="J584" t="inlineStr"/>
       <c r="K584" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33114,12 +33106,12 @@
       <c r="J585" t="inlineStr"/>
       <c r="K585" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L585" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33172,12 +33164,12 @@
       <c r="J586" t="inlineStr"/>
       <c r="K586" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L586" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33230,12 +33222,12 @@
       <c r="J587" t="inlineStr"/>
       <c r="K587" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L587" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33288,12 +33280,12 @@
       <c r="J588" t="inlineStr"/>
       <c r="K588" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33346,12 +33338,12 @@
       <c r="J589" t="inlineStr"/>
       <c r="K589" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L589" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33404,12 +33396,12 @@
       <c r="J590" t="inlineStr"/>
       <c r="K590" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L590" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33462,12 +33454,12 @@
       <c r="J591" t="inlineStr"/>
       <c r="K591" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L591" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33520,12 +33512,12 @@
       <c r="J592" t="inlineStr"/>
       <c r="K592" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L592" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33578,12 +33570,12 @@
       <c r="J593" t="inlineStr"/>
       <c r="K593" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L593" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33636,12 +33628,12 @@
       <c r="J594" t="inlineStr"/>
       <c r="K594" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L594" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33694,12 +33686,12 @@
       <c r="J595" t="inlineStr"/>
       <c r="K595" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33752,12 +33744,12 @@
       <c r="J596" t="inlineStr"/>
       <c r="K596" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L596" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33810,12 +33802,12 @@
       <c r="J597" t="inlineStr"/>
       <c r="K597" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33868,12 +33860,12 @@
       <c r="J598" t="inlineStr"/>
       <c r="K598" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33926,12 +33918,12 @@
       <c r="J599" t="inlineStr"/>
       <c r="K599" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -33984,12 +33976,12 @@
       <c r="J600" t="inlineStr"/>
       <c r="K600" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34042,12 +34034,12 @@
       <c r="J601" t="inlineStr"/>
       <c r="K601" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34100,12 +34092,12 @@
       <c r="J602" t="inlineStr"/>
       <c r="K602" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34158,12 +34150,12 @@
       <c r="J603" t="inlineStr"/>
       <c r="K603" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34216,12 +34208,12 @@
       <c r="J604" t="inlineStr"/>
       <c r="K604" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34274,12 +34266,12 @@
       <c r="J605" t="inlineStr"/>
       <c r="K605" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34332,12 +34324,12 @@
       <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34390,12 +34382,12 @@
       <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34448,12 +34440,12 @@
       <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34506,12 +34498,12 @@
       <c r="J609" t="inlineStr"/>
       <c r="K609" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34559,12 +34551,12 @@
       <c r="J610" t="inlineStr"/>
       <c r="K610" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34617,12 +34609,12 @@
       <c r="J611" t="inlineStr"/>
       <c r="K611" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34675,12 +34667,12 @@
       <c r="J612" t="inlineStr"/>
       <c r="K612" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L612" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34733,12 +34725,12 @@
       <c r="J613" t="inlineStr"/>
       <c r="K613" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34790,12 +34782,12 @@
       </c>
       <c r="K614" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M614" t="inlineStr">
         <is>
-          <t>1 day, 20:13:18.856082</t>
+          <t>20:13:49.094825</t>
         </is>
       </c>
     </row>
@@ -34843,12 +34835,12 @@
       <c r="J615" t="inlineStr"/>
       <c r="K615" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34896,12 +34888,12 @@
       <c r="J616" t="inlineStr"/>
       <c r="K616" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -34949,12 +34941,12 @@
       <c r="J617" t="inlineStr"/>
       <c r="K617" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35002,12 +34994,12 @@
       <c r="J618" t="inlineStr"/>
       <c r="K618" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35055,12 +35047,12 @@
       <c r="J619" t="inlineStr"/>
       <c r="K619" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35108,12 +35100,12 @@
       <c r="J620" t="inlineStr"/>
       <c r="K620" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35161,12 +35153,12 @@
       <c r="J621" t="inlineStr"/>
       <c r="K621" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35214,12 +35206,12 @@
       <c r="J622" t="inlineStr"/>
       <c r="K622" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35267,12 +35259,12 @@
       <c r="J623" t="inlineStr"/>
       <c r="K623" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35320,12 +35312,12 @@
       <c r="J624" t="inlineStr"/>
       <c r="K624" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35377,12 +35369,12 @@
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M625" t="inlineStr">
         <is>
-          <t>1 day, 19:43:18.855778</t>
+          <t>19:43:49.094508</t>
         </is>
       </c>
     </row>
@@ -35430,12 +35422,12 @@
       <c r="J626" t="inlineStr"/>
       <c r="K626" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L626" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35488,12 +35480,12 @@
       <c r="J627" t="inlineStr"/>
       <c r="K627" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L627" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35546,12 +35538,12 @@
       <c r="J628" t="inlineStr"/>
       <c r="K628" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35604,12 +35596,12 @@
       <c r="J629" t="inlineStr"/>
       <c r="K629" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L629" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35662,12 +35654,12 @@
       <c r="J630" t="inlineStr"/>
       <c r="K630" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35720,12 +35712,12 @@
       <c r="J631" t="inlineStr"/>
       <c r="K631" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35778,12 +35770,12 @@
       <c r="J632" t="inlineStr"/>
       <c r="K632" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L632" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35836,12 +35828,12 @@
       <c r="J633" t="inlineStr"/>
       <c r="K633" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35894,12 +35886,12 @@
       <c r="J634" t="inlineStr"/>
       <c r="K634" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L634" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -35952,12 +35944,12 @@
       <c r="J635" t="inlineStr"/>
       <c r="K635" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L635" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -36010,12 +36002,12 @@
       <c r="J636" t="inlineStr"/>
       <c r="K636" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L636" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -36068,12 +36060,12 @@
       <c r="J637" t="inlineStr"/>
       <c r="K637" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L637" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -36121,12 +36113,12 @@
       <c r="J638" t="inlineStr"/>
       <c r="K638" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L638" t="inlineStr">
         <is>
-          <t>08/14/26 11:16 AM</t>
+          <t>08/15/26 11:16 AM</t>
         </is>
       </c>
     </row>
@@ -36178,12 +36170,12 @@
       </c>
       <c r="K639" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M639" t="inlineStr">
         <is>
-          <t>1 day, 19:43:18.855377</t>
+          <t>19:43:49.094105</t>
         </is>
       </c>
     </row>
@@ -36235,12 +36227,12 @@
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M640" t="inlineStr">
         <is>
-          <t>1 day, 19:43:18.855339</t>
+          <t>19:43:49.094068</t>
         </is>
       </c>
     </row>
@@ -36292,12 +36284,12 @@
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M641" t="inlineStr">
         <is>
-          <t>1 day, 19:43:18.855302</t>
+          <t>19:43:49.094034</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -551,12 +551,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>23 days, 20:22:26.808971</t>
+          <t>22 days, 20:19:00.984271</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -661,12 +661,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>23 days, 3:22:26.808847</t>
+          <t>22 days, 3:19:00.984147</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>23 days, 2:22:26.808806</t>
+          <t>22 days, 2:19:00.984101</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>23 days, 2:22:26.808772</t>
+          <t>22 days, 2:19:00.984059</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>23 days, 2:22:26.808740</t>
+          <t>22 days, 2:19:00.984013</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>23 days, 2:22:26.808709</t>
+          <t>22 days, 2:19:00.983973</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>23 days, 2:22:26.808676</t>
+          <t>22 days, 2:19:00.983931</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>23 days, 2:22:26.808608</t>
+          <t>22 days, 2:19:00.983892</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>23 days, 2:22:26.808565</t>
+          <t>22 days, 2:19:00.983823</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>23 days, 2:07:26.808533</t>
+          <t>22 days, 2:04:00.983779</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>23 days, 2:07:26.808501</t>
+          <t>22 days, 2:04:00.983741</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>23 days, 2:07:26.808469</t>
+          <t>22 days, 2:04:00.983703</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>23 days, 2:07:26.808438</t>
+          <t>22 days, 2:04:00.983664</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>23 days, 2:07:26.808409</t>
+          <t>22 days, 2:04:00.983628</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>23 days, 2:07:26.808378</t>
+          <t>22 days, 2:04:00.983592</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>23 days, 2:07:26.808347</t>
+          <t>22 days, 2:04:00.983555</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>23 days, 2:07:26.808317</t>
+          <t>22 days, 2:04:00.983519</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>23 days, 2:07:26.808288</t>
+          <t>22 days, 2:04:00.983483</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>23 days, 2:07:26.808258</t>
+          <t>22 days, 2:04:00.983448</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>23 days, 2:07:26.808228</t>
+          <t>22 days, 2:04:00.983412</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>23 days, 1:37:26.808198</t>
+          <t>22 days, 1:34:00.983375</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>23 days, 1:37:26.808168</t>
+          <t>22 days, 1:34:00.983339</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>23 days, 1:37:26.808135</t>
+          <t>22 days, 1:34:00.983299</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>23 days, 1:37:26.808101</t>
+          <t>22 days, 1:34:00.983259</t>
         </is>
       </c>
     </row>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>23 days, 1:37:26.808069</t>
+          <t>22 days, 1:34:00.983219</t>
         </is>
       </c>
     </row>
@@ -2050,12 +2050,12 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>19 days, 20:22:26.807968</t>
+          <t>18 days, 20:19:00.983100</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>19 days, 5:22:26.807938</t>
+          <t>18 days, 5:19:00.983062</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2274,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>19 days, 5:22:26.807909</t>
+          <t>18 days, 5:19:00.983027</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19 days, 5:22:26.807882</t>
+          <t>18 days, 5:19:00.982993</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19 days, 4:22:26.807793</t>
+          <t>18 days, 4:19:00.982886</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>18 days, 22:22:26.807762</t>
+          <t>17 days, 22:19:00.982824</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2604,12 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2719,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>17 days, 23:52:26.807683</t>
+          <t>16 days, 23:49:00.982720</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -2825,12 +2825,12 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -2878,12 +2878,12 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -2931,12 +2931,12 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -2980,12 +2980,12 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>17 days, 22:07:26.807522</t>
+          <t>16 days, 22:04:00.982537</t>
         </is>
       </c>
     </row>
@@ -3090,12 +3090,12 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -3143,12 +3143,12 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -3200,12 +3200,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>17 days, 22:07:26.807442</t>
+          <t>16 days, 22:04:00.982439</t>
         </is>
       </c>
     </row>
@@ -3253,12 +3253,12 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -3412,12 +3412,12 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -3628,12 +3628,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>17 days, 20:22:26.807230</t>
+          <t>16 days, 20:19:00.982190</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>17 days, 20:22:26.807196</t>
+          <t>16 days, 20:19:00.982154</t>
         </is>
       </c>
     </row>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>17 days, 20:22:26.807161</t>
+          <t>16 days, 20:19:00.982116</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>17 days, 20:22:26.807131</t>
+          <t>16 days, 20:19:00.982080</t>
         </is>
       </c>
     </row>
@@ -3852,12 +3852,12 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -3905,12 +3905,12 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -3958,12 +3958,12 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4064,12 +4064,12 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4117,12 +4117,12 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4170,12 +4170,12 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4223,12 +4223,12 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4276,12 +4276,12 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4329,12 +4329,12 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4386,12 +4386,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>17 days, 20:22:26.806843</t>
+          <t>16 days, 20:19:00.981719</t>
         </is>
       </c>
     </row>
@@ -4443,12 +4443,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>17 days, 20:22:26.806811</t>
+          <t>16 days, 20:19:00.981673</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4549,12 +4549,12 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4602,12 +4602,12 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4655,12 +4655,12 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4708,12 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4761,12 +4761,12 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4867,12 +4867,12 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>17 days, 20:22:26.806555</t>
+          <t>16 days, 20:19:00.981380</t>
         </is>
       </c>
     </row>
@@ -4977,12 +4977,12 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5030,12 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5136,12 +5136,12 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5242,12 +5242,12 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5348,12 +5348,12 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5410,12 +5410,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>17 days, 5:52:26.806317</t>
+          <t>16 days, 5:49:00.981092</t>
         </is>
       </c>
     </row>
@@ -5472,12 +5472,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>17 days, 5:52:26.806291</t>
+          <t>16 days, 5:49:00.981058</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5578,12 +5578,12 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5684,12 +5684,12 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5790,12 +5790,12 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5901,12 +5901,12 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -5959,12 +5959,12 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6012,12 +6012,12 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6118,12 +6118,12 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6171,12 +6171,12 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6277,12 +6277,12 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6383,12 +6383,12 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6489,12 +6489,12 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6595,12 +6595,12 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6701,12 +6701,12 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6754,12 +6754,12 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6807,12 +6807,12 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -6970,12 +6970,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>12 days, 1:22:26.805603</t>
+          <t>11 days, 1:19:00.980214</t>
         </is>
       </c>
     </row>
@@ -7027,12 +7027,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>12 days, 1:22:26.805574</t>
+          <t>11 days, 1:19:00.980177</t>
         </is>
       </c>
     </row>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>12 days, 1:22:26.805546</t>
+          <t>11 days, 1:19:00.980145</t>
         </is>
       </c>
     </row>
@@ -7137,12 +7137,12 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -7190,12 +7190,12 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -7243,12 +7243,12 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -7296,12 +7296,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -7402,12 +7402,12 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -7508,12 +7508,12 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -7561,12 +7561,12 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -7614,12 +7614,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -7667,12 +7667,12 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.805228</t>
+          <t>10 days, 23:49:00.979743</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.805195</t>
+          <t>10 days, 23:49:00.979701</t>
         </is>
       </c>
     </row>
@@ -7891,12 +7891,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.805162</t>
+          <t>10 days, 23:49:00.979661</t>
         </is>
       </c>
     </row>
@@ -7948,12 +7948,12 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.805128</t>
+          <t>10 days, 23:49:00.979622</t>
         </is>
       </c>
     </row>
@@ -8005,12 +8005,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.805099</t>
+          <t>10 days, 23:49:00.979586</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.805069</t>
+          <t>10 days, 23:49:00.979550</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.805040</t>
+          <t>10 days, 23:49:00.979515</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.805011</t>
+          <t>10 days, 23:49:00.979480</t>
         </is>
       </c>
     </row>
@@ -8233,12 +8233,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.804982</t>
+          <t>10 days, 23:49:00.979444</t>
         </is>
       </c>
     </row>
@@ -8290,12 +8290,12 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.804951</t>
+          <t>10 days, 23:49:00.979407</t>
         </is>
       </c>
     </row>
@@ -8347,12 +8347,12 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.804919</t>
+          <t>10 days, 23:49:00.979366</t>
         </is>
       </c>
     </row>
@@ -8404,12 +8404,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.804886</t>
+          <t>10 days, 23:49:00.979328</t>
         </is>
       </c>
     </row>
@@ -8461,12 +8461,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.804853</t>
+          <t>10 days, 23:49:00.979288</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.804821</t>
+          <t>10 days, 23:49:00.979250</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.804787</t>
+          <t>10 days, 23:49:00.979208</t>
         </is>
       </c>
     </row>
@@ -8632,12 +8632,12 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.804754</t>
+          <t>10 days, 23:49:00.979169</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.804719</t>
+          <t>10 days, 23:49:00.979129</t>
         </is>
       </c>
     </row>
@@ -8746,12 +8746,12 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>11 days, 23:52:26.804684</t>
+          <t>10 days, 23:49:00.979089</t>
         </is>
       </c>
     </row>
@@ -8804,12 +8804,12 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -8978,12 +8978,12 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9210,12 +9210,12 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9268,12 +9268,12 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9326,12 +9326,12 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>11 days, 20:22:26.804357</t>
+          <t>10 days, 20:19:00.978730</t>
         </is>
       </c>
     </row>
@@ -9446,12 +9446,12 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9504,12 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9562,12 +9562,12 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9620,12 +9620,12 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9678,12 +9678,12 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9784,12 +9784,12 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9837,12 +9837,12 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9890,12 +9890,12 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9943,12 +9943,12 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -9996,12 +9996,12 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10049,12 +10049,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10102,12 +10102,12 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10155,12 +10155,12 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10208,12 +10208,12 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10261,12 +10261,12 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10314,12 +10314,12 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10367,12 +10367,12 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10420,12 +10420,12 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10473,12 +10473,12 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10526,12 +10526,12 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10579,12 +10579,12 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10632,12 +10632,12 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10685,12 +10685,12 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10738,12 +10738,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10791,12 +10791,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10844,12 +10844,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10897,12 +10897,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -10950,12 +10950,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11003,12 +11003,12 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11056,12 +11056,12 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11109,12 +11109,12 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11162,12 +11162,12 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11268,12 +11268,12 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11321,12 +11321,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11374,12 +11374,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11427,12 +11427,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11484,12 +11484,12 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>8 days, 23:52:26.803332</t>
+          <t>7 days, 23:49:00.977553</t>
         </is>
       </c>
     </row>
@@ -11537,12 +11537,12 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11590,12 +11590,12 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11643,12 +11643,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11696,12 +11696,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11749,12 +11749,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11802,12 +11802,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11855,12 +11855,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11908,12 +11908,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -11961,12 +11961,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12014,12 +12014,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12067,12 +12067,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12120,12 +12120,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12173,12 +12173,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12226,12 +12226,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12279,12 +12279,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12332,12 +12332,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12385,12 +12385,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12438,12 +12438,12 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12491,12 +12491,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12544,12 +12544,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12597,12 +12597,12 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12650,12 +12650,12 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12707,12 +12707,12 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>8 days, 20:22:26.802758</t>
+          <t>7 days, 20:19:00.976843</t>
         </is>
       </c>
     </row>
@@ -12764,12 +12764,12 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>8 days, 20:22:26.802731</t>
+          <t>7 days, 20:19:00.976806</t>
         </is>
       </c>
     </row>
@@ -12821,12 +12821,12 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>8 days, 20:22:26.802703</t>
+          <t>7 days, 20:19:00.976772</t>
         </is>
       </c>
     </row>
@@ -12874,12 +12874,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12927,12 +12927,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -12980,12 +12980,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13033,12 +13033,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13086,12 +13086,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13139,12 +13139,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13192,12 +13192,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13245,12 +13245,12 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13298,12 +13298,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13351,12 +13351,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13457,12 +13457,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13510,12 +13510,12 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13563,12 +13563,12 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13616,12 +13616,12 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13669,12 +13669,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13722,12 +13722,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13775,12 +13775,12 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13828,12 +13828,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13881,12 +13881,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13934,12 +13934,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -13987,12 +13987,12 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14040,12 +14040,12 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14093,12 +14093,12 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14146,12 +14146,12 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14199,12 +14199,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14252,12 +14252,12 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14305,12 +14305,12 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14358,12 +14358,12 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14411,12 +14411,12 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14464,12 +14464,12 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14517,12 +14517,12 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14570,12 +14570,12 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14623,12 +14623,12 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14676,12 +14676,12 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14729,12 +14729,12 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14782,12 +14782,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14835,12 +14835,12 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14941,12 +14941,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -14994,12 +14994,12 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15047,12 +15047,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15100,12 +15100,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15153,12 +15153,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15206,12 +15206,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15263,12 +15263,12 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>4 days, 0:07:26.801586</t>
+          <t>3 days, 0:04:00.975430</t>
         </is>
       </c>
     </row>
@@ -15316,12 +15316,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15373,12 +15373,12 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>4 days, 0:07:26.801537</t>
+          <t>3 days, 0:04:00.975369</t>
         </is>
       </c>
     </row>
@@ -15426,12 +15426,12 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15479,12 +15479,12 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15532,12 +15532,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15585,12 +15585,12 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15638,12 +15638,12 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15691,12 +15691,12 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15744,12 +15744,12 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15797,12 +15797,12 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15850,12 +15850,12 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15903,12 +15903,12 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -15956,12 +15956,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16009,12 +16009,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16062,12 +16062,12 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16115,12 +16115,12 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16168,12 +16168,12 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16221,12 +16221,12 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16274,12 +16274,12 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16327,12 +16327,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16380,12 +16380,12 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16433,12 +16433,12 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16486,12 +16486,12 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16539,12 +16539,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16592,12 +16592,12 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16645,12 +16645,12 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16698,12 +16698,12 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16756,12 +16756,12 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16814,12 +16814,12 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16872,12 +16872,12 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16930,12 +16930,12 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -16988,12 +16988,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -17046,12 +17046,12 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -17104,12 +17104,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -17162,12 +17162,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -17215,12 +17215,12 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -17268,12 +17268,12 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -17321,12 +17321,12 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -17374,12 +17374,12 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -17427,12 +17427,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>
@@ -17480,12 +17480,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>08/21/26 10:37 AM</t>
+          <t>08/22/26 10:40 AM</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -546,12 +546,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>23 days, 16:45:22.232103</t>
+          <t>22 days, 16:39:08.481465</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -652,12 +652,12 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -810,17 +810,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ATT01, COMDC, MCI03, PEPCODC, QGS06, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>ATT01, COMDC, MCI03, QGS06, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>19 days, 20:30:22.231822</t>
+          <t>18 days, 20:24:08.481205</t>
         </is>
       </c>
     </row>
@@ -867,17 +867,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ATT01, MCI03, PEPCODC, QGS06, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
+          <t>ATT01, MCI03, QGS06, WASA02 &amp; WGL07 - Not yet responded &amp; DCDOT01 - Not complete/In progress</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>19 days, 20:30:22.231767</t>
+          <t>18 days, 20:24:08.481151</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>19 days, 19:45:22.231726</t>
+          <t>18 days, 19:39:08.481111</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>19 days, 19:45:22.231688</t>
+          <t>18 days, 19:39:08.481073</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>19 days, 19:45:22.231648</t>
+          <t>18 days, 19:39:08.481035</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>19 days, 19:45:22.231611</t>
+          <t>18 days, 19:39:08.480998</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>19 days, 19:45:22.231574</t>
+          <t>18 days, 19:39:08.480962</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19 days, 19:45:22.231539</t>
+          <t>18 days, 19:39:08.480927</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19 days, 19:45:22.231504</t>
+          <t>18 days, 19:39:08.480892</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>19 days, 19:45:22.231470</t>
+          <t>18 days, 19:39:08.480858</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19 days, 19:45:22.231435</t>
+          <t>18 days, 19:39:08.480823</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>19 days, 19:45:22.231397</t>
+          <t>18 days, 19:39:08.480787</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19 days, 19:45:22.231361</t>
+          <t>18 days, 19:39:08.480751</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>19 days, 19:45:22.231328</t>
+          <t>18 days, 19:39:08.480717</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.231293</t>
+          <t>18 days, 16:39:08.480640</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.231259</t>
+          <t>18 days, 16:39:08.480598</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.231226</t>
+          <t>18 days, 16:39:08.480563</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.231193</t>
+          <t>18 days, 16:39:08.480529</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.231160</t>
+          <t>18 days, 16:39:08.480496</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.231127</t>
+          <t>18 days, 16:39:08.480462</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.231094</t>
+          <t>18 days, 16:39:08.480428</t>
         </is>
       </c>
     </row>
@@ -2012,12 +2012,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.231041</t>
+          <t>18 days, 16:39:08.480395</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.231006</t>
+          <t>18 days, 16:39:08.480356</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230973</t>
+          <t>18 days, 16:39:08.480321</t>
         </is>
       </c>
     </row>
@@ -2183,12 +2183,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230939</t>
+          <t>18 days, 16:39:08.480289</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230905</t>
+          <t>18 days, 16:39:08.480255</t>
         </is>
       </c>
     </row>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230874</t>
+          <t>18 days, 16:39:08.480223</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2347,19 +2347,15 @@
           <t>09/25/26 07:00 am</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>19 days, 16:45:22.230843</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2377,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2404,19 +2400,15 @@
           <t>09/25/26 07:00 am</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>19 days, 16:45:22.230813</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2430,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2461,19 +2453,15 @@
           <t>09/25/26 07:00 am</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>19 days, 16:45:22.230781</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2513,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230751</t>
+          <t>18 days, 16:39:08.480099</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2570,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230719</t>
+          <t>18 days, 16:39:08.480062</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2597,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2632,19 +2620,15 @@
           <t>09/25/26 07:00 am</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>19 days, 16:45:22.230687</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2680,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230654</t>
+          <t>18 days, 16:39:08.479999</t>
         </is>
       </c>
     </row>
@@ -2748,17 +2732,17 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>COMDC &amp; WGL07 - Not yet responded</t>
+          <t>COMDC - Not yet responded</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230621</t>
+          <t>18 days, 16:39:08.479966</t>
         </is>
       </c>
     </row>
@@ -2810,12 +2794,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230588</t>
+          <t>18 days, 16:39:08.479932</t>
         </is>
       </c>
     </row>
@@ -2867,12 +2851,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230557</t>
+          <t>18 days, 16:39:08.479900</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2878,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2917,19 +2901,15 @@
           <t>09/25/26 07:00 am</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>19 days, 16:45:22.230526</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -2981,12 +2961,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230495</t>
+          <t>18 days, 16:39:08.479839</t>
         </is>
       </c>
     </row>
@@ -3038,12 +3018,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230465</t>
+          <t>18 days, 16:39:08.479807</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3045,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3088,19 +3068,15 @@
           <t>09/25/26 07:00 am</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>19 days, 16:45:22.230436</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -3152,12 +3128,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230404</t>
+          <t>18 days, 16:39:08.479745</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3155,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3202,19 +3178,15 @@
           <t>09/25/26 07:00 am</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>19 days, 16:45:22.230374</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3208,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3259,19 +3231,15 @@
           <t>09/25/26 07:00 am</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>19 days, 16:45:22.230345</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -3318,17 +3286,17 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>COMDC &amp; WGL07 - Not yet responded</t>
+          <t>COMDC - Not yet responded</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>19 days, 16:45:22.230313</t>
+          <t>18 days, 16:39:08.479631</t>
         </is>
       </c>
     </row>
@@ -3380,12 +3348,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.230281</t>
+          <t>17 days, 21:09:08.479596</t>
         </is>
       </c>
     </row>
@@ -3437,12 +3405,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.230249</t>
+          <t>17 days, 21:09:08.479564</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3462,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.230217</t>
+          <t>17 days, 21:09:08.479532</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3519,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.230185</t>
+          <t>17 days, 21:09:08.479500</t>
         </is>
       </c>
     </row>
@@ -3608,12 +3576,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.230154</t>
+          <t>17 days, 21:09:08.479468</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3633,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.230122</t>
+          <t>17 days, 21:09:08.479433</t>
         </is>
       </c>
     </row>
@@ -3722,12 +3690,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.230090</t>
+          <t>17 days, 21:09:08.479399</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3747,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.230040</t>
+          <t>17 days, 21:09:08.479366</t>
         </is>
       </c>
     </row>
@@ -3836,12 +3804,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.230003</t>
+          <t>17 days, 21:09:08.479332</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3861,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.229970</t>
+          <t>17 days, 21:09:08.479298</t>
         </is>
       </c>
     </row>
@@ -3950,12 +3918,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.229938</t>
+          <t>17 days, 21:09:08.479258</t>
         </is>
       </c>
     </row>
@@ -4007,12 +3975,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.229907</t>
+          <t>17 days, 21:09:08.479223</t>
         </is>
       </c>
     </row>
@@ -4064,12 +4032,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.229875</t>
+          <t>17 days, 21:09:08.479192</t>
         </is>
       </c>
     </row>
@@ -4121,12 +4089,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.229844</t>
+          <t>17 days, 21:09:08.479162</t>
         </is>
       </c>
     </row>
@@ -4178,12 +4146,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>18 days, 21:15:22.229813</t>
+          <t>17 days, 21:09:08.479130</t>
         </is>
       </c>
     </row>
@@ -4235,12 +4203,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>17 days, 18:00:22.229782</t>
+          <t>16 days, 17:54:08.479099</t>
         </is>
       </c>
     </row>
@@ -4293,12 +4261,12 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4319,12 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -4408,17 +4376,17 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>WASA02 - Not complete/In progress</t>
+          <t>WASA02 - Dispute - Status Pending</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>17 days, 17:45:22.229668</t>
+          <t>16 days, 17:39:08.478978</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4439,12 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -4524,12 +4492,12 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -4577,12 +4545,12 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -4635,12 +4603,12 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4661,12 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -4751,12 +4719,12 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -4809,12 +4777,12 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -4867,12 +4835,12 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -4925,12 +4893,12 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -4983,12 +4951,12 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5004,12 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5093,12 +5061,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>15 days, 19:45:22.229265</t>
+          <t>14 days, 19:39:08.478532</t>
         </is>
       </c>
     </row>
@@ -5146,12 +5114,12 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5204,12 +5172,12 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5262,12 +5230,12 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5320,12 +5288,12 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5378,12 +5346,12 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5436,12 +5404,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5494,12 +5462,12 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5552,12 +5520,12 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5610,12 +5578,12 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5668,12 +5636,12 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5698,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>15 days, 17:15:22.228882</t>
+          <t>14 days, 17:09:08.478186</t>
         </is>
       </c>
     </row>
@@ -5788,12 +5756,12 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5814,12 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5904,12 +5872,12 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5930,12 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6020,12 +5988,12 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6046,12 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6136,12 +6104,12 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6162,12 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6252,12 +6220,12 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6310,12 +6278,12 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6368,12 +6336,12 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6394,12 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6484,12 +6452,12 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6510,12 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6600,12 +6568,12 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6658,12 +6626,12 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6716,12 +6684,12 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6774,12 +6742,12 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6832,12 +6800,12 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6890,12 +6858,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -6948,12 +6916,12 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7006,12 +6974,12 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7032,12 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7090,12 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7175,12 +7143,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7232,12 +7200,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>12 days, 19:45:22.228102</t>
+          <t>11 days, 19:39:08.477369</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7257,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>12 days, 19:45:22.228038</t>
+          <t>11 days, 19:39:08.477330</t>
         </is>
       </c>
     </row>
@@ -7346,12 +7314,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>12 days, 19:45:22.227994</t>
+          <t>11 days, 19:39:08.477292</t>
         </is>
       </c>
     </row>
@@ -7398,17 +7366,17 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>ATT01 - Not yet responded &amp; WASA02 - Not complete/In progress</t>
+          <t>ATT01 - Not yet responded &amp; WASA02 - Dispute - Status Pending</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>12 days, 19:45:22.227958</t>
+          <t>11 days, 19:39:08.477257</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7424,12 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7509,12 +7477,12 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7562,12 +7530,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7615,12 +7583,12 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7636,12 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7689,12 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7774,12 +7742,12 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7827,12 +7795,12 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7880,12 +7848,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -7937,12 +7905,12 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>11 days, 22:30:22.227624</t>
+          <t>10 days, 22:24:08.476934</t>
         </is>
       </c>
     </row>
@@ -7995,12 +7963,12 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8048,12 +8016,12 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8101,12 +8069,12 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8122,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8211,12 +8179,12 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>11 days, 21:45:22.227443</t>
+          <t>10 days, 21:39:08.476759</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8232,12 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8285,12 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8375,12 +8343,12 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8433,12 +8401,12 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8486,12 +8454,12 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8539,12 +8507,12 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8592,12 +8560,12 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8645,12 +8613,12 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8666,12 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8719,12 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8804,12 +8772,12 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8857,12 +8825,12 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8910,12 +8878,12 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -8963,12 +8931,12 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9016,12 +8984,12 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9069,12 +9037,12 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9122,12 +9090,12 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9175,12 +9143,12 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9228,12 +9196,12 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9281,12 +9249,12 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9338,12 +9306,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>11 days, 19:00:22.226760</t>
+          <t>10 days, 18:54:08.476106</t>
         </is>
       </c>
     </row>
@@ -9391,12 +9359,12 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9444,12 +9412,12 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9497,12 +9465,12 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9518,12 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9571,12 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9660,12 +9628,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>11 days, 19:00:22.226567</t>
+          <t>10 days, 18:54:08.475917</t>
         </is>
       </c>
     </row>
@@ -9717,12 +9685,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>11 days, 19:00:22.226529</t>
+          <t>10 days, 18:54:08.475879</t>
         </is>
       </c>
     </row>
@@ -9770,12 +9738,12 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9823,12 +9791,12 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9876,12 +9844,12 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9929,12 +9897,12 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9950,12 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10035,12 +10003,12 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10060,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>11 days, 18:00:22.226329</t>
+          <t>10 days, 17:54:08.475639</t>
         </is>
       </c>
     </row>
@@ -10145,12 +10113,12 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10198,12 +10166,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10251,12 +10219,12 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10304,12 +10272,12 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10357,12 +10325,12 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10410,12 +10378,12 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10463,12 +10431,12 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10484,12 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10569,12 +10537,12 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10622,12 +10590,12 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10675,12 +10643,12 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10728,12 +10696,12 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10749,12 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10834,12 +10802,12 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10887,12 +10855,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10940,12 +10908,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -10993,12 +10961,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11046,12 +11014,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11099,12 +11067,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11152,12 +11120,12 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11205,12 +11173,12 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11258,12 +11226,12 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11279,12 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11364,12 +11332,12 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11417,12 +11385,12 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11470,12 +11438,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11523,12 +11491,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11576,12 +11544,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11629,12 +11597,12 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11682,12 +11650,12 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11735,12 +11703,12 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11788,12 +11756,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11809,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11894,12 +11862,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -11947,12 +11915,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12000,12 +11968,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12053,12 +12021,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12074,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12159,12 +12127,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12212,12 +12180,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12265,12 +12233,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12318,12 +12286,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12371,12 +12339,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12424,12 +12392,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12477,12 +12445,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12498,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12587,12 +12555,12 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>11 days, 17:30:22.224933</t>
+          <t>10 days, 17:24:08.474197</t>
         </is>
       </c>
     </row>
@@ -12640,12 +12608,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12693,12 +12661,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12746,12 +12714,12 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12799,12 +12767,12 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12852,12 +12820,12 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12905,12 +12873,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -12958,12 +12926,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13011,12 +12979,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13032,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13117,12 +13085,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13170,12 +13138,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13223,12 +13191,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13276,12 +13244,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13329,12 +13297,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13382,12 +13350,12 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13435,12 +13403,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13488,12 +13456,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13541,12 +13509,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13594,12 +13562,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13647,12 +13615,12 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13700,12 +13668,12 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13753,12 +13721,12 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13806,12 +13774,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13859,12 +13827,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13912,12 +13880,12 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -13965,12 +13933,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14018,12 +13986,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14071,12 +14039,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14124,12 +14092,12 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14177,12 +14145,12 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14230,12 +14198,12 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14283,12 +14251,12 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14336,12 +14304,12 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14393,12 +14361,12 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>11 days, 17:00:22.223951</t>
+          <t>10 days, 16:54:08.473227</t>
         </is>
       </c>
     </row>
@@ -14446,12 +14414,12 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14499,12 +14467,12 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14552,12 +14520,12 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14605,12 +14573,12 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14658,12 +14626,12 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14711,12 +14679,12 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14764,12 +14732,12 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14817,12 +14785,12 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14870,12 +14838,12 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14923,12 +14891,12 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -14976,12 +14944,12 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15029,12 +14997,12 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15082,12 +15050,12 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15135,12 +15103,12 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15188,12 +15156,12 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15241,12 +15209,12 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15294,12 +15262,12 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15315,12 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15400,12 +15368,12 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15453,12 +15421,12 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15506,12 +15474,12 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15559,12 +15527,12 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15612,12 +15580,12 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15665,12 +15633,12 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15718,12 +15686,12 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15771,12 +15739,12 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15824,12 +15792,12 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15877,12 +15845,12 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15935,12 +15903,12 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -15993,12 +15961,12 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16051,12 +16019,12 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16109,12 +16077,12 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16167,12 +16135,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16225,12 +16193,12 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16287,12 +16255,12 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>10 days, 23:00:22.222867</t>
+          <t>9 days, 22:54:08.472147</t>
         </is>
       </c>
     </row>
@@ -16345,12 +16313,12 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16403,12 +16371,12 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16461,12 +16429,12 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16519,12 +16487,12 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16577,12 +16545,12 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16635,12 +16603,12 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16693,12 +16661,12 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16751,12 +16719,12 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16809,12 +16777,12 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16867,12 +16835,12 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16925,12 +16893,12 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -16983,12 +16951,12 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17041,12 +17009,12 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17099,12 +17067,12 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17157,12 +17125,12 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17215,12 +17183,12 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17273,12 +17241,12 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17331,12 +17299,12 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17389,12 +17357,12 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17447,12 +17415,12 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17505,12 +17473,12 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17563,12 +17531,12 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17621,12 +17589,12 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17679,12 +17647,12 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17737,12 +17705,12 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17795,12 +17763,12 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17853,12 +17821,12 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17911,12 +17879,12 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -17969,12 +17937,12 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18027,12 +17995,12 @@
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18085,12 +18053,12 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18143,12 +18111,12 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18201,12 +18169,12 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18259,12 +18227,12 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18317,12 +18285,12 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18375,12 +18343,12 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18433,12 +18401,12 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18491,12 +18459,12 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18549,12 +18517,12 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18607,12 +18575,12 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18665,12 +18633,12 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18723,12 +18691,12 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18781,12 +18749,12 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18839,12 +18807,12 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18897,12 +18865,12 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -18955,12 +18923,12 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19013,12 +18981,12 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19071,12 +19039,12 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19129,12 +19097,12 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19187,12 +19155,12 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19245,12 +19213,12 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19303,12 +19271,12 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19361,12 +19329,12 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19419,12 +19387,12 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19477,12 +19445,12 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19535,12 +19503,12 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19593,12 +19561,12 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19650,12 +19618,12 @@
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>10 days, 22:15:22.221216</t>
+          <t>9 days, 22:09:08.470459</t>
         </is>
       </c>
     </row>
@@ -19707,12 +19675,12 @@
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>10 days, 22:15:22.221173</t>
+          <t>9 days, 22:09:08.470415</t>
         </is>
       </c>
     </row>
@@ -19760,12 +19728,12 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19813,12 +19781,12 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19866,12 +19834,12 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19924,12 +19892,12 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -19982,12 +19950,12 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20040,12 +20008,12 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20098,12 +20066,12 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20156,12 +20124,12 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20214,12 +20182,12 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20272,12 +20240,12 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20330,12 +20298,12 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20388,12 +20356,12 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20446,12 +20414,12 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20503,12 +20471,12 @@
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>10 days, 16:45:22.220710</t>
+          <t>9 days, 16:39:08.469968</t>
         </is>
       </c>
     </row>
@@ -20560,12 +20528,12 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>10 days, 16:45:22.220672</t>
+          <t>9 days, 16:39:08.469930</t>
         </is>
       </c>
     </row>
@@ -20613,12 +20581,12 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20666,12 +20634,12 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20719,12 +20687,12 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20772,12 +20740,12 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20825,12 +20793,12 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20878,12 +20846,12 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20931,12 +20899,12 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -20984,12 +20952,12 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21037,12 +21005,12 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21094,12 +21062,12 @@
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>9 days, 21:30:22.220374</t>
+          <t>8 days, 21:24:08.469607</t>
         </is>
       </c>
     </row>
@@ -21147,12 +21115,12 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21200,12 +21168,12 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21253,12 +21221,12 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21306,12 +21274,12 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21359,12 +21327,12 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21412,12 +21380,12 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21465,12 +21433,12 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21518,12 +21486,12 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21571,12 +21539,12 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21624,12 +21592,12 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21681,12 +21649,12 @@
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>9 days, 20:45:22.220090</t>
+          <t>8 days, 20:39:08.469322</t>
         </is>
       </c>
     </row>
@@ -21734,12 +21702,12 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21787,12 +21755,12 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21840,12 +21808,12 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21893,12 +21861,12 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21946,12 +21914,12 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -21999,12 +21967,12 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22052,12 +22020,12 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22105,12 +22073,12 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22158,12 +22126,12 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22211,12 +22179,12 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22264,12 +22232,12 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22317,12 +22285,12 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22370,12 +22338,12 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22423,12 +22391,12 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22476,12 +22444,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22529,12 +22497,12 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22582,12 +22550,12 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22635,12 +22603,12 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22688,12 +22656,12 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22741,12 +22709,12 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22794,12 +22762,12 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22851,12 +22819,12 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>9 days, 19:15:22.219443</t>
+          <t>8 days, 19:09:08.468740</t>
         </is>
       </c>
     </row>
@@ -22904,12 +22872,12 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -22957,12 +22925,12 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23010,12 +22978,12 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23063,12 +23031,12 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23116,12 +23084,12 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23173,12 +23141,12 @@
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>9 days, 19:15:22.219230</t>
+          <t>8 days, 19:09:08.468494</t>
         </is>
       </c>
     </row>
@@ -23226,12 +23194,12 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23279,12 +23247,12 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23332,12 +23300,12 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23385,12 +23353,12 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23438,12 +23406,12 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23491,12 +23459,12 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23544,12 +23512,12 @@
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23597,12 +23565,12 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23650,12 +23618,12 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23703,12 +23671,12 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23756,12 +23724,12 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23809,12 +23777,12 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23862,12 +23830,12 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23915,12 +23883,12 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -23968,12 +23936,12 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24021,12 +23989,12 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24074,12 +24042,12 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24127,12 +24095,12 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24180,12 +24148,12 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24233,12 +24201,12 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24286,12 +24254,12 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24339,12 +24307,12 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24392,12 +24360,12 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24445,12 +24413,12 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24498,12 +24466,12 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24551,12 +24519,12 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24604,12 +24572,12 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24657,12 +24625,12 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24710,12 +24678,12 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24763,12 +24731,12 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24816,12 +24784,12 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24869,12 +24837,12 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24922,12 +24890,12 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -24975,12 +24943,12 @@
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25028,12 +24996,12 @@
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25081,12 +25049,12 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25138,12 +25106,12 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>9 days, 18:00:22.218127</t>
+          <t>8 days, 17:54:08.467375</t>
         </is>
       </c>
     </row>
@@ -25191,12 +25159,12 @@
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25244,12 +25212,12 @@
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25297,12 +25265,12 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25350,12 +25318,12 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25403,12 +25371,12 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25456,12 +25424,12 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25509,12 +25477,12 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25562,12 +25530,12 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25615,12 +25583,12 @@
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25668,12 +25636,12 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25721,12 +25689,12 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25774,12 +25742,12 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25827,12 +25795,12 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25880,12 +25848,12 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25933,12 +25901,12 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -25986,12 +25954,12 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26039,12 +26007,12 @@
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26092,12 +26060,12 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26145,12 +26113,12 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26198,12 +26166,12 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26251,12 +26219,12 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26304,12 +26272,12 @@
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26357,12 +26325,12 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26410,12 +26378,12 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26463,12 +26431,12 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26516,12 +26484,12 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26569,12 +26537,12 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26622,12 +26590,12 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26675,12 +26643,12 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26728,12 +26696,12 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26781,12 +26749,12 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26834,12 +26802,12 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26887,12 +26855,12 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26940,12 +26908,12 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -26993,12 +26961,12 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27046,12 +27014,12 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27099,12 +27067,12 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27152,12 +27120,12 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27205,12 +27173,12 @@
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27258,12 +27226,12 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27311,12 +27279,12 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27364,12 +27332,12 @@
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27417,12 +27385,12 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27470,12 +27438,12 @@
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27523,12 +27491,12 @@
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27585,12 +27553,12 @@
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>9 days, 16:45:22.216887</t>
+          <t>8 days, 16:39:08.466170</t>
         </is>
       </c>
     </row>
@@ -27638,12 +27606,12 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27695,12 +27663,12 @@
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>8 days, 23:45:22.216804</t>
+          <t>7 days, 23:39:08.466098</t>
         </is>
       </c>
     </row>
@@ -27748,12 +27716,12 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27801,12 +27769,12 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27858,12 +27826,12 @@
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>8 days, 22:45:22.216710</t>
+          <t>7 days, 22:39:08.466006</t>
         </is>
       </c>
     </row>
@@ -27911,12 +27879,12 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -27964,12 +27932,12 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -28017,12 +27985,12 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -28070,12 +28038,12 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -28123,12 +28091,12 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -28176,12 +28144,12 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -28229,12 +28197,12 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -28286,12 +28254,12 @@
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M507" t="inlineStr">
         <is>
-          <t>8 days, 22:30:22.216469</t>
+          <t>7 days, 22:24:08.465776</t>
         </is>
       </c>
     </row>
@@ -28343,12 +28311,12 @@
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M508" t="inlineStr">
         <is>
-          <t>8 days, 22:30:22.216437</t>
+          <t>7 days, 22:24:08.465744</t>
         </is>
       </c>
     </row>
@@ -28396,12 +28364,12 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -28453,12 +28421,12 @@
       </c>
       <c r="K510" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M510" t="inlineStr">
         <is>
-          <t>8 days, 22:30:22.216373</t>
+          <t>7 days, 22:24:08.465659</t>
         </is>
       </c>
     </row>
@@ -28506,12 +28474,12 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -28559,12 +28527,12 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -28616,12 +28584,12 @@
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M513" t="inlineStr">
         <is>
-          <t>8 days, 22:30:22.216280</t>
+          <t>7 days, 22:24:08.465561</t>
         </is>
       </c>
     </row>
@@ -28673,12 +28641,12 @@
       </c>
       <c r="K514" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t>8 days, 22:30:22.216247</t>
+          <t>7 days, 22:24:08.465526</t>
         </is>
       </c>
     </row>
@@ -28731,12 +28699,12 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -28789,12 +28757,12 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -28847,12 +28815,12 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -28905,12 +28873,12 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -28963,12 +28931,12 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29016,12 +28984,12 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29069,12 +29037,12 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29126,12 +29094,12 @@
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M522" t="inlineStr">
         <is>
-          <t>5 days, 16:45:22.215973</t>
+          <t>4 days, 16:39:08.465271</t>
         </is>
       </c>
     </row>
@@ -29179,12 +29147,12 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29232,12 +29200,12 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29285,12 +29253,12 @@
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29338,12 +29306,12 @@
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29391,12 +29359,12 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29448,12 +29416,12 @@
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M528" t="inlineStr">
         <is>
-          <t>5 days, 0:45:22.215786</t>
+          <t>4 days, 0:39:08.465092</t>
         </is>
       </c>
     </row>
@@ -29505,12 +29473,12 @@
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M529" t="inlineStr">
         <is>
-          <t>4 days, 18:45:22.215750</t>
+          <t>3 days, 18:39:08.465056</t>
         </is>
       </c>
     </row>
@@ -29558,12 +29526,12 @@
       <c r="J530" t="inlineStr"/>
       <c r="K530" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29616,12 +29584,12 @@
       <c r="J531" t="inlineStr"/>
       <c r="K531" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29673,12 +29641,12 @@
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M532" t="inlineStr">
         <is>
-          <t>3 days, 20:15:22.215657</t>
+          <t>2 days, 20:09:08.464964</t>
         </is>
       </c>
     </row>
@@ -29726,12 +29694,12 @@
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29779,12 +29747,12 @@
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29832,12 +29800,12 @@
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29885,12 +29853,12 @@
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29934,12 +29902,12 @@
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -29987,12 +29955,12 @@
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30040,12 +30008,12 @@
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30093,12 +30061,12 @@
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30146,12 +30114,12 @@
       <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30199,12 +30167,12 @@
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30252,12 +30220,12 @@
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30305,12 +30273,12 @@
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30358,12 +30326,12 @@
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30411,12 +30379,12 @@
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30464,12 +30432,12 @@
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30517,12 +30485,12 @@
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30570,12 +30538,12 @@
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30623,12 +30591,12 @@
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30676,12 +30644,12 @@
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30729,12 +30697,12 @@
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30782,12 +30750,12 @@
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30835,12 +30803,12 @@
       <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30888,12 +30856,12 @@
       <c r="J555" t="inlineStr"/>
       <c r="K555" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30941,12 +30909,12 @@
       <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -30994,12 +30962,12 @@
       <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31047,12 +31015,12 @@
       <c r="J558" t="inlineStr"/>
       <c r="K558" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31100,12 +31068,12 @@
       <c r="J559" t="inlineStr"/>
       <c r="K559" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31153,12 +31121,12 @@
       <c r="J560" t="inlineStr"/>
       <c r="K560" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31206,12 +31174,12 @@
       <c r="J561" t="inlineStr"/>
       <c r="K561" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31259,12 +31227,12 @@
       <c r="J562" t="inlineStr"/>
       <c r="K562" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31312,12 +31280,12 @@
       <c r="J563" t="inlineStr"/>
       <c r="K563" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31365,12 +31333,12 @@
       <c r="J564" t="inlineStr"/>
       <c r="K564" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31418,12 +31386,12 @@
       <c r="J565" t="inlineStr"/>
       <c r="K565" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31471,12 +31439,12 @@
       <c r="J566" t="inlineStr"/>
       <c r="K566" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31524,12 +31492,12 @@
       <c r="J567" t="inlineStr"/>
       <c r="K567" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31577,12 +31545,12 @@
       <c r="J568" t="inlineStr"/>
       <c r="K568" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31630,12 +31598,12 @@
       <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31683,12 +31651,12 @@
       <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31736,12 +31704,12 @@
       <c r="J571" t="inlineStr"/>
       <c r="K571" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31789,12 +31757,12 @@
       <c r="J572" t="inlineStr"/>
       <c r="K572" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31842,12 +31810,12 @@
       <c r="J573" t="inlineStr"/>
       <c r="K573" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L573" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31895,12 +31863,12 @@
       <c r="J574" t="inlineStr"/>
       <c r="K574" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L574" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -31948,12 +31916,12 @@
       <c r="J575" t="inlineStr"/>
       <c r="K575" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -32001,12 +31969,12 @@
       <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L576" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -32054,12 +32022,12 @@
       <c r="J577" t="inlineStr"/>
       <c r="K577" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L577" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -32107,12 +32075,12 @@
       <c r="J578" t="inlineStr"/>
       <c r="K578" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L578" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -32160,12 +32128,12 @@
       <c r="J579" t="inlineStr"/>
       <c r="K579" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -32213,12 +32181,12 @@
       <c r="J580" t="inlineStr"/>
       <c r="K580" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L580" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -32266,12 +32234,12 @@
       <c r="J581" t="inlineStr"/>
       <c r="K581" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L581" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -32324,12 +32292,12 @@
       <c r="J582" t="inlineStr"/>
       <c r="K582" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L582" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -32382,12 +32350,12 @@
       <c r="J583" t="inlineStr"/>
       <c r="K583" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L583" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -32435,12 +32403,12 @@
       <c r="J584" t="inlineStr"/>
       <c r="K584" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -32492,12 +32460,12 @@
       </c>
       <c r="K585" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M585" t="inlineStr">
         <is>
-          <t>2 days, 18:15:22.214083</t>
+          <t>1 day, 18:09:08.463381</t>
         </is>
       </c>
     </row>
@@ -32549,12 +32517,12 @@
       </c>
       <c r="K586" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M586" t="inlineStr">
         <is>
-          <t>2 days, 17:00:22.213983</t>
+          <t>1 day, 16:54:08.463328</t>
         </is>
       </c>
     </row>
@@ -32602,12 +32570,12 @@
       <c r="J587" t="inlineStr"/>
       <c r="K587" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L587" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -32655,12 +32623,12 @@
       <c r="J588" t="inlineStr"/>
       <c r="K588" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>
@@ -32708,12 +32676,12 @@
       <c r="J589" t="inlineStr"/>
       <c r="K589" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L589" t="inlineStr">
         <is>
-          <t>09/04/26 02:14 PM</t>
+          <t>09/05/26 02:20 PM</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -546,12 +546,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>22 days, 16:39:08.481465</t>
+          <t>21 days, 14:28:25.152119</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -652,12 +652,12 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>18 days, 20:24:08.481205</t>
+          <t>17 days, 18:13:25.151866</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>18 days, 20:24:08.481151</t>
+          <t>17 days, 18:13:25.151815</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>18 days, 19:39:08.481111</t>
+          <t>17 days, 17:28:25.151774</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>18 days, 19:39:08.481073</t>
+          <t>17 days, 17:28:25.151735</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>18 days, 19:39:08.481035</t>
+          <t>17 days, 17:28:25.151696</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>18 days, 19:39:08.480998</t>
+          <t>17 days, 17:28:25.151658</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>18 days, 19:39:08.480962</t>
+          <t>17 days, 17:28:25.151592</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18 days, 19:39:08.480927</t>
+          <t>17 days, 17:28:25.151554</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>18 days, 19:39:08.480892</t>
+          <t>17 days, 17:28:25.151517</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>18 days, 19:39:08.480858</t>
+          <t>17 days, 17:28:25.151481</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>18 days, 19:39:08.480823</t>
+          <t>17 days, 17:28:25.151444</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>18 days, 19:39:08.480787</t>
+          <t>17 days, 17:28:25.151406</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>18 days, 19:39:08.480751</t>
+          <t>17 days, 17:28:25.151369</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>18 days, 19:39:08.480717</t>
+          <t>17 days, 17:28:25.151335</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480640</t>
+          <t>17 days, 14:28:25.151301</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480598</t>
+          <t>17 days, 14:28:25.151267</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480563</t>
+          <t>17 days, 14:28:25.151233</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480529</t>
+          <t>17 days, 14:28:25.151199</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480496</t>
+          <t>17 days, 14:28:25.151165</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480462</t>
+          <t>17 days, 14:28:25.151132</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480428</t>
+          <t>17 days, 14:28:25.151100</t>
         </is>
       </c>
     </row>
@@ -2012,12 +2012,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480395</t>
+          <t>17 days, 14:28:25.151068</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480356</t>
+          <t>17 days, 14:28:25.151035</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480321</t>
+          <t>17 days, 14:28:25.151001</t>
         </is>
       </c>
     </row>
@@ -2183,12 +2183,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480289</t>
+          <t>17 days, 14:28:25.150968</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480255</t>
+          <t>17 days, 14:28:25.150934</t>
         </is>
       </c>
     </row>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480223</t>
+          <t>17 days, 14:28:25.150901</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2350,12 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -2403,12 +2403,12 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -2456,12 +2456,12 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480099</t>
+          <t>17 days, 14:28:25.150776</t>
         </is>
       </c>
     </row>
@@ -2570,12 +2570,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.480062</t>
+          <t>17 days, 14:28:25.150740</t>
         </is>
       </c>
     </row>
@@ -2623,12 +2623,12 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.479999</t>
+          <t>17 days, 14:28:25.150674</t>
         </is>
       </c>
     </row>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.479966</t>
+          <t>17 days, 14:28:25.150617</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.479932</t>
+          <t>17 days, 14:28:25.150578</t>
         </is>
       </c>
     </row>
@@ -2851,12 +2851,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.479900</t>
+          <t>17 days, 14:28:25.150545</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2954,19 +2954,15 @@
           <t>09/25/26 07:00 am</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>WGL07 - Not yet responded</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>18 days, 16:39:08.479839</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -3018,12 +3014,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.479807</t>
+          <t>17 days, 14:28:25.150455</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3067,12 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -3128,12 +3124,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.479745</t>
+          <t>17 days, 14:28:25.150391</t>
         </is>
       </c>
     </row>
@@ -3181,12 +3177,12 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3230,12 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -3291,12 +3287,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>18 days, 16:39:08.479631</t>
+          <t>17 days, 14:28:25.150303</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3344,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479596</t>
+          <t>16 days, 18:58:25.150269</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3401,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479564</t>
+          <t>16 days, 18:58:25.150237</t>
         </is>
       </c>
     </row>
@@ -3462,12 +3458,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479532</t>
+          <t>16 days, 18:58:25.150204</t>
         </is>
       </c>
     </row>
@@ -3519,12 +3515,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479500</t>
+          <t>16 days, 18:58:25.150171</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3572,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479468</t>
+          <t>16 days, 18:58:25.150137</t>
         </is>
       </c>
     </row>
@@ -3633,12 +3629,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479433</t>
+          <t>16 days, 18:58:25.150102</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3686,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479399</t>
+          <t>16 days, 18:58:25.150068</t>
         </is>
       </c>
     </row>
@@ -3747,12 +3743,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479366</t>
+          <t>16 days, 18:58:25.150035</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3800,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479332</t>
+          <t>16 days, 18:58:25.150001</t>
         </is>
       </c>
     </row>
@@ -3861,12 +3857,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479298</t>
+          <t>16 days, 18:58:25.149967</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3914,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479258</t>
+          <t>16 days, 18:58:25.149935</t>
         </is>
       </c>
     </row>
@@ -3975,12 +3971,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479223</t>
+          <t>16 days, 18:58:25.149903</t>
         </is>
       </c>
     </row>
@@ -4032,12 +4028,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479192</t>
+          <t>16 days, 18:58:25.149871</t>
         </is>
       </c>
     </row>
@@ -4089,12 +4085,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479162</t>
+          <t>16 days, 18:58:25.149840</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4142,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>17 days, 21:09:08.479130</t>
+          <t>16 days, 18:58:25.149809</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4199,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>16 days, 17:54:08.479099</t>
+          <t>15 days, 15:43:25.149778</t>
         </is>
       </c>
     </row>
@@ -4261,12 +4257,12 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4315,12 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4377,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>16 days, 17:39:08.478978</t>
+          <t>15 days, 15:28:25.149668</t>
         </is>
       </c>
     </row>
@@ -4439,12 +4435,12 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4488,12 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -4545,12 +4541,12 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4599,12 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -4661,12 +4657,12 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -4719,12 +4715,12 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -4777,12 +4773,12 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -4835,12 +4831,12 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -4893,12 +4889,12 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -4951,12 +4947,12 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5004,12 +5000,12 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5057,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>14 days, 19:39:08.478532</t>
+          <t>13 days, 17:28:25.149248</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5110,12 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5168,12 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5226,12 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5284,12 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5346,12 +5342,12 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5400,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5462,12 +5458,12 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5520,12 +5516,12 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5578,12 +5574,12 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5636,12 +5632,12 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5698,12 +5694,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>14 days, 17:09:08.478186</t>
+          <t>13 days, 14:58:25.148917</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5752,12 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5814,12 +5810,12 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5872,12 +5868,12 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5930,12 +5926,12 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -5988,12 +5984,12 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6046,12 +6042,12 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6104,12 +6100,12 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6162,12 +6158,12 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6220,12 +6216,12 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6278,12 +6274,12 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6336,12 +6332,12 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6394,12 +6390,12 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6452,12 +6448,12 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6510,12 +6506,12 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6564,12 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6626,12 +6622,12 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6680,12 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6742,12 +6738,12 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6796,12 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6858,12 +6854,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6916,12 +6912,12 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6970,12 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7028,12 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7086,12 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -7143,12 +7139,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -7200,12 +7196,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>11 days, 19:39:08.477369</t>
+          <t>10 days, 17:28:25.148087</t>
         </is>
       </c>
     </row>
@@ -7257,12 +7253,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>11 days, 19:39:08.477330</t>
+          <t>10 days, 17:28:25.148048</t>
         </is>
       </c>
     </row>
@@ -7314,12 +7310,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>11 days, 19:39:08.477292</t>
+          <t>10 days, 17:28:25.148008</t>
         </is>
       </c>
     </row>
@@ -7371,12 +7367,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>11 days, 19:39:08.477257</t>
+          <t>10 days, 17:28:25.147971</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7420,12 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -7477,12 +7473,12 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -7530,12 +7526,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -7583,12 +7579,12 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -7636,12 +7632,12 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -7689,12 +7685,12 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -7742,12 +7738,12 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7791,12 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -7848,12 +7844,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -7905,12 +7901,12 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>10 days, 22:24:08.476934</t>
+          <t>9 days, 20:13:25.147617</t>
         </is>
       </c>
     </row>
@@ -7963,12 +7959,12 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8012,12 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8065,12 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8122,12 +8118,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8149,7 +8145,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8172,19 +8168,15 @@
           <t>09/17/26 12:00 pm</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>VDC &amp; WGL07 - Not complete/In progress</t>
-        </is>
-      </c>
+      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>10 days, 21:39:08.476759</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8232,12 +8224,12 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8285,12 +8277,12 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8343,12 +8335,12 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8401,12 +8393,12 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8454,12 +8446,12 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8507,12 +8499,12 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8560,12 +8552,12 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8613,12 +8605,12 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8666,12 +8658,12 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8719,12 +8711,12 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8772,12 +8764,12 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8825,12 +8817,12 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8878,12 +8870,12 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8931,12 +8923,12 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -8984,12 +8976,12 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9029,12 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9090,12 +9082,12 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9143,12 +9135,12 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9196,12 +9188,12 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9249,12 +9241,12 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9306,12 +9298,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>10 days, 18:54:08.476106</t>
+          <t>9 days, 16:43:25.146811</t>
         </is>
       </c>
     </row>
@@ -9359,12 +9351,12 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9412,12 +9404,12 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9465,12 +9457,12 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9518,12 +9510,12 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9571,12 +9563,12 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9628,12 +9620,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>10 days, 18:54:08.475917</t>
+          <t>9 days, 16:43:25.146600</t>
         </is>
       </c>
     </row>
@@ -9685,12 +9677,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>10 days, 18:54:08.475879</t>
+          <t>9 days, 16:43:25.146559</t>
         </is>
       </c>
     </row>
@@ -9738,12 +9730,12 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9791,12 +9783,12 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9844,12 +9836,12 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9897,12 +9889,12 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -9950,12 +9942,12 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10003,12 +9995,12 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10052,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>10 days, 17:54:08.475639</t>
+          <t>9 days, 15:43:25.146352</t>
         </is>
       </c>
     </row>
@@ -10113,12 +10105,12 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10158,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10219,12 +10211,12 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10272,12 +10264,12 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10317,12 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10378,12 +10370,12 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10431,12 +10423,12 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10484,12 +10476,12 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10537,12 +10529,12 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10590,12 +10582,12 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10643,12 +10635,12 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10688,12 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10749,12 +10741,12 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10802,12 +10794,12 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10855,12 +10847,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10908,12 +10900,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -10961,12 +10953,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11014,12 +11006,12 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11067,12 +11059,12 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11120,12 +11112,12 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11173,12 +11165,12 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11226,12 +11218,12 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11279,12 +11271,12 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11332,12 +11324,12 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11377,12 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11438,12 +11430,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11491,12 +11483,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11544,12 +11536,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11597,12 +11589,12 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11650,12 +11642,12 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11703,12 +11695,12 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11756,12 +11748,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11809,12 +11801,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11862,12 +11854,12 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11915,12 +11907,12 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -11968,12 +11960,12 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12021,12 +12013,12 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12066,12 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12127,12 +12119,12 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12180,12 +12172,12 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12233,12 +12225,12 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12286,12 +12278,12 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12339,12 +12331,12 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12392,12 +12384,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12445,12 +12437,12 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12498,12 +12490,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12555,12 +12547,12 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>10 days, 17:24:08.474197</t>
+          <t>9 days, 15:13:25.144939</t>
         </is>
       </c>
     </row>
@@ -12608,12 +12600,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12661,12 +12653,12 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12714,12 +12706,12 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12767,12 +12759,12 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12820,12 +12812,12 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12865,12 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12926,12 +12918,12 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -12979,12 +12971,12 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13032,12 +13024,12 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13085,12 +13077,12 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13138,12 +13130,12 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13191,12 +13183,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13244,12 +13236,12 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13297,12 +13289,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13350,12 +13342,12 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13403,12 +13395,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13456,12 +13448,12 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13509,12 +13501,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13562,12 +13554,12 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13615,12 +13607,12 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13668,12 +13660,12 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13721,12 +13713,12 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13774,12 +13766,12 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13827,12 +13819,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13880,12 +13872,12 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13933,12 +13925,12 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -13986,12 +13978,12 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>09/05/26 02:20 PM</t>
+          <t>09/06/26 04:31 PM</t>
         </is>
       </c>
     </row>
@@ -14039,12 +14031,12 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>